--- a/src/main/resources/templates/excel/interim_template.xlsx
+++ b/src/main/resources/templates/excel/interim_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PUJ\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IUIU\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DC586A-FE35-438A-B55F-6ACC735DD5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC189416-377B-4A8A-BA68-335EC95F031E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="1" r:id="rId1"/>
@@ -843,7 +843,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>기성내역서</t>
   </si>
@@ -947,9 +947,6 @@
     <t>총 용 역 비</t>
   </si>
   <si>
-    <t>백단위 절사(낙찰율 94%)</t>
-  </si>
-  <si>
     <t>부동산종합공부시스템 국산 공간정보 SW 유지보수 용역 내역</t>
   </si>
   <si>
@@ -992,26 +989,28 @@
     <t xml:space="preserve">      2026년도</t>
   </si>
   <si>
-    <t>부동산종합공부시스템 국산 공간정보 SW 유지보수 용역</t>
-  </si>
-  <si>
-    <t>강릉시</t>
-  </si>
-  <si>
-    <t>가. 용    역     명 : 부동산종합공부시스템 국산 공간정보 SW 유지보수 용역</t>
-  </si>
-  <si>
-    <t>나. 계  약  금  액 : 금8,670,000원(금팔백육십칠만원)</t>
-  </si>
-  <si>
-    <t>바. 금회기성신청금액 : 금4,335,000원(금사백삼십삼만오천원)</t>
-  </si>
-  <si>
     <t>사. 수행기간: 2026.01~2026.12(12개월)</t>
   </si>
   <si>
-    <t>연간 유지관리비
-(낙찰율 94%)</t>
+    <t>양주시</t>
+  </si>
+  <si>
+    <t>가. 용    역     명 : 2026년 부동산종합공부시스템 GeoNURIS for KRAS v1.0 유지보수 용역</t>
+  </si>
+  <si>
+    <t>2026년 부동산종합공부시스템 GeoNURIS for KRAS v1.0 유지보수 용역</t>
+    <phoneticPr fontId="69" type="noConversion"/>
+  </si>
+  <si>
+    <t>연간 유지관리비</t>
+    <phoneticPr fontId="69" type="noConversion"/>
+  </si>
+  <si>
+    <t>바. 금회기성신청금액 : 금4,620,000원(금사백육십이만원)</t>
+    <phoneticPr fontId="69" type="noConversion"/>
+  </si>
+  <si>
+    <t>나. 계  약  금  액 : 금9,240,000원(금구백이십사만원)</t>
     <phoneticPr fontId="69" type="noConversion"/>
   </si>
 </sst>
@@ -1067,7 +1066,7 @@
     <numFmt numFmtId="220" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* \-_-;_-@_-"/>
     <numFmt numFmtId="221" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-_-;_-@_-"/>
     <numFmt numFmtId="222" formatCode="0&quot; 개월&quot;"/>
-    <numFmt numFmtId="224" formatCode="0\ &quot;개월&quot;"/>
+    <numFmt numFmtId="223" formatCode="0\ &quot;개월&quot;"/>
   </numFmts>
   <fonts count="70">
     <font>
@@ -2719,47 +2718,8 @@
   </cellStyleXfs>
   <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="1" xfId="461" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="461" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="461" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="14" xfId="460" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="216" fontId="37" fillId="0" borderId="0" xfId="460" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="215" fontId="37" fillId="0" borderId="0" xfId="460" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="460" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="460" applyFont="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="460" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="460" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="0" xfId="460" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="14" xfId="460" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="460" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="12" xfId="460" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="460" applyFont="1">
       <alignment vertical="center"/>
@@ -2874,9 +2834,6 @@
     </xf>
     <xf numFmtId="183" fontId="53" fillId="0" borderId="0" xfId="421" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="461" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="461" applyFont="1">
       <alignment vertical="center"/>
@@ -3140,11 +3097,56 @@
     <xf numFmtId="183" fontId="57" fillId="0" borderId="0" xfId="459" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="223" fontId="63" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="12" xfId="460" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="460" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="0" xfId="460" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="460" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="14" xfId="460" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="460" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="460" applyFont="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="460" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="215" fontId="37" fillId="0" borderId="0" xfId="460" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="216" fontId="37" fillId="0" borderId="0" xfId="460" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="461" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="461" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="1" xfId="461" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="183" fontId="55" fillId="2" borderId="19" xfId="421" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="183" fontId="55" fillId="2" borderId="18" xfId="421" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="64" fillId="8" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="distributed" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="58" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3158,8 +3160,11 @@
     <xf numFmtId="49" fontId="61" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="64" fillId="8" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="distributed" vertical="center"/>
+    <xf numFmtId="183" fontId="63" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="63" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="19" xfId="459" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3176,14 +3181,8 @@
     <xf numFmtId="183" fontId="67" fillId="8" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="63" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="63" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="224" fontId="63" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="14" xfId="460" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="467">
@@ -33427,221 +33426,221 @@
   <dimension ref="A1:IW112"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="20.25"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="15" customWidth="1"/>
-    <col min="2" max="2" width="20" style="15" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" style="15" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" style="15" customWidth="1"/>
-    <col min="5" max="5" width="7.77734375" style="15" customWidth="1"/>
-    <col min="6" max="6" width="19.77734375" style="15" customWidth="1"/>
-    <col min="7" max="7" width="7.77734375" style="15" customWidth="1"/>
-    <col min="8" max="8" width="19.77734375" style="15" customWidth="1"/>
-    <col min="9" max="9" width="7.77734375" style="15" customWidth="1"/>
-    <col min="10" max="10" width="19.77734375" style="15" customWidth="1"/>
-    <col min="11" max="257" width="8.88671875" style="15"/>
+    <col min="1" max="1" width="7.77734375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20" style="2" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.77734375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19.77734375" style="2" customWidth="1"/>
+    <col min="11" max="257" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="16"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="18"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="5"/>
     </row>
     <row r="2" spans="1:10" ht="60" customHeight="1">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="22"/>
+      <c r="A2" s="137"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="28"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1">
-      <c r="A4" s="23"/>
-      <c r="B4" s="13" t="s">
-        <v>47</v>
+      <c r="A4" s="10"/>
+      <c r="B4" s="138" t="s">
+        <v>46</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="J4" s="28"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="J4" s="15"/>
     </row>
     <row r="5" spans="1:10" ht="50.1" customHeight="1">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="164" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="164"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="164"/>
+      <c r="E5" s="164"/>
+      <c r="F5" s="164"/>
+      <c r="G5" s="164"/>
+      <c r="H5" s="164"/>
+      <c r="I5" s="164"/>
+      <c r="J5" s="164"/>
+    </row>
+    <row r="6" spans="1:10" ht="45" customHeight="1">
+      <c r="A6" s="16"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="139"/>
+      <c r="E6" s="139"/>
+      <c r="F6" s="139"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="139"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7" spans="1:10" ht="89.25" customHeight="1">
+      <c r="A7" s="18"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1">
+      <c r="A8" s="22"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="142"/>
+      <c r="D8" s="142"/>
+      <c r="E8" s="142"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" spans="1:10" ht="30" customHeight="1">
+      <c r="A9" s="22"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="142"/>
+      <c r="D9" s="142"/>
+      <c r="E9" s="142"/>
+      <c r="F9" s="142"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="142"/>
+      <c r="I9" s="142"/>
+      <c r="J9" s="25"/>
+    </row>
+    <row r="10" spans="1:10" ht="30.75" customHeight="1">
+      <c r="A10" s="22"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="25"/>
+    </row>
+    <row r="11" spans="1:10" ht="30" customHeight="1">
+      <c r="A11" s="22"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="146"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="25"/>
+    </row>
+    <row r="12" spans="1:10" ht="78" customHeight="1">
+      <c r="A12" s="141" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
+      <c r="B12" s="141"/>
+      <c r="C12" s="141"/>
+      <c r="D12" s="141"/>
+      <c r="E12" s="141"/>
+      <c r="F12" s="141"/>
+      <c r="G12" s="141"/>
+      <c r="H12" s="141"/>
+      <c r="I12" s="141"/>
+      <c r="J12" s="141"/>
     </row>
-    <row r="6" spans="1:10" ht="45" customHeight="1">
-      <c r="A6" s="29"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="11" t="s">
+    <row r="13" spans="1:10" ht="30" customHeight="1">
+      <c r="A13" s="22"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="31"/>
+    </row>
+    <row r="14" spans="1:10" ht="30" customHeight="1">
+      <c r="A14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="36"/>
+    </row>
+    <row r="17" spans="6:6">
+      <c r="F17" s="37"/>
+    </row>
+    <row r="108" spans="2:7">
+      <c r="B108" s="2">
+        <v>0.49852999999999997</v>
+      </c>
+      <c r="C108" s="2">
+        <v>6.6299999999999998E-2</v>
+      </c>
+      <c r="D108" s="2">
+        <v>8.6709999999999995E-2</v>
+      </c>
+      <c r="E108" s="2">
         <v>0</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" spans="1:10" ht="89.25" customHeight="1">
-      <c r="A7" s="31"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="34"/>
-    </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1">
-      <c r="A8" s="35"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="36"/>
-    </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1">
-      <c r="A9" s="35"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="38"/>
-    </row>
-    <row r="10" spans="1:10" ht="30.75" customHeight="1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="38"/>
-    </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1">
-      <c r="A11" s="35"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="38"/>
-    </row>
-    <row r="12" spans="1:10" ht="78" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1">
-      <c r="A13" s="35"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="44"/>
-    </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1">
-      <c r="A14" s="45"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="49"/>
-    </row>
-    <row r="17" spans="6:6">
-      <c r="F17" s="50"/>
-    </row>
-    <row r="108" spans="2:7">
-      <c r="B108" s="15">
-        <v>0.49852999999999997</v>
-      </c>
-      <c r="C108" s="15">
-        <v>6.6299999999999998E-2</v>
-      </c>
-      <c r="D108" s="15">
-        <v>8.6709999999999995E-2</v>
-      </c>
-      <c r="E108" s="15">
+      <c r="F108" s="2">
         <v>0</v>
       </c>
-      <c r="F108" s="15">
-        <v>0</v>
-      </c>
-      <c r="G108" s="15">
+      <c r="G108" s="2">
         <v>6.8974599999999997</v>
       </c>
     </row>
     <row r="112" spans="2:7">
-      <c r="C112" s="15">
+      <c r="C112" s="2">
         <v>65.010999999999996</v>
       </c>
-      <c r="D112" s="15">
+      <c r="D112" s="2">
         <v>0</v>
       </c>
-      <c r="E112" s="15">
+      <c r="E112" s="2">
         <v>0</v>
       </c>
     </row>
@@ -33663,7 +33662,7 @@
   <phoneticPr fontId="69" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="82" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -33684,160 +33683,160 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="147" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
     </row>
     <row r="2" spans="1:13" ht="24">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
     </row>
     <row r="3" spans="1:13" ht="24">
-      <c r="A3" s="2" t="s">
-        <v>50</v>
+      <c r="A3" s="148" t="s">
+        <v>49</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="51"/>
+      <c r="B3" s="148"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="38"/>
     </row>
     <row r="4" spans="1:13" ht="24">
-      <c r="A4" s="2" t="s">
-        <v>51</v>
+      <c r="A4" s="148" t="s">
+        <v>53</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="51"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="38"/>
     </row>
     <row r="5" spans="1:13" ht="24">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="51"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="148"/>
+      <c r="G5" s="148"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="38"/>
     </row>
     <row r="6" spans="1:13" ht="24">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="148" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="51"/>
+      <c r="B6" s="148"/>
+      <c r="C6" s="148"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="148"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="38"/>
     </row>
     <row r="7" spans="1:13" ht="24">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="148" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="51"/>
+      <c r="B7" s="148"/>
+      <c r="C7" s="148"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="148"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="38"/>
     </row>
     <row r="8" spans="1:13" ht="24">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="148" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="51"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="38"/>
     </row>
     <row r="9" spans="1:13" ht="24">
-      <c r="A9" s="53" t="s">
-        <v>53</v>
+      <c r="A9" s="1" t="s">
+        <v>47</v>
       </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="51"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="38"/>
     </row>
     <row r="10" spans="1:13" ht="24">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="148" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="51"/>
+      <c r="B10" s="148"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="148"/>
+      <c r="F10" s="148"/>
+      <c r="G10" s="148"/>
+      <c r="H10" s="148"/>
+      <c r="I10" s="148"/>
+      <c r="J10" s="38"/>
     </row>
     <row r="11" spans="1:13" ht="5.0999999999999996" customHeight="1">
-      <c r="A11" s="55"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="56"/>
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="42"/>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="43" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="150" t="s">
@@ -33858,199 +33857,199 @@
       <c r="J12" s="151"/>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="58" t="s">
+      <c r="A13" s="149"/>
+      <c r="B13" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="59" t="s">
+      <c r="E13" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="58" t="s">
+      <c r="F13" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="59" t="s">
+      <c r="G13" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="58" t="s">
+      <c r="H13" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="59" t="s">
+      <c r="I13" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="58" t="s">
+      <c r="J13" s="44" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="24" customHeight="1">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="61">
+      <c r="B14" s="47">
         <f>총괄표!H5</f>
-        <v>7882560</v>
+        <v>8400000</v>
       </c>
-      <c r="C14" s="62">
+      <c r="C14" s="48">
         <v>0</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="49">
         <v>0</v>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="50">
         <f>총괄표!F5</f>
-        <v>3941280</v>
+        <v>4200000</v>
       </c>
-      <c r="F14" s="65">
+      <c r="F14" s="51">
         <v>0.5</v>
       </c>
-      <c r="G14" s="66">
+      <c r="G14" s="52">
         <f>E14</f>
-        <v>3941280</v>
+        <v>4200000</v>
       </c>
-      <c r="H14" s="65">
+      <c r="H14" s="51">
         <f>D14+F14</f>
         <v>0.5</v>
       </c>
-      <c r="I14" s="62">
+      <c r="I14" s="48">
         <f>총괄표!G5</f>
-        <v>3941280</v>
+        <v>4200000</v>
       </c>
-      <c r="J14" s="67">
+      <c r="J14" s="53">
         <f>100%-H14</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="69">
+      <c r="B15" s="55">
         <f>B14</f>
-        <v>7882560</v>
+        <v>8400000</v>
       </c>
-      <c r="C15" s="70">
+      <c r="C15" s="56">
         <v>0</v>
       </c>
-      <c r="D15" s="71"/>
-      <c r="E15" s="70">
+      <c r="D15" s="57"/>
+      <c r="E15" s="56">
         <f>E14</f>
-        <v>3941280</v>
+        <v>4200000</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="72">
+      <c r="F15" s="51"/>
+      <c r="G15" s="58">
         <f>G14</f>
-        <v>3941280</v>
+        <v>4200000</v>
       </c>
-      <c r="H15" s="73"/>
-      <c r="I15" s="70">
+      <c r="H15" s="59"/>
+      <c r="I15" s="56">
         <f>I14</f>
-        <v>3941280</v>
+        <v>4200000</v>
       </c>
-      <c r="J15" s="73"/>
-      <c r="M15" s="74"/>
+      <c r="J15" s="59"/>
+      <c r="M15" s="60"/>
     </row>
     <row r="16" spans="1:13" ht="24" customHeight="1">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="75">
+      <c r="B16" s="61">
         <f>B15*0.1</f>
-        <v>788256</v>
+        <v>840000</v>
       </c>
-      <c r="C16" s="76">
+      <c r="C16" s="62">
         <v>0</v>
       </c>
-      <c r="D16" s="77"/>
-      <c r="E16" s="76">
+      <c r="D16" s="63"/>
+      <c r="E16" s="62">
         <f>E15*0.1</f>
-        <v>394128</v>
+        <v>420000</v>
       </c>
-      <c r="F16" s="77"/>
-      <c r="G16" s="78">
+      <c r="F16" s="63"/>
+      <c r="G16" s="64">
         <f>G15*0.1</f>
-        <v>394128</v>
+        <v>420000</v>
       </c>
-      <c r="H16" s="79"/>
-      <c r="I16" s="76">
+      <c r="H16" s="65"/>
+      <c r="I16" s="62">
         <f>I15*0.1</f>
-        <v>394128</v>
+        <v>420000</v>
       </c>
-      <c r="J16" s="79"/>
+      <c r="J16" s="65"/>
     </row>
     <row r="17" spans="1:13" ht="24" customHeight="1">
-      <c r="A17" s="80" t="s">
+      <c r="A17" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="81">
+      <c r="B17" s="67">
         <f>B15+B16</f>
-        <v>8670816</v>
+        <v>9240000</v>
       </c>
-      <c r="C17" s="81"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="81">
+      <c r="C17" s="67"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="67">
         <f>E15+E16</f>
-        <v>4335408</v>
+        <v>4620000</v>
       </c>
-      <c r="F17" s="82"/>
-      <c r="G17" s="83">
+      <c r="F17" s="68"/>
+      <c r="G17" s="69">
         <f>G15+G16</f>
-        <v>4335408</v>
+        <v>4620000</v>
       </c>
-      <c r="H17" s="84"/>
-      <c r="I17" s="83">
+      <c r="H17" s="70"/>
+      <c r="I17" s="69">
         <f>I15+I16</f>
-        <v>4335408</v>
+        <v>4620000</v>
       </c>
-      <c r="J17" s="84"/>
+      <c r="J17" s="70"/>
     </row>
     <row r="18" spans="1:13" ht="24" customHeight="1">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="86">
-        <f>ROUNDDOWN(B17*1,-3)</f>
-        <v>8670000</v>
+      <c r="B18" s="72">
+        <f>B17</f>
+        <v>9240000</v>
       </c>
-      <c r="C18" s="87" t="s">
+      <c r="C18" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="87"/>
-      <c r="E18" s="86">
-        <f>ROUNDDOWN(E17*1,-3)</f>
-        <v>4335000</v>
+      <c r="D18" s="73"/>
+      <c r="E18" s="72">
+        <f>E17</f>
+        <v>4620000</v>
       </c>
-      <c r="F18" s="87"/>
-      <c r="G18" s="86">
-        <f>ROUNDDOWN(G17*1,-3)</f>
-        <v>4335000</v>
+      <c r="F18" s="73"/>
+      <c r="G18" s="72">
+        <f>G17</f>
+        <v>4620000</v>
       </c>
-      <c r="H18" s="88"/>
-      <c r="I18" s="86">
-        <f>ROUNDDOWN(I17*1,-3)</f>
-        <v>4335000</v>
+      <c r="H18" s="74"/>
+      <c r="I18" s="72">
+        <f>I17</f>
+        <v>4620000</v>
       </c>
-      <c r="J18" s="88"/>
-      <c r="M18" s="89"/>
+      <c r="J18" s="74"/>
+      <c r="M18" s="75"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="M19" s="89"/>
+      <c r="M19" s="75"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="E20" s="74"/>
+      <c r="E20" s="60"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="B21" s="90"/>
+      <c r="B21" s="76"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="B22" s="90"/>
+      <c r="B22" s="76"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="B24" s="90"/>
+      <c r="B24" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -34082,1690 +34081,1688 @@
   <dimension ref="A1:IW18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1" style="91" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" style="91" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" style="91" customWidth="1"/>
-    <col min="4" max="8" width="20.77734375" style="91" customWidth="1"/>
-    <col min="9" max="9" width="31" style="91" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" style="92" customWidth="1"/>
-    <col min="11" max="11" width="15" style="93" customWidth="1"/>
-    <col min="12" max="12" width="21.21875" style="93" customWidth="1"/>
-    <col min="13" max="13" width="28.109375" style="94" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" style="94" customWidth="1"/>
-    <col min="15" max="257" width="8.88671875" style="91"/>
+    <col min="1" max="1" width="1" style="77" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" style="77" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" style="77" customWidth="1"/>
+    <col min="4" max="8" width="20.77734375" style="77" customWidth="1"/>
+    <col min="9" max="9" width="31" style="77" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" style="78" customWidth="1"/>
+    <col min="11" max="11" width="15" style="79" customWidth="1"/>
+    <col min="12" max="12" width="21.21875" style="79" customWidth="1"/>
+    <col min="13" max="13" width="28.109375" style="80" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" style="80" customWidth="1"/>
+    <col min="15" max="257" width="8.88671875" style="77"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:257" ht="51.75" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="153" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="95"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
-      <c r="W1" s="96"/>
-      <c r="X1" s="96"/>
-      <c r="Y1" s="96"/>
-      <c r="Z1" s="96"/>
-      <c r="AA1" s="96"/>
-      <c r="AB1" s="96"/>
-      <c r="AC1" s="96"/>
-      <c r="AD1" s="96"/>
-      <c r="AE1" s="96"/>
-      <c r="AF1" s="96"/>
-      <c r="AG1" s="96"/>
-      <c r="AH1" s="96"/>
-      <c r="AI1" s="96"/>
-      <c r="AJ1" s="96"/>
-      <c r="AK1" s="96"/>
-      <c r="AL1" s="96"/>
-      <c r="AM1" s="96"/>
-      <c r="AN1" s="96"/>
-      <c r="AO1" s="96"/>
-      <c r="AP1" s="96"/>
-      <c r="AQ1" s="96"/>
-      <c r="AR1" s="96"/>
-      <c r="AS1" s="96"/>
-      <c r="AT1" s="96"/>
-      <c r="AU1" s="96"/>
-      <c r="AV1" s="96"/>
-      <c r="AW1" s="96"/>
-      <c r="AX1" s="96"/>
-      <c r="AY1" s="96"/>
-      <c r="AZ1" s="96"/>
-      <c r="BA1" s="96"/>
-      <c r="BB1" s="96"/>
-      <c r="BC1" s="96"/>
-      <c r="BD1" s="96"/>
-      <c r="BE1" s="96"/>
-      <c r="BF1" s="96"/>
-      <c r="BG1" s="96"/>
-      <c r="BH1" s="96"/>
-      <c r="BI1" s="96"/>
-      <c r="BJ1" s="96"/>
-      <c r="BK1" s="96"/>
-      <c r="BL1" s="96"/>
-      <c r="BM1" s="96"/>
-      <c r="BN1" s="96"/>
-      <c r="BO1" s="96"/>
-      <c r="BP1" s="96"/>
-      <c r="BQ1" s="96"/>
-      <c r="BR1" s="96"/>
-      <c r="BS1" s="96"/>
-      <c r="BT1" s="96"/>
-      <c r="BU1" s="96"/>
-      <c r="BV1" s="96"/>
-      <c r="BW1" s="96"/>
-      <c r="BX1" s="96"/>
-      <c r="BY1" s="96"/>
-      <c r="BZ1" s="96"/>
-      <c r="CA1" s="96"/>
-      <c r="CB1" s="96"/>
-      <c r="CC1" s="96"/>
-      <c r="CD1" s="96"/>
-      <c r="CE1" s="96"/>
-      <c r="CF1" s="96"/>
-      <c r="CG1" s="96"/>
-      <c r="CH1" s="96"/>
-      <c r="CI1" s="96"/>
-      <c r="CJ1" s="96"/>
-      <c r="CK1" s="96"/>
-      <c r="CL1" s="96"/>
-      <c r="CM1" s="96"/>
-      <c r="CN1" s="96"/>
-      <c r="CO1" s="96"/>
-      <c r="CP1" s="96"/>
-      <c r="CQ1" s="96"/>
-      <c r="CR1" s="96"/>
-      <c r="CS1" s="96"/>
-      <c r="CT1" s="96"/>
-      <c r="CU1" s="96"/>
-      <c r="CV1" s="96"/>
-      <c r="CW1" s="96"/>
-      <c r="CX1" s="96"/>
-      <c r="CY1" s="96"/>
-      <c r="CZ1" s="96"/>
-      <c r="DA1" s="96"/>
-      <c r="DB1" s="96"/>
-      <c r="DC1" s="96"/>
-      <c r="DD1" s="96"/>
-      <c r="DE1" s="96"/>
-      <c r="DF1" s="96"/>
-      <c r="DG1" s="96"/>
-      <c r="DH1" s="96"/>
-      <c r="DI1" s="96"/>
-      <c r="DJ1" s="96"/>
-      <c r="DK1" s="96"/>
-      <c r="DL1" s="96"/>
-      <c r="DM1" s="96"/>
-      <c r="DN1" s="96"/>
-      <c r="DO1" s="96"/>
-      <c r="DP1" s="96"/>
-      <c r="DQ1" s="96"/>
-      <c r="DR1" s="96"/>
-      <c r="DS1" s="96"/>
-      <c r="DT1" s="96"/>
-      <c r="DU1" s="96"/>
-      <c r="DV1" s="96"/>
-      <c r="DW1" s="96"/>
-      <c r="DX1" s="96"/>
-      <c r="DY1" s="96"/>
-      <c r="DZ1" s="96"/>
-      <c r="EA1" s="96"/>
-      <c r="EB1" s="96"/>
-      <c r="EC1" s="96"/>
-      <c r="ED1" s="96"/>
-      <c r="EE1" s="96"/>
-      <c r="EF1" s="96"/>
-      <c r="EG1" s="96"/>
-      <c r="EH1" s="96"/>
-      <c r="EI1" s="96"/>
-      <c r="EJ1" s="96"/>
-      <c r="EK1" s="96"/>
-      <c r="EL1" s="96"/>
-      <c r="EM1" s="96"/>
-      <c r="EN1" s="96"/>
-      <c r="EO1" s="96"/>
-      <c r="EP1" s="96"/>
-      <c r="EQ1" s="96"/>
-      <c r="ER1" s="96"/>
-      <c r="ES1" s="96"/>
-      <c r="ET1" s="96"/>
-      <c r="EU1" s="96"/>
-      <c r="EV1" s="96"/>
-      <c r="EW1" s="96"/>
-      <c r="EX1" s="96"/>
-      <c r="EY1" s="96"/>
-      <c r="EZ1" s="96"/>
-      <c r="FA1" s="96"/>
-      <c r="FB1" s="96"/>
-      <c r="FC1" s="96"/>
-      <c r="FD1" s="96"/>
-      <c r="FE1" s="96"/>
-      <c r="FF1" s="96"/>
-      <c r="FG1" s="96"/>
-      <c r="FH1" s="96"/>
-      <c r="FI1" s="96"/>
-      <c r="FJ1" s="96"/>
-      <c r="FK1" s="96"/>
-      <c r="FL1" s="96"/>
-      <c r="FM1" s="96"/>
-      <c r="FN1" s="96"/>
-      <c r="FO1" s="96"/>
-      <c r="FP1" s="96"/>
-      <c r="FQ1" s="96"/>
-      <c r="FR1" s="96"/>
-      <c r="FS1" s="96"/>
-      <c r="FT1" s="96"/>
-      <c r="FU1" s="96"/>
-      <c r="FV1" s="96"/>
-      <c r="FW1" s="96"/>
-      <c r="FX1" s="96"/>
-      <c r="FY1" s="96"/>
-      <c r="FZ1" s="96"/>
-      <c r="GA1" s="96"/>
-      <c r="GB1" s="96"/>
-      <c r="GC1" s="96"/>
-      <c r="GD1" s="96"/>
-      <c r="GE1" s="96"/>
-      <c r="GF1" s="96"/>
-      <c r="GG1" s="96"/>
-      <c r="GH1" s="96"/>
-      <c r="GI1" s="96"/>
-      <c r="GJ1" s="96"/>
-      <c r="GK1" s="96"/>
-      <c r="GL1" s="96"/>
-      <c r="GM1" s="96"/>
-      <c r="GN1" s="96"/>
-      <c r="GO1" s="96"/>
-      <c r="GP1" s="96"/>
-      <c r="GQ1" s="96"/>
-      <c r="GR1" s="96"/>
-      <c r="GS1" s="96"/>
-      <c r="GT1" s="96"/>
-      <c r="GU1" s="96"/>
-      <c r="GV1" s="96"/>
-      <c r="GW1" s="96"/>
-      <c r="GX1" s="96"/>
-      <c r="GY1" s="96"/>
-      <c r="GZ1" s="96"/>
-      <c r="HA1" s="96"/>
-      <c r="HB1" s="96"/>
-      <c r="HC1" s="96"/>
-      <c r="HD1" s="96"/>
-      <c r="HE1" s="96"/>
-      <c r="HF1" s="96"/>
-      <c r="HG1" s="96"/>
-      <c r="HH1" s="96"/>
-      <c r="HI1" s="96"/>
-      <c r="HJ1" s="96"/>
-      <c r="HK1" s="96"/>
-      <c r="HL1" s="96"/>
-      <c r="HM1" s="96"/>
-      <c r="HN1" s="96"/>
-      <c r="HO1" s="96"/>
-      <c r="HP1" s="96"/>
-      <c r="HQ1" s="96"/>
-      <c r="HR1" s="96"/>
-      <c r="HS1" s="96"/>
-      <c r="HT1" s="96"/>
-      <c r="HU1" s="96"/>
-      <c r="HV1" s="96"/>
-      <c r="HW1" s="96"/>
-      <c r="HX1" s="96"/>
-      <c r="HY1" s="96"/>
-      <c r="HZ1" s="96"/>
-      <c r="IA1" s="96"/>
-      <c r="IB1" s="96"/>
-      <c r="IC1" s="96"/>
-      <c r="ID1" s="96"/>
-      <c r="IE1" s="96"/>
-      <c r="IF1" s="96"/>
-      <c r="IG1" s="96"/>
-      <c r="IH1" s="96"/>
-      <c r="II1" s="96"/>
-      <c r="IJ1" s="96"/>
-      <c r="IK1" s="96"/>
-      <c r="IL1" s="96"/>
-      <c r="IM1" s="96"/>
-      <c r="IN1" s="96"/>
-      <c r="IO1" s="96"/>
-      <c r="IP1" s="96"/>
-      <c r="IQ1" s="96"/>
-      <c r="IR1" s="96"/>
-      <c r="IS1" s="96"/>
-      <c r="IT1" s="96"/>
-      <c r="IU1" s="96"/>
-      <c r="IV1" s="96"/>
-      <c r="IW1" s="96"/>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="81"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
+      <c r="Y1" s="82"/>
+      <c r="Z1" s="82"/>
+      <c r="AA1" s="82"/>
+      <c r="AB1" s="82"/>
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="82"/>
+      <c r="AE1" s="82"/>
+      <c r="AF1" s="82"/>
+      <c r="AG1" s="82"/>
+      <c r="AH1" s="82"/>
+      <c r="AI1" s="82"/>
+      <c r="AJ1" s="82"/>
+      <c r="AK1" s="82"/>
+      <c r="AL1" s="82"/>
+      <c r="AM1" s="82"/>
+      <c r="AN1" s="82"/>
+      <c r="AO1" s="82"/>
+      <c r="AP1" s="82"/>
+      <c r="AQ1" s="82"/>
+      <c r="AR1" s="82"/>
+      <c r="AS1" s="82"/>
+      <c r="AT1" s="82"/>
+      <c r="AU1" s="82"/>
+      <c r="AV1" s="82"/>
+      <c r="AW1" s="82"/>
+      <c r="AX1" s="82"/>
+      <c r="AY1" s="82"/>
+      <c r="AZ1" s="82"/>
+      <c r="BA1" s="82"/>
+      <c r="BB1" s="82"/>
+      <c r="BC1" s="82"/>
+      <c r="BD1" s="82"/>
+      <c r="BE1" s="82"/>
+      <c r="BF1" s="82"/>
+      <c r="BG1" s="82"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="82"/>
+      <c r="BJ1" s="82"/>
+      <c r="BK1" s="82"/>
+      <c r="BL1" s="82"/>
+      <c r="BM1" s="82"/>
+      <c r="BN1" s="82"/>
+      <c r="BO1" s="82"/>
+      <c r="BP1" s="82"/>
+      <c r="BQ1" s="82"/>
+      <c r="BR1" s="82"/>
+      <c r="BS1" s="82"/>
+      <c r="BT1" s="82"/>
+      <c r="BU1" s="82"/>
+      <c r="BV1" s="82"/>
+      <c r="BW1" s="82"/>
+      <c r="BX1" s="82"/>
+      <c r="BY1" s="82"/>
+      <c r="BZ1" s="82"/>
+      <c r="CA1" s="82"/>
+      <c r="CB1" s="82"/>
+      <c r="CC1" s="82"/>
+      <c r="CD1" s="82"/>
+      <c r="CE1" s="82"/>
+      <c r="CF1" s="82"/>
+      <c r="CG1" s="82"/>
+      <c r="CH1" s="82"/>
+      <c r="CI1" s="82"/>
+      <c r="CJ1" s="82"/>
+      <c r="CK1" s="82"/>
+      <c r="CL1" s="82"/>
+      <c r="CM1" s="82"/>
+      <c r="CN1" s="82"/>
+      <c r="CO1" s="82"/>
+      <c r="CP1" s="82"/>
+      <c r="CQ1" s="82"/>
+      <c r="CR1" s="82"/>
+      <c r="CS1" s="82"/>
+      <c r="CT1" s="82"/>
+      <c r="CU1" s="82"/>
+      <c r="CV1" s="82"/>
+      <c r="CW1" s="82"/>
+      <c r="CX1" s="82"/>
+      <c r="CY1" s="82"/>
+      <c r="CZ1" s="82"/>
+      <c r="DA1" s="82"/>
+      <c r="DB1" s="82"/>
+      <c r="DC1" s="82"/>
+      <c r="DD1" s="82"/>
+      <c r="DE1" s="82"/>
+      <c r="DF1" s="82"/>
+      <c r="DG1" s="82"/>
+      <c r="DH1" s="82"/>
+      <c r="DI1" s="82"/>
+      <c r="DJ1" s="82"/>
+      <c r="DK1" s="82"/>
+      <c r="DL1" s="82"/>
+      <c r="DM1" s="82"/>
+      <c r="DN1" s="82"/>
+      <c r="DO1" s="82"/>
+      <c r="DP1" s="82"/>
+      <c r="DQ1" s="82"/>
+      <c r="DR1" s="82"/>
+      <c r="DS1" s="82"/>
+      <c r="DT1" s="82"/>
+      <c r="DU1" s="82"/>
+      <c r="DV1" s="82"/>
+      <c r="DW1" s="82"/>
+      <c r="DX1" s="82"/>
+      <c r="DY1" s="82"/>
+      <c r="DZ1" s="82"/>
+      <c r="EA1" s="82"/>
+      <c r="EB1" s="82"/>
+      <c r="EC1" s="82"/>
+      <c r="ED1" s="82"/>
+      <c r="EE1" s="82"/>
+      <c r="EF1" s="82"/>
+      <c r="EG1" s="82"/>
+      <c r="EH1" s="82"/>
+      <c r="EI1" s="82"/>
+      <c r="EJ1" s="82"/>
+      <c r="EK1" s="82"/>
+      <c r="EL1" s="82"/>
+      <c r="EM1" s="82"/>
+      <c r="EN1" s="82"/>
+      <c r="EO1" s="82"/>
+      <c r="EP1" s="82"/>
+      <c r="EQ1" s="82"/>
+      <c r="ER1" s="82"/>
+      <c r="ES1" s="82"/>
+      <c r="ET1" s="82"/>
+      <c r="EU1" s="82"/>
+      <c r="EV1" s="82"/>
+      <c r="EW1" s="82"/>
+      <c r="EX1" s="82"/>
+      <c r="EY1" s="82"/>
+      <c r="EZ1" s="82"/>
+      <c r="FA1" s="82"/>
+      <c r="FB1" s="82"/>
+      <c r="FC1" s="82"/>
+      <c r="FD1" s="82"/>
+      <c r="FE1" s="82"/>
+      <c r="FF1" s="82"/>
+      <c r="FG1" s="82"/>
+      <c r="FH1" s="82"/>
+      <c r="FI1" s="82"/>
+      <c r="FJ1" s="82"/>
+      <c r="FK1" s="82"/>
+      <c r="FL1" s="82"/>
+      <c r="FM1" s="82"/>
+      <c r="FN1" s="82"/>
+      <c r="FO1" s="82"/>
+      <c r="FP1" s="82"/>
+      <c r="FQ1" s="82"/>
+      <c r="FR1" s="82"/>
+      <c r="FS1" s="82"/>
+      <c r="FT1" s="82"/>
+      <c r="FU1" s="82"/>
+      <c r="FV1" s="82"/>
+      <c r="FW1" s="82"/>
+      <c r="FX1" s="82"/>
+      <c r="FY1" s="82"/>
+      <c r="FZ1" s="82"/>
+      <c r="GA1" s="82"/>
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="82"/>
+      <c r="HF1" s="82"/>
+      <c r="HG1" s="82"/>
+      <c r="HH1" s="82"/>
+      <c r="HI1" s="82"/>
+      <c r="HJ1" s="82"/>
+      <c r="HK1" s="82"/>
+      <c r="HL1" s="82"/>
+      <c r="HM1" s="82"/>
+      <c r="HN1" s="82"/>
+      <c r="HO1" s="82"/>
+      <c r="HP1" s="82"/>
+      <c r="HQ1" s="82"/>
+      <c r="HR1" s="82"/>
+      <c r="HS1" s="82"/>
+      <c r="HT1" s="82"/>
+      <c r="HU1" s="82"/>
+      <c r="HV1" s="82"/>
+      <c r="HW1" s="82"/>
+      <c r="HX1" s="82"/>
+      <c r="HY1" s="82"/>
+      <c r="HZ1" s="82"/>
+      <c r="IA1" s="82"/>
+      <c r="IB1" s="82"/>
+      <c r="IC1" s="82"/>
+      <c r="ID1" s="82"/>
+      <c r="IE1" s="82"/>
+      <c r="IF1" s="82"/>
+      <c r="IG1" s="82"/>
+      <c r="IH1" s="82"/>
+      <c r="II1" s="82"/>
+      <c r="IJ1" s="82"/>
+      <c r="IK1" s="82"/>
+      <c r="IL1" s="82"/>
+      <c r="IM1" s="82"/>
+      <c r="IN1" s="82"/>
+      <c r="IO1" s="82"/>
+      <c r="IP1" s="82"/>
+      <c r="IQ1" s="82"/>
+      <c r="IR1" s="82"/>
+      <c r="IS1" s="82"/>
+      <c r="IT1" s="82"/>
+      <c r="IU1" s="82"/>
+      <c r="IV1" s="82"/>
+      <c r="IW1" s="82"/>
     </row>
     <row r="2" spans="1:257" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="153" t="s">
+      <c r="A2" s="154" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="97" t="s">
+      <c r="B2" s="154"/>
+      <c r="C2" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="98" t="s">
+      <c r="D2" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="98" t="s">
+      <c r="E2" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="98" t="s">
+      <c r="F2" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="98" t="s">
+      <c r="G2" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="97" t="s">
+      <c r="H2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="99" t="s">
+      <c r="I2" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="100"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="103"/>
-      <c r="S2" s="103"/>
-      <c r="T2" s="103"/>
-      <c r="U2" s="103"/>
-      <c r="V2" s="103"/>
-      <c r="W2" s="103"/>
-      <c r="X2" s="103"/>
-      <c r="Y2" s="103"/>
-      <c r="Z2" s="103"/>
-      <c r="AA2" s="103"/>
-      <c r="AB2" s="103"/>
-      <c r="AC2" s="103"/>
-      <c r="AD2" s="103"/>
-      <c r="AE2" s="103"/>
-      <c r="AF2" s="103"/>
-      <c r="AG2" s="103"/>
-      <c r="AH2" s="103"/>
-      <c r="AI2" s="103"/>
-      <c r="AJ2" s="103"/>
-      <c r="AK2" s="103"/>
-      <c r="AL2" s="103"/>
-      <c r="AM2" s="103"/>
-      <c r="AN2" s="103"/>
-      <c r="AO2" s="103"/>
-      <c r="AP2" s="103"/>
-      <c r="AQ2" s="103"/>
-      <c r="AR2" s="103"/>
-      <c r="AS2" s="103"/>
-      <c r="AT2" s="103"/>
-      <c r="AU2" s="103"/>
-      <c r="AV2" s="103"/>
-      <c r="AW2" s="103"/>
-      <c r="AX2" s="103"/>
-      <c r="AY2" s="103"/>
-      <c r="AZ2" s="103"/>
-      <c r="BA2" s="103"/>
-      <c r="BB2" s="103"/>
-      <c r="BC2" s="103"/>
-      <c r="BD2" s="103"/>
-      <c r="BE2" s="103"/>
-      <c r="BF2" s="103"/>
-      <c r="BG2" s="103"/>
-      <c r="BH2" s="103"/>
-      <c r="BI2" s="103"/>
-      <c r="BJ2" s="103"/>
-      <c r="BK2" s="103"/>
-      <c r="BL2" s="103"/>
-      <c r="BM2" s="103"/>
-      <c r="BN2" s="103"/>
-      <c r="BO2" s="103"/>
-      <c r="BP2" s="103"/>
-      <c r="BQ2" s="103"/>
-      <c r="BR2" s="103"/>
-      <c r="BS2" s="103"/>
-      <c r="BT2" s="103"/>
-      <c r="BU2" s="103"/>
-      <c r="BV2" s="103"/>
-      <c r="BW2" s="103"/>
-      <c r="BX2" s="103"/>
-      <c r="BY2" s="103"/>
-      <c r="BZ2" s="103"/>
-      <c r="CA2" s="103"/>
-      <c r="CB2" s="103"/>
-      <c r="CC2" s="103"/>
-      <c r="CD2" s="103"/>
-      <c r="CE2" s="103"/>
-      <c r="CF2" s="103"/>
-      <c r="CG2" s="103"/>
-      <c r="CH2" s="103"/>
-      <c r="CI2" s="103"/>
-      <c r="CJ2" s="103"/>
-      <c r="CK2" s="103"/>
-      <c r="CL2" s="103"/>
-      <c r="CM2" s="103"/>
-      <c r="CN2" s="103"/>
-      <c r="CO2" s="103"/>
-      <c r="CP2" s="103"/>
-      <c r="CQ2" s="103"/>
-      <c r="CR2" s="103"/>
-      <c r="CS2" s="103"/>
-      <c r="CT2" s="103"/>
-      <c r="CU2" s="103"/>
-      <c r="CV2" s="103"/>
-      <c r="CW2" s="103"/>
-      <c r="CX2" s="103"/>
-      <c r="CY2" s="103"/>
-      <c r="CZ2" s="103"/>
-      <c r="DA2" s="103"/>
-      <c r="DB2" s="103"/>
-      <c r="DC2" s="103"/>
-      <c r="DD2" s="103"/>
-      <c r="DE2" s="103"/>
-      <c r="DF2" s="103"/>
-      <c r="DG2" s="103"/>
-      <c r="DH2" s="103"/>
-      <c r="DI2" s="103"/>
-      <c r="DJ2" s="103"/>
-      <c r="DK2" s="103"/>
-      <c r="DL2" s="103"/>
-      <c r="DM2" s="103"/>
-      <c r="DN2" s="103"/>
-      <c r="DO2" s="103"/>
-      <c r="DP2" s="103"/>
-      <c r="DQ2" s="103"/>
-      <c r="DR2" s="103"/>
-      <c r="DS2" s="103"/>
-      <c r="DT2" s="103"/>
-      <c r="DU2" s="103"/>
-      <c r="DV2" s="103"/>
-      <c r="DW2" s="103"/>
-      <c r="DX2" s="103"/>
-      <c r="DY2" s="103"/>
-      <c r="DZ2" s="103"/>
-      <c r="EA2" s="103"/>
-      <c r="EB2" s="103"/>
-      <c r="EC2" s="103"/>
-      <c r="ED2" s="103"/>
-      <c r="EE2" s="103"/>
-      <c r="EF2" s="103"/>
-      <c r="EG2" s="103"/>
-      <c r="EH2" s="103"/>
-      <c r="EI2" s="103"/>
-      <c r="EJ2" s="103"/>
-      <c r="EK2" s="103"/>
-      <c r="EL2" s="103"/>
-      <c r="EM2" s="103"/>
-      <c r="EN2" s="103"/>
-      <c r="EO2" s="103"/>
-      <c r="EP2" s="103"/>
-      <c r="EQ2" s="103"/>
-      <c r="ER2" s="103"/>
-      <c r="ES2" s="103"/>
-      <c r="ET2" s="103"/>
-      <c r="EU2" s="103"/>
-      <c r="EV2" s="103"/>
-      <c r="EW2" s="103"/>
-      <c r="EX2" s="103"/>
-      <c r="EY2" s="103"/>
-      <c r="EZ2" s="103"/>
-      <c r="FA2" s="103"/>
-      <c r="FB2" s="103"/>
-      <c r="FC2" s="103"/>
-      <c r="FD2" s="103"/>
-      <c r="FE2" s="103"/>
-      <c r="FF2" s="103"/>
-      <c r="FG2" s="103"/>
-      <c r="FH2" s="103"/>
-      <c r="FI2" s="103"/>
-      <c r="FJ2" s="103"/>
-      <c r="FK2" s="103"/>
-      <c r="FL2" s="103"/>
-      <c r="FM2" s="103"/>
-      <c r="FN2" s="103"/>
-      <c r="FO2" s="103"/>
-      <c r="FP2" s="103"/>
-      <c r="FQ2" s="103"/>
-      <c r="FR2" s="103"/>
-      <c r="FS2" s="103"/>
-      <c r="FT2" s="103"/>
-      <c r="FU2" s="103"/>
-      <c r="FV2" s="103"/>
-      <c r="FW2" s="103"/>
-      <c r="FX2" s="103"/>
-      <c r="FY2" s="103"/>
-      <c r="FZ2" s="103"/>
-      <c r="GA2" s="103"/>
-      <c r="GB2" s="103"/>
-      <c r="GC2" s="103"/>
-      <c r="GD2" s="103"/>
-      <c r="GE2" s="103"/>
-      <c r="GF2" s="103"/>
-      <c r="GG2" s="103"/>
-      <c r="GH2" s="103"/>
-      <c r="GI2" s="103"/>
-      <c r="GJ2" s="103"/>
-      <c r="GK2" s="103"/>
-      <c r="GL2" s="103"/>
-      <c r="GM2" s="103"/>
-      <c r="GN2" s="103"/>
-      <c r="GO2" s="103"/>
-      <c r="GP2" s="103"/>
-      <c r="GQ2" s="103"/>
-      <c r="GR2" s="103"/>
-      <c r="GS2" s="103"/>
-      <c r="GT2" s="103"/>
-      <c r="GU2" s="103"/>
-      <c r="GV2" s="103"/>
-      <c r="GW2" s="103"/>
-      <c r="GX2" s="103"/>
-      <c r="GY2" s="103"/>
-      <c r="GZ2" s="103"/>
-      <c r="HA2" s="103"/>
-      <c r="HB2" s="103"/>
-      <c r="HC2" s="103"/>
-      <c r="HD2" s="103"/>
-      <c r="HE2" s="103"/>
-      <c r="HF2" s="103"/>
-      <c r="HG2" s="103"/>
-      <c r="HH2" s="103"/>
-      <c r="HI2" s="103"/>
-      <c r="HJ2" s="103"/>
-      <c r="HK2" s="103"/>
-      <c r="HL2" s="103"/>
-      <c r="HM2" s="103"/>
-      <c r="HN2" s="103"/>
-      <c r="HO2" s="103"/>
-      <c r="HP2" s="103"/>
-      <c r="HQ2" s="103"/>
-      <c r="HR2" s="103"/>
-      <c r="HS2" s="103"/>
-      <c r="HT2" s="103"/>
-      <c r="HU2" s="103"/>
-      <c r="HV2" s="103"/>
-      <c r="HW2" s="103"/>
-      <c r="HX2" s="103"/>
-      <c r="HY2" s="103"/>
-      <c r="HZ2" s="103"/>
-      <c r="IA2" s="103"/>
-      <c r="IB2" s="103"/>
-      <c r="IC2" s="103"/>
-      <c r="ID2" s="103"/>
-      <c r="IE2" s="103"/>
-      <c r="IF2" s="103"/>
-      <c r="IG2" s="103"/>
-      <c r="IH2" s="103"/>
-      <c r="II2" s="103"/>
-      <c r="IJ2" s="103"/>
-      <c r="IK2" s="103"/>
-      <c r="IL2" s="103"/>
-      <c r="IM2" s="103"/>
-      <c r="IN2" s="103"/>
-      <c r="IO2" s="103"/>
-      <c r="IP2" s="103"/>
-      <c r="IQ2" s="103"/>
-      <c r="IR2" s="103"/>
-      <c r="IS2" s="103"/>
-      <c r="IT2" s="103"/>
-      <c r="IU2" s="103"/>
-      <c r="IV2" s="103"/>
-      <c r="IW2" s="103"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
+      <c r="W2" s="89"/>
+      <c r="X2" s="89"/>
+      <c r="Y2" s="89"/>
+      <c r="Z2" s="89"/>
+      <c r="AA2" s="89"/>
+      <c r="AB2" s="89"/>
+      <c r="AC2" s="89"/>
+      <c r="AD2" s="89"/>
+      <c r="AE2" s="89"/>
+      <c r="AF2" s="89"/>
+      <c r="AG2" s="89"/>
+      <c r="AH2" s="89"/>
+      <c r="AI2" s="89"/>
+      <c r="AJ2" s="89"/>
+      <c r="AK2" s="89"/>
+      <c r="AL2" s="89"/>
+      <c r="AM2" s="89"/>
+      <c r="AN2" s="89"/>
+      <c r="AO2" s="89"/>
+      <c r="AP2" s="89"/>
+      <c r="AQ2" s="89"/>
+      <c r="AR2" s="89"/>
+      <c r="AS2" s="89"/>
+      <c r="AT2" s="89"/>
+      <c r="AU2" s="89"/>
+      <c r="AV2" s="89"/>
+      <c r="AW2" s="89"/>
+      <c r="AX2" s="89"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
+      <c r="BB2" s="89"/>
+      <c r="BC2" s="89"/>
+      <c r="BD2" s="89"/>
+      <c r="BE2" s="89"/>
+      <c r="BF2" s="89"/>
+      <c r="BG2" s="89"/>
+      <c r="BH2" s="89"/>
+      <c r="BI2" s="89"/>
+      <c r="BJ2" s="89"/>
+      <c r="BK2" s="89"/>
+      <c r="BL2" s="89"/>
+      <c r="BM2" s="89"/>
+      <c r="BN2" s="89"/>
+      <c r="BO2" s="89"/>
+      <c r="BP2" s="89"/>
+      <c r="BQ2" s="89"/>
+      <c r="BR2" s="89"/>
+      <c r="BS2" s="89"/>
+      <c r="BT2" s="89"/>
+      <c r="BU2" s="89"/>
+      <c r="BV2" s="89"/>
+      <c r="BW2" s="89"/>
+      <c r="BX2" s="89"/>
+      <c r="BY2" s="89"/>
+      <c r="BZ2" s="89"/>
+      <c r="CA2" s="89"/>
+      <c r="CB2" s="89"/>
+      <c r="CC2" s="89"/>
+      <c r="CD2" s="89"/>
+      <c r="CE2" s="89"/>
+      <c r="CF2" s="89"/>
+      <c r="CG2" s="89"/>
+      <c r="CH2" s="89"/>
+      <c r="CI2" s="89"/>
+      <c r="CJ2" s="89"/>
+      <c r="CK2" s="89"/>
+      <c r="CL2" s="89"/>
+      <c r="CM2" s="89"/>
+      <c r="CN2" s="89"/>
+      <c r="CO2" s="89"/>
+      <c r="CP2" s="89"/>
+      <c r="CQ2" s="89"/>
+      <c r="CR2" s="89"/>
+      <c r="CS2" s="89"/>
+      <c r="CT2" s="89"/>
+      <c r="CU2" s="89"/>
+      <c r="CV2" s="89"/>
+      <c r="CW2" s="89"/>
+      <c r="CX2" s="89"/>
+      <c r="CY2" s="89"/>
+      <c r="CZ2" s="89"/>
+      <c r="DA2" s="89"/>
+      <c r="DB2" s="89"/>
+      <c r="DC2" s="89"/>
+      <c r="DD2" s="89"/>
+      <c r="DE2" s="89"/>
+      <c r="DF2" s="89"/>
+      <c r="DG2" s="89"/>
+      <c r="DH2" s="89"/>
+      <c r="DI2" s="89"/>
+      <c r="DJ2" s="89"/>
+      <c r="DK2" s="89"/>
+      <c r="DL2" s="89"/>
+      <c r="DM2" s="89"/>
+      <c r="DN2" s="89"/>
+      <c r="DO2" s="89"/>
+      <c r="DP2" s="89"/>
+      <c r="DQ2" s="89"/>
+      <c r="DR2" s="89"/>
+      <c r="DS2" s="89"/>
+      <c r="DT2" s="89"/>
+      <c r="DU2" s="89"/>
+      <c r="DV2" s="89"/>
+      <c r="DW2" s="89"/>
+      <c r="DX2" s="89"/>
+      <c r="DY2" s="89"/>
+      <c r="DZ2" s="89"/>
+      <c r="EA2" s="89"/>
+      <c r="EB2" s="89"/>
+      <c r="EC2" s="89"/>
+      <c r="ED2" s="89"/>
+      <c r="EE2" s="89"/>
+      <c r="EF2" s="89"/>
+      <c r="EG2" s="89"/>
+      <c r="EH2" s="89"/>
+      <c r="EI2" s="89"/>
+      <c r="EJ2" s="89"/>
+      <c r="EK2" s="89"/>
+      <c r="EL2" s="89"/>
+      <c r="EM2" s="89"/>
+      <c r="EN2" s="89"/>
+      <c r="EO2" s="89"/>
+      <c r="EP2" s="89"/>
+      <c r="EQ2" s="89"/>
+      <c r="ER2" s="89"/>
+      <c r="ES2" s="89"/>
+      <c r="ET2" s="89"/>
+      <c r="EU2" s="89"/>
+      <c r="EV2" s="89"/>
+      <c r="EW2" s="89"/>
+      <c r="EX2" s="89"/>
+      <c r="EY2" s="89"/>
+      <c r="EZ2" s="89"/>
+      <c r="FA2" s="89"/>
+      <c r="FB2" s="89"/>
+      <c r="FC2" s="89"/>
+      <c r="FD2" s="89"/>
+      <c r="FE2" s="89"/>
+      <c r="FF2" s="89"/>
+      <c r="FG2" s="89"/>
+      <c r="FH2" s="89"/>
+      <c r="FI2" s="89"/>
+      <c r="FJ2" s="89"/>
+      <c r="FK2" s="89"/>
+      <c r="FL2" s="89"/>
+      <c r="FM2" s="89"/>
+      <c r="FN2" s="89"/>
+      <c r="FO2" s="89"/>
+      <c r="FP2" s="89"/>
+      <c r="FQ2" s="89"/>
+      <c r="FR2" s="89"/>
+      <c r="FS2" s="89"/>
+      <c r="FT2" s="89"/>
+      <c r="FU2" s="89"/>
+      <c r="FV2" s="89"/>
+      <c r="FW2" s="89"/>
+      <c r="FX2" s="89"/>
+      <c r="FY2" s="89"/>
+      <c r="FZ2" s="89"/>
+      <c r="GA2" s="89"/>
+      <c r="GB2" s="89"/>
+      <c r="GC2" s="89"/>
+      <c r="GD2" s="89"/>
+      <c r="GE2" s="89"/>
+      <c r="GF2" s="89"/>
+      <c r="GG2" s="89"/>
+      <c r="GH2" s="89"/>
+      <c r="GI2" s="89"/>
+      <c r="GJ2" s="89"/>
+      <c r="GK2" s="89"/>
+      <c r="GL2" s="89"/>
+      <c r="GM2" s="89"/>
+      <c r="GN2" s="89"/>
+      <c r="GO2" s="89"/>
+      <c r="GP2" s="89"/>
+      <c r="GQ2" s="89"/>
+      <c r="GR2" s="89"/>
+      <c r="GS2" s="89"/>
+      <c r="GT2" s="89"/>
+      <c r="GU2" s="89"/>
+      <c r="GV2" s="89"/>
+      <c r="GW2" s="89"/>
+      <c r="GX2" s="89"/>
+      <c r="GY2" s="89"/>
+      <c r="GZ2" s="89"/>
+      <c r="HA2" s="89"/>
+      <c r="HB2" s="89"/>
+      <c r="HC2" s="89"/>
+      <c r="HD2" s="89"/>
+      <c r="HE2" s="89"/>
+      <c r="HF2" s="89"/>
+      <c r="HG2" s="89"/>
+      <c r="HH2" s="89"/>
+      <c r="HI2" s="89"/>
+      <c r="HJ2" s="89"/>
+      <c r="HK2" s="89"/>
+      <c r="HL2" s="89"/>
+      <c r="HM2" s="89"/>
+      <c r="HN2" s="89"/>
+      <c r="HO2" s="89"/>
+      <c r="HP2" s="89"/>
+      <c r="HQ2" s="89"/>
+      <c r="HR2" s="89"/>
+      <c r="HS2" s="89"/>
+      <c r="HT2" s="89"/>
+      <c r="HU2" s="89"/>
+      <c r="HV2" s="89"/>
+      <c r="HW2" s="89"/>
+      <c r="HX2" s="89"/>
+      <c r="HY2" s="89"/>
+      <c r="HZ2" s="89"/>
+      <c r="IA2" s="89"/>
+      <c r="IB2" s="89"/>
+      <c r="IC2" s="89"/>
+      <c r="ID2" s="89"/>
+      <c r="IE2" s="89"/>
+      <c r="IF2" s="89"/>
+      <c r="IG2" s="89"/>
+      <c r="IH2" s="89"/>
+      <c r="II2" s="89"/>
+      <c r="IJ2" s="89"/>
+      <c r="IK2" s="89"/>
+      <c r="IL2" s="89"/>
+      <c r="IM2" s="89"/>
+      <c r="IN2" s="89"/>
+      <c r="IO2" s="89"/>
+      <c r="IP2" s="89"/>
+      <c r="IQ2" s="89"/>
+      <c r="IR2" s="89"/>
+      <c r="IS2" s="89"/>
+      <c r="IT2" s="89"/>
+      <c r="IU2" s="89"/>
+      <c r="IV2" s="89"/>
+      <c r="IW2" s="89"/>
     </row>
     <row r="3" spans="1:257" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="105" t="s">
+      <c r="A3" s="90"/>
+      <c r="B3" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="112"/>
-      <c r="P3" s="112"/>
-      <c r="Q3" s="112"/>
-      <c r="R3" s="112"/>
-      <c r="S3" s="112"/>
-      <c r="T3" s="112"/>
-      <c r="U3" s="112"/>
-      <c r="V3" s="112"/>
-      <c r="W3" s="112"/>
-      <c r="X3" s="112"/>
-      <c r="Y3" s="112"/>
-      <c r="Z3" s="112"/>
-      <c r="AA3" s="112"/>
-      <c r="AB3" s="112"/>
-      <c r="AC3" s="112"/>
-      <c r="AD3" s="112"/>
-      <c r="AE3" s="112"/>
-      <c r="AF3" s="112"/>
-      <c r="AG3" s="112"/>
-      <c r="AH3" s="112"/>
-      <c r="AI3" s="112"/>
-      <c r="AJ3" s="112"/>
-      <c r="AK3" s="112"/>
-      <c r="AL3" s="112"/>
-      <c r="AM3" s="112"/>
-      <c r="AN3" s="112"/>
-      <c r="AO3" s="112"/>
-      <c r="AP3" s="112"/>
-      <c r="AQ3" s="112"/>
-      <c r="AR3" s="112"/>
-      <c r="AS3" s="112"/>
-      <c r="AT3" s="112"/>
-      <c r="AU3" s="112"/>
-      <c r="AV3" s="112"/>
-      <c r="AW3" s="112"/>
-      <c r="AX3" s="112"/>
-      <c r="AY3" s="112"/>
-      <c r="AZ3" s="112"/>
-      <c r="BA3" s="112"/>
-      <c r="BB3" s="112"/>
-      <c r="BC3" s="112"/>
-      <c r="BD3" s="112"/>
-      <c r="BE3" s="112"/>
-      <c r="BF3" s="112"/>
-      <c r="BG3" s="112"/>
-      <c r="BH3" s="112"/>
-      <c r="BI3" s="112"/>
-      <c r="BJ3" s="112"/>
-      <c r="BK3" s="112"/>
-      <c r="BL3" s="112"/>
-      <c r="BM3" s="112"/>
-      <c r="BN3" s="112"/>
-      <c r="BO3" s="112"/>
-      <c r="BP3" s="112"/>
-      <c r="BQ3" s="112"/>
-      <c r="BR3" s="112"/>
-      <c r="BS3" s="112"/>
-      <c r="BT3" s="112"/>
-      <c r="BU3" s="112"/>
-      <c r="BV3" s="112"/>
-      <c r="BW3" s="112"/>
-      <c r="BX3" s="112"/>
-      <c r="BY3" s="112"/>
-      <c r="BZ3" s="112"/>
-      <c r="CA3" s="112"/>
-      <c r="CB3" s="112"/>
-      <c r="CC3" s="112"/>
-      <c r="CD3" s="112"/>
-      <c r="CE3" s="112"/>
-      <c r="CF3" s="112"/>
-      <c r="CG3" s="112"/>
-      <c r="CH3" s="112"/>
-      <c r="CI3" s="112"/>
-      <c r="CJ3" s="112"/>
-      <c r="CK3" s="112"/>
-      <c r="CL3" s="112"/>
-      <c r="CM3" s="112"/>
-      <c r="CN3" s="112"/>
-      <c r="CO3" s="112"/>
-      <c r="CP3" s="112"/>
-      <c r="CQ3" s="112"/>
-      <c r="CR3" s="112"/>
-      <c r="CS3" s="112"/>
-      <c r="CT3" s="112"/>
-      <c r="CU3" s="112"/>
-      <c r="CV3" s="112"/>
-      <c r="CW3" s="112"/>
-      <c r="CX3" s="112"/>
-      <c r="CY3" s="112"/>
-      <c r="CZ3" s="112"/>
-      <c r="DA3" s="112"/>
-      <c r="DB3" s="112"/>
-      <c r="DC3" s="112"/>
-      <c r="DD3" s="112"/>
-      <c r="DE3" s="112"/>
-      <c r="DF3" s="112"/>
-      <c r="DG3" s="112"/>
-      <c r="DH3" s="112"/>
-      <c r="DI3" s="112"/>
-      <c r="DJ3" s="112"/>
-      <c r="DK3" s="112"/>
-      <c r="DL3" s="112"/>
-      <c r="DM3" s="112"/>
-      <c r="DN3" s="112"/>
-      <c r="DO3" s="112"/>
-      <c r="DP3" s="112"/>
-      <c r="DQ3" s="112"/>
-      <c r="DR3" s="112"/>
-      <c r="DS3" s="112"/>
-      <c r="DT3" s="112"/>
-      <c r="DU3" s="112"/>
-      <c r="DV3" s="112"/>
-      <c r="DW3" s="112"/>
-      <c r="DX3" s="112"/>
-      <c r="DY3" s="112"/>
-      <c r="DZ3" s="112"/>
-      <c r="EA3" s="112"/>
-      <c r="EB3" s="112"/>
-      <c r="EC3" s="112"/>
-      <c r="ED3" s="112"/>
-      <c r="EE3" s="112"/>
-      <c r="EF3" s="112"/>
-      <c r="EG3" s="112"/>
-      <c r="EH3" s="112"/>
-      <c r="EI3" s="112"/>
-      <c r="EJ3" s="112"/>
-      <c r="EK3" s="112"/>
-      <c r="EL3" s="112"/>
-      <c r="EM3" s="112"/>
-      <c r="EN3" s="112"/>
-      <c r="EO3" s="112"/>
-      <c r="EP3" s="112"/>
-      <c r="EQ3" s="112"/>
-      <c r="ER3" s="112"/>
-      <c r="ES3" s="112"/>
-      <c r="ET3" s="112"/>
-      <c r="EU3" s="112"/>
-      <c r="EV3" s="112"/>
-      <c r="EW3" s="112"/>
-      <c r="EX3" s="112"/>
-      <c r="EY3" s="112"/>
-      <c r="EZ3" s="112"/>
-      <c r="FA3" s="112"/>
-      <c r="FB3" s="112"/>
-      <c r="FC3" s="112"/>
-      <c r="FD3" s="112"/>
-      <c r="FE3" s="112"/>
-      <c r="FF3" s="112"/>
-      <c r="FG3" s="112"/>
-      <c r="FH3" s="112"/>
-      <c r="FI3" s="112"/>
-      <c r="FJ3" s="112"/>
-      <c r="FK3" s="112"/>
-      <c r="FL3" s="112"/>
-      <c r="FM3" s="112"/>
-      <c r="FN3" s="112"/>
-      <c r="FO3" s="112"/>
-      <c r="FP3" s="112"/>
-      <c r="FQ3" s="112"/>
-      <c r="FR3" s="112"/>
-      <c r="FS3" s="112"/>
-      <c r="FT3" s="112"/>
-      <c r="FU3" s="112"/>
-      <c r="FV3" s="112"/>
-      <c r="FW3" s="112"/>
-      <c r="FX3" s="112"/>
-      <c r="FY3" s="112"/>
-      <c r="FZ3" s="112"/>
-      <c r="GA3" s="112"/>
-      <c r="GB3" s="112"/>
-      <c r="GC3" s="112"/>
-      <c r="GD3" s="112"/>
-      <c r="GE3" s="112"/>
-      <c r="GF3" s="112"/>
-      <c r="GG3" s="112"/>
-      <c r="GH3" s="112"/>
-      <c r="GI3" s="112"/>
-      <c r="GJ3" s="112"/>
-      <c r="GK3" s="112"/>
-      <c r="GL3" s="112"/>
-      <c r="GM3" s="112"/>
-      <c r="GN3" s="112"/>
-      <c r="GO3" s="112"/>
-      <c r="GP3" s="112"/>
-      <c r="GQ3" s="112"/>
-      <c r="GR3" s="112"/>
-      <c r="GS3" s="112"/>
-      <c r="GT3" s="112"/>
-      <c r="GU3" s="112"/>
-      <c r="GV3" s="112"/>
-      <c r="GW3" s="112"/>
-      <c r="GX3" s="112"/>
-      <c r="GY3" s="112"/>
-      <c r="GZ3" s="112"/>
-      <c r="HA3" s="112"/>
-      <c r="HB3" s="112"/>
-      <c r="HC3" s="112"/>
-      <c r="HD3" s="112"/>
-      <c r="HE3" s="112"/>
-      <c r="HF3" s="112"/>
-      <c r="HG3" s="112"/>
-      <c r="HH3" s="112"/>
-      <c r="HI3" s="112"/>
-      <c r="HJ3" s="112"/>
-      <c r="HK3" s="112"/>
-      <c r="HL3" s="112"/>
-      <c r="HM3" s="112"/>
-      <c r="HN3" s="112"/>
-      <c r="HO3" s="112"/>
-      <c r="HP3" s="112"/>
-      <c r="HQ3" s="112"/>
-      <c r="HR3" s="112"/>
-      <c r="HS3" s="112"/>
-      <c r="HT3" s="112"/>
-      <c r="HU3" s="112"/>
-      <c r="HV3" s="112"/>
-      <c r="HW3" s="112"/>
-      <c r="HX3" s="112"/>
-      <c r="HY3" s="112"/>
-      <c r="HZ3" s="112"/>
-      <c r="IA3" s="112"/>
-      <c r="IB3" s="112"/>
-      <c r="IC3" s="112"/>
-      <c r="ID3" s="112"/>
-      <c r="IE3" s="112"/>
-      <c r="IF3" s="112"/>
-      <c r="IG3" s="112"/>
-      <c r="IH3" s="112"/>
-      <c r="II3" s="112"/>
-      <c r="IJ3" s="112"/>
-      <c r="IK3" s="112"/>
-      <c r="IL3" s="112"/>
-      <c r="IM3" s="112"/>
-      <c r="IN3" s="112"/>
-      <c r="IO3" s="112"/>
-      <c r="IP3" s="112"/>
-      <c r="IQ3" s="112"/>
-      <c r="IR3" s="112"/>
-      <c r="IS3" s="112"/>
-      <c r="IT3" s="112"/>
-      <c r="IU3" s="112"/>
-      <c r="IV3" s="112"/>
-      <c r="IW3" s="112"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="98"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="98"/>
+      <c r="S3" s="98"/>
+      <c r="T3" s="98"/>
+      <c r="U3" s="98"/>
+      <c r="V3" s="98"/>
+      <c r="W3" s="98"/>
+      <c r="X3" s="98"/>
+      <c r="Y3" s="98"/>
+      <c r="Z3" s="98"/>
+      <c r="AA3" s="98"/>
+      <c r="AB3" s="98"/>
+      <c r="AC3" s="98"/>
+      <c r="AD3" s="98"/>
+      <c r="AE3" s="98"/>
+      <c r="AF3" s="98"/>
+      <c r="AG3" s="98"/>
+      <c r="AH3" s="98"/>
+      <c r="AI3" s="98"/>
+      <c r="AJ3" s="98"/>
+      <c r="AK3" s="98"/>
+      <c r="AL3" s="98"/>
+      <c r="AM3" s="98"/>
+      <c r="AN3" s="98"/>
+      <c r="AO3" s="98"/>
+      <c r="AP3" s="98"/>
+      <c r="AQ3" s="98"/>
+      <c r="AR3" s="98"/>
+      <c r="AS3" s="98"/>
+      <c r="AT3" s="98"/>
+      <c r="AU3" s="98"/>
+      <c r="AV3" s="98"/>
+      <c r="AW3" s="98"/>
+      <c r="AX3" s="98"/>
+      <c r="AY3" s="98"/>
+      <c r="AZ3" s="98"/>
+      <c r="BA3" s="98"/>
+      <c r="BB3" s="98"/>
+      <c r="BC3" s="98"/>
+      <c r="BD3" s="98"/>
+      <c r="BE3" s="98"/>
+      <c r="BF3" s="98"/>
+      <c r="BG3" s="98"/>
+      <c r="BH3" s="98"/>
+      <c r="BI3" s="98"/>
+      <c r="BJ3" s="98"/>
+      <c r="BK3" s="98"/>
+      <c r="BL3" s="98"/>
+      <c r="BM3" s="98"/>
+      <c r="BN3" s="98"/>
+      <c r="BO3" s="98"/>
+      <c r="BP3" s="98"/>
+      <c r="BQ3" s="98"/>
+      <c r="BR3" s="98"/>
+      <c r="BS3" s="98"/>
+      <c r="BT3" s="98"/>
+      <c r="BU3" s="98"/>
+      <c r="BV3" s="98"/>
+      <c r="BW3" s="98"/>
+      <c r="BX3" s="98"/>
+      <c r="BY3" s="98"/>
+      <c r="BZ3" s="98"/>
+      <c r="CA3" s="98"/>
+      <c r="CB3" s="98"/>
+      <c r="CC3" s="98"/>
+      <c r="CD3" s="98"/>
+      <c r="CE3" s="98"/>
+      <c r="CF3" s="98"/>
+      <c r="CG3" s="98"/>
+      <c r="CH3" s="98"/>
+      <c r="CI3" s="98"/>
+      <c r="CJ3" s="98"/>
+      <c r="CK3" s="98"/>
+      <c r="CL3" s="98"/>
+      <c r="CM3" s="98"/>
+      <c r="CN3" s="98"/>
+      <c r="CO3" s="98"/>
+      <c r="CP3" s="98"/>
+      <c r="CQ3" s="98"/>
+      <c r="CR3" s="98"/>
+      <c r="CS3" s="98"/>
+      <c r="CT3" s="98"/>
+      <c r="CU3" s="98"/>
+      <c r="CV3" s="98"/>
+      <c r="CW3" s="98"/>
+      <c r="CX3" s="98"/>
+      <c r="CY3" s="98"/>
+      <c r="CZ3" s="98"/>
+      <c r="DA3" s="98"/>
+      <c r="DB3" s="98"/>
+      <c r="DC3" s="98"/>
+      <c r="DD3" s="98"/>
+      <c r="DE3" s="98"/>
+      <c r="DF3" s="98"/>
+      <c r="DG3" s="98"/>
+      <c r="DH3" s="98"/>
+      <c r="DI3" s="98"/>
+      <c r="DJ3" s="98"/>
+      <c r="DK3" s="98"/>
+      <c r="DL3" s="98"/>
+      <c r="DM3" s="98"/>
+      <c r="DN3" s="98"/>
+      <c r="DO3" s="98"/>
+      <c r="DP3" s="98"/>
+      <c r="DQ3" s="98"/>
+      <c r="DR3" s="98"/>
+      <c r="DS3" s="98"/>
+      <c r="DT3" s="98"/>
+      <c r="DU3" s="98"/>
+      <c r="DV3" s="98"/>
+      <c r="DW3" s="98"/>
+      <c r="DX3" s="98"/>
+      <c r="DY3" s="98"/>
+      <c r="DZ3" s="98"/>
+      <c r="EA3" s="98"/>
+      <c r="EB3" s="98"/>
+      <c r="EC3" s="98"/>
+      <c r="ED3" s="98"/>
+      <c r="EE3" s="98"/>
+      <c r="EF3" s="98"/>
+      <c r="EG3" s="98"/>
+      <c r="EH3" s="98"/>
+      <c r="EI3" s="98"/>
+      <c r="EJ3" s="98"/>
+      <c r="EK3" s="98"/>
+      <c r="EL3" s="98"/>
+      <c r="EM3" s="98"/>
+      <c r="EN3" s="98"/>
+      <c r="EO3" s="98"/>
+      <c r="EP3" s="98"/>
+      <c r="EQ3" s="98"/>
+      <c r="ER3" s="98"/>
+      <c r="ES3" s="98"/>
+      <c r="ET3" s="98"/>
+      <c r="EU3" s="98"/>
+      <c r="EV3" s="98"/>
+      <c r="EW3" s="98"/>
+      <c r="EX3" s="98"/>
+      <c r="EY3" s="98"/>
+      <c r="EZ3" s="98"/>
+      <c r="FA3" s="98"/>
+      <c r="FB3" s="98"/>
+      <c r="FC3" s="98"/>
+      <c r="FD3" s="98"/>
+      <c r="FE3" s="98"/>
+      <c r="FF3" s="98"/>
+      <c r="FG3" s="98"/>
+      <c r="FH3" s="98"/>
+      <c r="FI3" s="98"/>
+      <c r="FJ3" s="98"/>
+      <c r="FK3" s="98"/>
+      <c r="FL3" s="98"/>
+      <c r="FM3" s="98"/>
+      <c r="FN3" s="98"/>
+      <c r="FO3" s="98"/>
+      <c r="FP3" s="98"/>
+      <c r="FQ3" s="98"/>
+      <c r="FR3" s="98"/>
+      <c r="FS3" s="98"/>
+      <c r="FT3" s="98"/>
+      <c r="FU3" s="98"/>
+      <c r="FV3" s="98"/>
+      <c r="FW3" s="98"/>
+      <c r="FX3" s="98"/>
+      <c r="FY3" s="98"/>
+      <c r="FZ3" s="98"/>
+      <c r="GA3" s="98"/>
+      <c r="GB3" s="98"/>
+      <c r="GC3" s="98"/>
+      <c r="GD3" s="98"/>
+      <c r="GE3" s="98"/>
+      <c r="GF3" s="98"/>
+      <c r="GG3" s="98"/>
+      <c r="GH3" s="98"/>
+      <c r="GI3" s="98"/>
+      <c r="GJ3" s="98"/>
+      <c r="GK3" s="98"/>
+      <c r="GL3" s="98"/>
+      <c r="GM3" s="98"/>
+      <c r="GN3" s="98"/>
+      <c r="GO3" s="98"/>
+      <c r="GP3" s="98"/>
+      <c r="GQ3" s="98"/>
+      <c r="GR3" s="98"/>
+      <c r="GS3" s="98"/>
+      <c r="GT3" s="98"/>
+      <c r="GU3" s="98"/>
+      <c r="GV3" s="98"/>
+      <c r="GW3" s="98"/>
+      <c r="GX3" s="98"/>
+      <c r="GY3" s="98"/>
+      <c r="GZ3" s="98"/>
+      <c r="HA3" s="98"/>
+      <c r="HB3" s="98"/>
+      <c r="HC3" s="98"/>
+      <c r="HD3" s="98"/>
+      <c r="HE3" s="98"/>
+      <c r="HF3" s="98"/>
+      <c r="HG3" s="98"/>
+      <c r="HH3" s="98"/>
+      <c r="HI3" s="98"/>
+      <c r="HJ3" s="98"/>
+      <c r="HK3" s="98"/>
+      <c r="HL3" s="98"/>
+      <c r="HM3" s="98"/>
+      <c r="HN3" s="98"/>
+      <c r="HO3" s="98"/>
+      <c r="HP3" s="98"/>
+      <c r="HQ3" s="98"/>
+      <c r="HR3" s="98"/>
+      <c r="HS3" s="98"/>
+      <c r="HT3" s="98"/>
+      <c r="HU3" s="98"/>
+      <c r="HV3" s="98"/>
+      <c r="HW3" s="98"/>
+      <c r="HX3" s="98"/>
+      <c r="HY3" s="98"/>
+      <c r="HZ3" s="98"/>
+      <c r="IA3" s="98"/>
+      <c r="IB3" s="98"/>
+      <c r="IC3" s="98"/>
+      <c r="ID3" s="98"/>
+      <c r="IE3" s="98"/>
+      <c r="IF3" s="98"/>
+      <c r="IG3" s="98"/>
+      <c r="IH3" s="98"/>
+      <c r="II3" s="98"/>
+      <c r="IJ3" s="98"/>
+      <c r="IK3" s="98"/>
+      <c r="IL3" s="98"/>
+      <c r="IM3" s="98"/>
+      <c r="IN3" s="98"/>
+      <c r="IO3" s="98"/>
+      <c r="IP3" s="98"/>
+      <c r="IQ3" s="98"/>
+      <c r="IR3" s="98"/>
+      <c r="IS3" s="98"/>
+      <c r="IT3" s="98"/>
+      <c r="IU3" s="98"/>
+      <c r="IV3" s="98"/>
+      <c r="IW3" s="98"/>
     </row>
     <row r="4" spans="1:257" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="113" t="s">
+      <c r="A4" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="115"/>
-      <c r="D4" s="116">
+      <c r="C4" s="101"/>
+      <c r="D4" s="102">
         <f>'GeoNURIS for KRAS 1.0 유지관리'!H4</f>
-        <v>7882560</v>
+        <v>8400000</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="117">
+      <c r="E4" s="102"/>
+      <c r="F4" s="103">
         <f>'GeoNURIS for KRAS 1.0 유지관리'!J4</f>
-        <v>3941280</v>
+        <v>4200000</v>
       </c>
-      <c r="G4" s="116">
+      <c r="G4" s="102">
         <f>'GeoNURIS for KRAS 1.0 유지관리'!L4</f>
-        <v>3941280</v>
+        <v>4200000</v>
       </c>
-      <c r="H4" s="116">
+      <c r="H4" s="102">
         <f>F4+G4</f>
-        <v>7882560</v>
+        <v>8400000</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="101"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
-      <c r="AB4" s="112"/>
-      <c r="AC4" s="112"/>
-      <c r="AD4" s="112"/>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="112"/>
-      <c r="AQ4" s="112"/>
-      <c r="AR4" s="112"/>
-      <c r="AS4" s="112"/>
-      <c r="AT4" s="112"/>
-      <c r="AU4" s="112"/>
-      <c r="AV4" s="112"/>
-      <c r="AW4" s="112"/>
-      <c r="AX4" s="112"/>
-      <c r="AY4" s="112"/>
-      <c r="AZ4" s="112"/>
-      <c r="BA4" s="112"/>
-      <c r="BB4" s="112"/>
-      <c r="BC4" s="112"/>
-      <c r="BD4" s="112"/>
-      <c r="BE4" s="112"/>
-      <c r="BF4" s="112"/>
-      <c r="BG4" s="112"/>
-      <c r="BH4" s="112"/>
-      <c r="BI4" s="112"/>
-      <c r="BJ4" s="112"/>
-      <c r="BK4" s="112"/>
-      <c r="BL4" s="112"/>
-      <c r="BM4" s="112"/>
-      <c r="BN4" s="112"/>
-      <c r="BO4" s="112"/>
-      <c r="BP4" s="112"/>
-      <c r="BQ4" s="112"/>
-      <c r="BR4" s="112"/>
-      <c r="BS4" s="112"/>
-      <c r="BT4" s="112"/>
-      <c r="BU4" s="112"/>
-      <c r="BV4" s="112"/>
-      <c r="BW4" s="112"/>
-      <c r="BX4" s="112"/>
-      <c r="BY4" s="112"/>
-      <c r="BZ4" s="112"/>
-      <c r="CA4" s="112"/>
-      <c r="CB4" s="112"/>
-      <c r="CC4" s="112"/>
-      <c r="CD4" s="112"/>
-      <c r="CE4" s="112"/>
-      <c r="CF4" s="112"/>
-      <c r="CG4" s="112"/>
-      <c r="CH4" s="112"/>
-      <c r="CI4" s="112"/>
-      <c r="CJ4" s="112"/>
-      <c r="CK4" s="112"/>
-      <c r="CL4" s="112"/>
-      <c r="CM4" s="112"/>
-      <c r="CN4" s="112"/>
-      <c r="CO4" s="112"/>
-      <c r="CP4" s="112"/>
-      <c r="CQ4" s="112"/>
-      <c r="CR4" s="112"/>
-      <c r="CS4" s="112"/>
-      <c r="CT4" s="112"/>
-      <c r="CU4" s="112"/>
-      <c r="CV4" s="112"/>
-      <c r="CW4" s="112"/>
-      <c r="CX4" s="112"/>
-      <c r="CY4" s="112"/>
-      <c r="CZ4" s="112"/>
-      <c r="DA4" s="112"/>
-      <c r="DB4" s="112"/>
-      <c r="DC4" s="112"/>
-      <c r="DD4" s="112"/>
-      <c r="DE4" s="112"/>
-      <c r="DF4" s="112"/>
-      <c r="DG4" s="112"/>
-      <c r="DH4" s="112"/>
-      <c r="DI4" s="112"/>
-      <c r="DJ4" s="112"/>
-      <c r="DK4" s="112"/>
-      <c r="DL4" s="112"/>
-      <c r="DM4" s="112"/>
-      <c r="DN4" s="112"/>
-      <c r="DO4" s="112"/>
-      <c r="DP4" s="112"/>
-      <c r="DQ4" s="112"/>
-      <c r="DR4" s="112"/>
-      <c r="DS4" s="112"/>
-      <c r="DT4" s="112"/>
-      <c r="DU4" s="112"/>
-      <c r="DV4" s="112"/>
-      <c r="DW4" s="112"/>
-      <c r="DX4" s="112"/>
-      <c r="DY4" s="112"/>
-      <c r="DZ4" s="112"/>
-      <c r="EA4" s="112"/>
-      <c r="EB4" s="112"/>
-      <c r="EC4" s="112"/>
-      <c r="ED4" s="112"/>
-      <c r="EE4" s="112"/>
-      <c r="EF4" s="112"/>
-      <c r="EG4" s="112"/>
-      <c r="EH4" s="112"/>
-      <c r="EI4" s="112"/>
-      <c r="EJ4" s="112"/>
-      <c r="EK4" s="112"/>
-      <c r="EL4" s="112"/>
-      <c r="EM4" s="112"/>
-      <c r="EN4" s="112"/>
-      <c r="EO4" s="112"/>
-      <c r="EP4" s="112"/>
-      <c r="EQ4" s="112"/>
-      <c r="ER4" s="112"/>
-      <c r="ES4" s="112"/>
-      <c r="ET4" s="112"/>
-      <c r="EU4" s="112"/>
-      <c r="EV4" s="112"/>
-      <c r="EW4" s="112"/>
-      <c r="EX4" s="112"/>
-      <c r="EY4" s="112"/>
-      <c r="EZ4" s="112"/>
-      <c r="FA4" s="112"/>
-      <c r="FB4" s="112"/>
-      <c r="FC4" s="112"/>
-      <c r="FD4" s="112"/>
-      <c r="FE4" s="112"/>
-      <c r="FF4" s="112"/>
-      <c r="FG4" s="112"/>
-      <c r="FH4" s="112"/>
-      <c r="FI4" s="112"/>
-      <c r="FJ4" s="112"/>
-      <c r="FK4" s="112"/>
-      <c r="FL4" s="112"/>
-      <c r="FM4" s="112"/>
-      <c r="FN4" s="112"/>
-      <c r="FO4" s="112"/>
-      <c r="FP4" s="112"/>
-      <c r="FQ4" s="112"/>
-      <c r="FR4" s="112"/>
-      <c r="FS4" s="112"/>
-      <c r="FT4" s="112"/>
-      <c r="FU4" s="112"/>
-      <c r="FV4" s="112"/>
-      <c r="FW4" s="112"/>
-      <c r="FX4" s="112"/>
-      <c r="FY4" s="112"/>
-      <c r="FZ4" s="112"/>
-      <c r="GA4" s="112"/>
-      <c r="GB4" s="112"/>
-      <c r="GC4" s="112"/>
-      <c r="GD4" s="112"/>
-      <c r="GE4" s="112"/>
-      <c r="GF4" s="112"/>
-      <c r="GG4" s="112"/>
-      <c r="GH4" s="112"/>
-      <c r="GI4" s="112"/>
-      <c r="GJ4" s="112"/>
-      <c r="GK4" s="112"/>
-      <c r="GL4" s="112"/>
-      <c r="GM4" s="112"/>
-      <c r="GN4" s="112"/>
-      <c r="GO4" s="112"/>
-      <c r="GP4" s="112"/>
-      <c r="GQ4" s="112"/>
-      <c r="GR4" s="112"/>
-      <c r="GS4" s="112"/>
-      <c r="GT4" s="112"/>
-      <c r="GU4" s="112"/>
-      <c r="GV4" s="112"/>
-      <c r="GW4" s="112"/>
-      <c r="GX4" s="112"/>
-      <c r="GY4" s="112"/>
-      <c r="GZ4" s="112"/>
-      <c r="HA4" s="112"/>
-      <c r="HB4" s="112"/>
-      <c r="HC4" s="112"/>
-      <c r="HD4" s="112"/>
-      <c r="HE4" s="112"/>
-      <c r="HF4" s="112"/>
-      <c r="HG4" s="112"/>
-      <c r="HH4" s="112"/>
-      <c r="HI4" s="112"/>
-      <c r="HJ4" s="112"/>
-      <c r="HK4" s="112"/>
-      <c r="HL4" s="112"/>
-      <c r="HM4" s="112"/>
-      <c r="HN4" s="112"/>
-      <c r="HO4" s="112"/>
-      <c r="HP4" s="112"/>
-      <c r="HQ4" s="112"/>
-      <c r="HR4" s="112"/>
-      <c r="HS4" s="112"/>
-      <c r="HT4" s="112"/>
-      <c r="HU4" s="112"/>
-      <c r="HV4" s="112"/>
-      <c r="HW4" s="112"/>
-      <c r="HX4" s="112"/>
-      <c r="HY4" s="112"/>
-      <c r="HZ4" s="112"/>
-      <c r="IA4" s="112"/>
-      <c r="IB4" s="112"/>
-      <c r="IC4" s="112"/>
-      <c r="ID4" s="112"/>
-      <c r="IE4" s="112"/>
-      <c r="IF4" s="112"/>
-      <c r="IG4" s="112"/>
-      <c r="IH4" s="112"/>
-      <c r="II4" s="112"/>
-      <c r="IJ4" s="112"/>
-      <c r="IK4" s="112"/>
-      <c r="IL4" s="112"/>
-      <c r="IM4" s="112"/>
-      <c r="IN4" s="112"/>
-      <c r="IO4" s="112"/>
-      <c r="IP4" s="112"/>
-      <c r="IQ4" s="112"/>
-      <c r="IR4" s="112"/>
-      <c r="IS4" s="112"/>
-      <c r="IT4" s="112"/>
-      <c r="IU4" s="112"/>
-      <c r="IV4" s="112"/>
-      <c r="IW4" s="112"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="87"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="98"/>
+      <c r="Q4" s="98"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="98"/>
+      <c r="W4" s="98"/>
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="98"/>
+      <c r="AB4" s="98"/>
+      <c r="AC4" s="98"/>
+      <c r="AD4" s="98"/>
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="98"/>
+      <c r="AH4" s="98"/>
+      <c r="AI4" s="98"/>
+      <c r="AJ4" s="98"/>
+      <c r="AK4" s="98"/>
+      <c r="AL4" s="98"/>
+      <c r="AM4" s="98"/>
+      <c r="AN4" s="98"/>
+      <c r="AO4" s="98"/>
+      <c r="AP4" s="98"/>
+      <c r="AQ4" s="98"/>
+      <c r="AR4" s="98"/>
+      <c r="AS4" s="98"/>
+      <c r="AT4" s="98"/>
+      <c r="AU4" s="98"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="98"/>
+      <c r="AX4" s="98"/>
+      <c r="AY4" s="98"/>
+      <c r="AZ4" s="98"/>
+      <c r="BA4" s="98"/>
+      <c r="BB4" s="98"/>
+      <c r="BC4" s="98"/>
+      <c r="BD4" s="98"/>
+      <c r="BE4" s="98"/>
+      <c r="BF4" s="98"/>
+      <c r="BG4" s="98"/>
+      <c r="BH4" s="98"/>
+      <c r="BI4" s="98"/>
+      <c r="BJ4" s="98"/>
+      <c r="BK4" s="98"/>
+      <c r="BL4" s="98"/>
+      <c r="BM4" s="98"/>
+      <c r="BN4" s="98"/>
+      <c r="BO4" s="98"/>
+      <c r="BP4" s="98"/>
+      <c r="BQ4" s="98"/>
+      <c r="BR4" s="98"/>
+      <c r="BS4" s="98"/>
+      <c r="BT4" s="98"/>
+      <c r="BU4" s="98"/>
+      <c r="BV4" s="98"/>
+      <c r="BW4" s="98"/>
+      <c r="BX4" s="98"/>
+      <c r="BY4" s="98"/>
+      <c r="BZ4" s="98"/>
+      <c r="CA4" s="98"/>
+      <c r="CB4" s="98"/>
+      <c r="CC4" s="98"/>
+      <c r="CD4" s="98"/>
+      <c r="CE4" s="98"/>
+      <c r="CF4" s="98"/>
+      <c r="CG4" s="98"/>
+      <c r="CH4" s="98"/>
+      <c r="CI4" s="98"/>
+      <c r="CJ4" s="98"/>
+      <c r="CK4" s="98"/>
+      <c r="CL4" s="98"/>
+      <c r="CM4" s="98"/>
+      <c r="CN4" s="98"/>
+      <c r="CO4" s="98"/>
+      <c r="CP4" s="98"/>
+      <c r="CQ4" s="98"/>
+      <c r="CR4" s="98"/>
+      <c r="CS4" s="98"/>
+      <c r="CT4" s="98"/>
+      <c r="CU4" s="98"/>
+      <c r="CV4" s="98"/>
+      <c r="CW4" s="98"/>
+      <c r="CX4" s="98"/>
+      <c r="CY4" s="98"/>
+      <c r="CZ4" s="98"/>
+      <c r="DA4" s="98"/>
+      <c r="DB4" s="98"/>
+      <c r="DC4" s="98"/>
+      <c r="DD4" s="98"/>
+      <c r="DE4" s="98"/>
+      <c r="DF4" s="98"/>
+      <c r="DG4" s="98"/>
+      <c r="DH4" s="98"/>
+      <c r="DI4" s="98"/>
+      <c r="DJ4" s="98"/>
+      <c r="DK4" s="98"/>
+      <c r="DL4" s="98"/>
+      <c r="DM4" s="98"/>
+      <c r="DN4" s="98"/>
+      <c r="DO4" s="98"/>
+      <c r="DP4" s="98"/>
+      <c r="DQ4" s="98"/>
+      <c r="DR4" s="98"/>
+      <c r="DS4" s="98"/>
+      <c r="DT4" s="98"/>
+      <c r="DU4" s="98"/>
+      <c r="DV4" s="98"/>
+      <c r="DW4" s="98"/>
+      <c r="DX4" s="98"/>
+      <c r="DY4" s="98"/>
+      <c r="DZ4" s="98"/>
+      <c r="EA4" s="98"/>
+      <c r="EB4" s="98"/>
+      <c r="EC4" s="98"/>
+      <c r="ED4" s="98"/>
+      <c r="EE4" s="98"/>
+      <c r="EF4" s="98"/>
+      <c r="EG4" s="98"/>
+      <c r="EH4" s="98"/>
+      <c r="EI4" s="98"/>
+      <c r="EJ4" s="98"/>
+      <c r="EK4" s="98"/>
+      <c r="EL4" s="98"/>
+      <c r="EM4" s="98"/>
+      <c r="EN4" s="98"/>
+      <c r="EO4" s="98"/>
+      <c r="EP4" s="98"/>
+      <c r="EQ4" s="98"/>
+      <c r="ER4" s="98"/>
+      <c r="ES4" s="98"/>
+      <c r="ET4" s="98"/>
+      <c r="EU4" s="98"/>
+      <c r="EV4" s="98"/>
+      <c r="EW4" s="98"/>
+      <c r="EX4" s="98"/>
+      <c r="EY4" s="98"/>
+      <c r="EZ4" s="98"/>
+      <c r="FA4" s="98"/>
+      <c r="FB4" s="98"/>
+      <c r="FC4" s="98"/>
+      <c r="FD4" s="98"/>
+      <c r="FE4" s="98"/>
+      <c r="FF4" s="98"/>
+      <c r="FG4" s="98"/>
+      <c r="FH4" s="98"/>
+      <c r="FI4" s="98"/>
+      <c r="FJ4" s="98"/>
+      <c r="FK4" s="98"/>
+      <c r="FL4" s="98"/>
+      <c r="FM4" s="98"/>
+      <c r="FN4" s="98"/>
+      <c r="FO4" s="98"/>
+      <c r="FP4" s="98"/>
+      <c r="FQ4" s="98"/>
+      <c r="FR4" s="98"/>
+      <c r="FS4" s="98"/>
+      <c r="FT4" s="98"/>
+      <c r="FU4" s="98"/>
+      <c r="FV4" s="98"/>
+      <c r="FW4" s="98"/>
+      <c r="FX4" s="98"/>
+      <c r="FY4" s="98"/>
+      <c r="FZ4" s="98"/>
+      <c r="GA4" s="98"/>
+      <c r="GB4" s="98"/>
+      <c r="GC4" s="98"/>
+      <c r="GD4" s="98"/>
+      <c r="GE4" s="98"/>
+      <c r="GF4" s="98"/>
+      <c r="GG4" s="98"/>
+      <c r="GH4" s="98"/>
+      <c r="GI4" s="98"/>
+      <c r="GJ4" s="98"/>
+      <c r="GK4" s="98"/>
+      <c r="GL4" s="98"/>
+      <c r="GM4" s="98"/>
+      <c r="GN4" s="98"/>
+      <c r="GO4" s="98"/>
+      <c r="GP4" s="98"/>
+      <c r="GQ4" s="98"/>
+      <c r="GR4" s="98"/>
+      <c r="GS4" s="98"/>
+      <c r="GT4" s="98"/>
+      <c r="GU4" s="98"/>
+      <c r="GV4" s="98"/>
+      <c r="GW4" s="98"/>
+      <c r="GX4" s="98"/>
+      <c r="GY4" s="98"/>
+      <c r="GZ4" s="98"/>
+      <c r="HA4" s="98"/>
+      <c r="HB4" s="98"/>
+      <c r="HC4" s="98"/>
+      <c r="HD4" s="98"/>
+      <c r="HE4" s="98"/>
+      <c r="HF4" s="98"/>
+      <c r="HG4" s="98"/>
+      <c r="HH4" s="98"/>
+      <c r="HI4" s="98"/>
+      <c r="HJ4" s="98"/>
+      <c r="HK4" s="98"/>
+      <c r="HL4" s="98"/>
+      <c r="HM4" s="98"/>
+      <c r="HN4" s="98"/>
+      <c r="HO4" s="98"/>
+      <c r="HP4" s="98"/>
+      <c r="HQ4" s="98"/>
+      <c r="HR4" s="98"/>
+      <c r="HS4" s="98"/>
+      <c r="HT4" s="98"/>
+      <c r="HU4" s="98"/>
+      <c r="HV4" s="98"/>
+      <c r="HW4" s="98"/>
+      <c r="HX4" s="98"/>
+      <c r="HY4" s="98"/>
+      <c r="HZ4" s="98"/>
+      <c r="IA4" s="98"/>
+      <c r="IB4" s="98"/>
+      <c r="IC4" s="98"/>
+      <c r="ID4" s="98"/>
+      <c r="IE4" s="98"/>
+      <c r="IF4" s="98"/>
+      <c r="IG4" s="98"/>
+      <c r="IH4" s="98"/>
+      <c r="II4" s="98"/>
+      <c r="IJ4" s="98"/>
+      <c r="IK4" s="98"/>
+      <c r="IL4" s="98"/>
+      <c r="IM4" s="98"/>
+      <c r="IN4" s="98"/>
+      <c r="IO4" s="98"/>
+      <c r="IP4" s="98"/>
+      <c r="IQ4" s="98"/>
+      <c r="IR4" s="98"/>
+      <c r="IS4" s="98"/>
+      <c r="IT4" s="98"/>
+      <c r="IU4" s="98"/>
+      <c r="IV4" s="98"/>
+      <c r="IW4" s="98"/>
     </row>
     <row r="5" spans="1:257" ht="39.950000000000003" customHeight="1">
-      <c r="A5" s="154" t="s">
+      <c r="A5" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="154"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="120">
+      <c r="B5" s="155"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="106">
         <f>F4</f>
-        <v>3941280</v>
+        <v>4200000</v>
       </c>
-      <c r="G5" s="120">
+      <c r="G5" s="106">
         <f>G4</f>
-        <v>3941280</v>
+        <v>4200000</v>
       </c>
-      <c r="H5" s="106">
+      <c r="H5" s="92">
         <f>H4</f>
-        <v>7882560</v>
+        <v>8400000</v>
       </c>
-      <c r="I5" s="121"/>
+      <c r="I5" s="107"/>
     </row>
     <row r="6" spans="1:257" ht="39.950000000000003" customHeight="1">
-      <c r="A6" s="155" t="s">
+      <c r="A6" s="156" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="155"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="123">
+      <c r="B6" s="156"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109">
         <f>F5*0.1</f>
-        <v>394128</v>
+        <v>420000</v>
       </c>
-      <c r="G6" s="124">
+      <c r="G6" s="110">
         <f>G5*0.1</f>
-        <v>394128</v>
+        <v>420000</v>
       </c>
-      <c r="H6" s="123">
+      <c r="H6" s="109">
         <f>H5*0.1</f>
-        <v>788256</v>
+        <v>840000</v>
       </c>
-      <c r="I6" s="125"/>
+      <c r="I6" s="111"/>
     </row>
     <row r="7" spans="1:257" ht="39.950000000000003" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="155" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="154"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="120">
+      <c r="B7" s="155"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="106">
         <f>SUM(F5:F6)</f>
-        <v>4335408</v>
+        <v>4620000</v>
       </c>
-      <c r="G7" s="120">
+      <c r="G7" s="106">
         <f>SUM(G5:G6)</f>
-        <v>4335408</v>
+        <v>4620000</v>
       </c>
-      <c r="H7" s="106">
+      <c r="H7" s="92">
         <f>H5+H6</f>
-        <v>8670816</v>
+        <v>9240000</v>
       </c>
-      <c r="I7" s="126"/>
-      <c r="J7" s="109"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110"/>
-      <c r="M7" s="101"/>
-      <c r="N7" s="101"/>
-      <c r="O7" s="112"/>
-      <c r="P7" s="112"/>
-      <c r="Q7" s="112"/>
-      <c r="R7" s="112"/>
-      <c r="S7" s="112"/>
-      <c r="T7" s="112"/>
-      <c r="U7" s="112"/>
-      <c r="V7" s="112"/>
-      <c r="W7" s="112"/>
-      <c r="X7" s="112"/>
-      <c r="Y7" s="112"/>
-      <c r="Z7" s="112"/>
-      <c r="AA7" s="112"/>
-      <c r="AB7" s="112"/>
-      <c r="AC7" s="112"/>
-      <c r="AD7" s="112"/>
-      <c r="AE7" s="112"/>
-      <c r="AF7" s="112"/>
-      <c r="AG7" s="112"/>
-      <c r="AH7" s="112"/>
-      <c r="AI7" s="112"/>
-      <c r="AJ7" s="112"/>
-      <c r="AK7" s="112"/>
-      <c r="AL7" s="112"/>
-      <c r="AM7" s="112"/>
-      <c r="AN7" s="112"/>
-      <c r="AO7" s="112"/>
-      <c r="AP7" s="112"/>
-      <c r="AQ7" s="112"/>
-      <c r="AR7" s="112"/>
-      <c r="AS7" s="112"/>
-      <c r="AT7" s="112"/>
-      <c r="AU7" s="112"/>
-      <c r="AV7" s="112"/>
-      <c r="AW7" s="112"/>
-      <c r="AX7" s="112"/>
-      <c r="AY7" s="112"/>
-      <c r="AZ7" s="112"/>
-      <c r="BA7" s="112"/>
-      <c r="BB7" s="112"/>
-      <c r="BC7" s="112"/>
-      <c r="BD7" s="112"/>
-      <c r="BE7" s="112"/>
-      <c r="BF7" s="112"/>
-      <c r="BG7" s="112"/>
-      <c r="BH7" s="112"/>
-      <c r="BI7" s="112"/>
-      <c r="BJ7" s="112"/>
-      <c r="BK7" s="112"/>
-      <c r="BL7" s="112"/>
-      <c r="BM7" s="112"/>
-      <c r="BN7" s="112"/>
-      <c r="BO7" s="112"/>
-      <c r="BP7" s="112"/>
-      <c r="BQ7" s="112"/>
-      <c r="BR7" s="112"/>
-      <c r="BS7" s="112"/>
-      <c r="BT7" s="112"/>
-      <c r="BU7" s="112"/>
-      <c r="BV7" s="112"/>
-      <c r="BW7" s="112"/>
-      <c r="BX7" s="112"/>
-      <c r="BY7" s="112"/>
-      <c r="BZ7" s="112"/>
-      <c r="CA7" s="112"/>
-      <c r="CB7" s="112"/>
-      <c r="CC7" s="112"/>
-      <c r="CD7" s="112"/>
-      <c r="CE7" s="112"/>
-      <c r="CF7" s="112"/>
-      <c r="CG7" s="112"/>
-      <c r="CH7" s="112"/>
-      <c r="CI7" s="112"/>
-      <c r="CJ7" s="112"/>
-      <c r="CK7" s="112"/>
-      <c r="CL7" s="112"/>
-      <c r="CM7" s="112"/>
-      <c r="CN7" s="112"/>
-      <c r="CO7" s="112"/>
-      <c r="CP7" s="112"/>
-      <c r="CQ7" s="112"/>
-      <c r="CR7" s="112"/>
-      <c r="CS7" s="112"/>
-      <c r="CT7" s="112"/>
-      <c r="CU7" s="112"/>
-      <c r="CV7" s="112"/>
-      <c r="CW7" s="112"/>
-      <c r="CX7" s="112"/>
-      <c r="CY7" s="112"/>
-      <c r="CZ7" s="112"/>
-      <c r="DA7" s="112"/>
-      <c r="DB7" s="112"/>
-      <c r="DC7" s="112"/>
-      <c r="DD7" s="112"/>
-      <c r="DE7" s="112"/>
-      <c r="DF7" s="112"/>
-      <c r="DG7" s="112"/>
-      <c r="DH7" s="112"/>
-      <c r="DI7" s="112"/>
-      <c r="DJ7" s="112"/>
-      <c r="DK7" s="112"/>
-      <c r="DL7" s="112"/>
-      <c r="DM7" s="112"/>
-      <c r="DN7" s="112"/>
-      <c r="DO7" s="112"/>
-      <c r="DP7" s="112"/>
-      <c r="DQ7" s="112"/>
-      <c r="DR7" s="112"/>
-      <c r="DS7" s="112"/>
-      <c r="DT7" s="112"/>
-      <c r="DU7" s="112"/>
-      <c r="DV7" s="112"/>
-      <c r="DW7" s="112"/>
-      <c r="DX7" s="112"/>
-      <c r="DY7" s="112"/>
-      <c r="DZ7" s="112"/>
-      <c r="EA7" s="112"/>
-      <c r="EB7" s="112"/>
-      <c r="EC7" s="112"/>
-      <c r="ED7" s="112"/>
-      <c r="EE7" s="112"/>
-      <c r="EF7" s="112"/>
-      <c r="EG7" s="112"/>
-      <c r="EH7" s="112"/>
-      <c r="EI7" s="112"/>
-      <c r="EJ7" s="112"/>
-      <c r="EK7" s="112"/>
-      <c r="EL7" s="112"/>
-      <c r="EM7" s="112"/>
-      <c r="EN7" s="112"/>
-      <c r="EO7" s="112"/>
-      <c r="EP7" s="112"/>
-      <c r="EQ7" s="112"/>
-      <c r="ER7" s="112"/>
-      <c r="ES7" s="112"/>
-      <c r="ET7" s="112"/>
-      <c r="EU7" s="112"/>
-      <c r="EV7" s="112"/>
-      <c r="EW7" s="112"/>
-      <c r="EX7" s="112"/>
-      <c r="EY7" s="112"/>
-      <c r="EZ7" s="112"/>
-      <c r="FA7" s="112"/>
-      <c r="FB7" s="112"/>
-      <c r="FC7" s="112"/>
-      <c r="FD7" s="112"/>
-      <c r="FE7" s="112"/>
-      <c r="FF7" s="112"/>
-      <c r="FG7" s="112"/>
-      <c r="FH7" s="112"/>
-      <c r="FI7" s="112"/>
-      <c r="FJ7" s="112"/>
-      <c r="FK7" s="112"/>
-      <c r="FL7" s="112"/>
-      <c r="FM7" s="112"/>
-      <c r="FN7" s="112"/>
-      <c r="FO7" s="112"/>
-      <c r="FP7" s="112"/>
-      <c r="FQ7" s="112"/>
-      <c r="FR7" s="112"/>
-      <c r="FS7" s="112"/>
-      <c r="FT7" s="112"/>
-      <c r="FU7" s="112"/>
-      <c r="FV7" s="112"/>
-      <c r="FW7" s="112"/>
-      <c r="FX7" s="112"/>
-      <c r="FY7" s="112"/>
-      <c r="FZ7" s="112"/>
-      <c r="GA7" s="112"/>
-      <c r="GB7" s="112"/>
-      <c r="GC7" s="112"/>
-      <c r="GD7" s="112"/>
-      <c r="GE7" s="112"/>
-      <c r="GF7" s="112"/>
-      <c r="GG7" s="112"/>
-      <c r="GH7" s="112"/>
-      <c r="GI7" s="112"/>
-      <c r="GJ7" s="112"/>
-      <c r="GK7" s="112"/>
-      <c r="GL7" s="112"/>
-      <c r="GM7" s="112"/>
-      <c r="GN7" s="112"/>
-      <c r="GO7" s="112"/>
-      <c r="GP7" s="112"/>
-      <c r="GQ7" s="112"/>
-      <c r="GR7" s="112"/>
-      <c r="GS7" s="112"/>
-      <c r="GT7" s="112"/>
-      <c r="GU7" s="112"/>
-      <c r="GV7" s="112"/>
-      <c r="GW7" s="112"/>
-      <c r="GX7" s="112"/>
-      <c r="GY7" s="112"/>
-      <c r="GZ7" s="112"/>
-      <c r="HA7" s="112"/>
-      <c r="HB7" s="112"/>
-      <c r="HC7" s="112"/>
-      <c r="HD7" s="112"/>
-      <c r="HE7" s="112"/>
-      <c r="HF7" s="112"/>
-      <c r="HG7" s="112"/>
-      <c r="HH7" s="112"/>
-      <c r="HI7" s="112"/>
-      <c r="HJ7" s="112"/>
-      <c r="HK7" s="112"/>
-      <c r="HL7" s="112"/>
-      <c r="HM7" s="112"/>
-      <c r="HN7" s="112"/>
-      <c r="HO7" s="112"/>
-      <c r="HP7" s="112"/>
-      <c r="HQ7" s="112"/>
-      <c r="HR7" s="112"/>
-      <c r="HS7" s="112"/>
-      <c r="HT7" s="112"/>
-      <c r="HU7" s="112"/>
-      <c r="HV7" s="112"/>
-      <c r="HW7" s="112"/>
-      <c r="HX7" s="112"/>
-      <c r="HY7" s="112"/>
-      <c r="HZ7" s="112"/>
-      <c r="IA7" s="112"/>
-      <c r="IB7" s="112"/>
-      <c r="IC7" s="112"/>
-      <c r="ID7" s="112"/>
-      <c r="IE7" s="112"/>
-      <c r="IF7" s="112"/>
-      <c r="IG7" s="112"/>
-      <c r="IH7" s="112"/>
-      <c r="II7" s="112"/>
-      <c r="IJ7" s="112"/>
-      <c r="IK7" s="112"/>
-      <c r="IL7" s="112"/>
-      <c r="IM7" s="112"/>
-      <c r="IN7" s="112"/>
-      <c r="IO7" s="112"/>
-      <c r="IP7" s="112"/>
-      <c r="IQ7" s="112"/>
-      <c r="IR7" s="112"/>
-      <c r="IS7" s="112"/>
-      <c r="IT7" s="112"/>
-      <c r="IU7" s="112"/>
-      <c r="IV7" s="112"/>
-      <c r="IW7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="95"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="98"/>
+      <c r="P7" s="98"/>
+      <c r="Q7" s="98"/>
+      <c r="R7" s="98"/>
+      <c r="S7" s="98"/>
+      <c r="T7" s="98"/>
+      <c r="U7" s="98"/>
+      <c r="V7" s="98"/>
+      <c r="W7" s="98"/>
+      <c r="X7" s="98"/>
+      <c r="Y7" s="98"/>
+      <c r="Z7" s="98"/>
+      <c r="AA7" s="98"/>
+      <c r="AB7" s="98"/>
+      <c r="AC7" s="98"/>
+      <c r="AD7" s="98"/>
+      <c r="AE7" s="98"/>
+      <c r="AF7" s="98"/>
+      <c r="AG7" s="98"/>
+      <c r="AH7" s="98"/>
+      <c r="AI7" s="98"/>
+      <c r="AJ7" s="98"/>
+      <c r="AK7" s="98"/>
+      <c r="AL7" s="98"/>
+      <c r="AM7" s="98"/>
+      <c r="AN7" s="98"/>
+      <c r="AO7" s="98"/>
+      <c r="AP7" s="98"/>
+      <c r="AQ7" s="98"/>
+      <c r="AR7" s="98"/>
+      <c r="AS7" s="98"/>
+      <c r="AT7" s="98"/>
+      <c r="AU7" s="98"/>
+      <c r="AV7" s="98"/>
+      <c r="AW7" s="98"/>
+      <c r="AX7" s="98"/>
+      <c r="AY7" s="98"/>
+      <c r="AZ7" s="98"/>
+      <c r="BA7" s="98"/>
+      <c r="BB7" s="98"/>
+      <c r="BC7" s="98"/>
+      <c r="BD7" s="98"/>
+      <c r="BE7" s="98"/>
+      <c r="BF7" s="98"/>
+      <c r="BG7" s="98"/>
+      <c r="BH7" s="98"/>
+      <c r="BI7" s="98"/>
+      <c r="BJ7" s="98"/>
+      <c r="BK7" s="98"/>
+      <c r="BL7" s="98"/>
+      <c r="BM7" s="98"/>
+      <c r="BN7" s="98"/>
+      <c r="BO7" s="98"/>
+      <c r="BP7" s="98"/>
+      <c r="BQ7" s="98"/>
+      <c r="BR7" s="98"/>
+      <c r="BS7" s="98"/>
+      <c r="BT7" s="98"/>
+      <c r="BU7" s="98"/>
+      <c r="BV7" s="98"/>
+      <c r="BW7" s="98"/>
+      <c r="BX7" s="98"/>
+      <c r="BY7" s="98"/>
+      <c r="BZ7" s="98"/>
+      <c r="CA7" s="98"/>
+      <c r="CB7" s="98"/>
+      <c r="CC7" s="98"/>
+      <c r="CD7" s="98"/>
+      <c r="CE7" s="98"/>
+      <c r="CF7" s="98"/>
+      <c r="CG7" s="98"/>
+      <c r="CH7" s="98"/>
+      <c r="CI7" s="98"/>
+      <c r="CJ7" s="98"/>
+      <c r="CK7" s="98"/>
+      <c r="CL7" s="98"/>
+      <c r="CM7" s="98"/>
+      <c r="CN7" s="98"/>
+      <c r="CO7" s="98"/>
+      <c r="CP7" s="98"/>
+      <c r="CQ7" s="98"/>
+      <c r="CR7" s="98"/>
+      <c r="CS7" s="98"/>
+      <c r="CT7" s="98"/>
+      <c r="CU7" s="98"/>
+      <c r="CV7" s="98"/>
+      <c r="CW7" s="98"/>
+      <c r="CX7" s="98"/>
+      <c r="CY7" s="98"/>
+      <c r="CZ7" s="98"/>
+      <c r="DA7" s="98"/>
+      <c r="DB7" s="98"/>
+      <c r="DC7" s="98"/>
+      <c r="DD7" s="98"/>
+      <c r="DE7" s="98"/>
+      <c r="DF7" s="98"/>
+      <c r="DG7" s="98"/>
+      <c r="DH7" s="98"/>
+      <c r="DI7" s="98"/>
+      <c r="DJ7" s="98"/>
+      <c r="DK7" s="98"/>
+      <c r="DL7" s="98"/>
+      <c r="DM7" s="98"/>
+      <c r="DN7" s="98"/>
+      <c r="DO7" s="98"/>
+      <c r="DP7" s="98"/>
+      <c r="DQ7" s="98"/>
+      <c r="DR7" s="98"/>
+      <c r="DS7" s="98"/>
+      <c r="DT7" s="98"/>
+      <c r="DU7" s="98"/>
+      <c r="DV7" s="98"/>
+      <c r="DW7" s="98"/>
+      <c r="DX7" s="98"/>
+      <c r="DY7" s="98"/>
+      <c r="DZ7" s="98"/>
+      <c r="EA7" s="98"/>
+      <c r="EB7" s="98"/>
+      <c r="EC7" s="98"/>
+      <c r="ED7" s="98"/>
+      <c r="EE7" s="98"/>
+      <c r="EF7" s="98"/>
+      <c r="EG7" s="98"/>
+      <c r="EH7" s="98"/>
+      <c r="EI7" s="98"/>
+      <c r="EJ7" s="98"/>
+      <c r="EK7" s="98"/>
+      <c r="EL7" s="98"/>
+      <c r="EM7" s="98"/>
+      <c r="EN7" s="98"/>
+      <c r="EO7" s="98"/>
+      <c r="EP7" s="98"/>
+      <c r="EQ7" s="98"/>
+      <c r="ER7" s="98"/>
+      <c r="ES7" s="98"/>
+      <c r="ET7" s="98"/>
+      <c r="EU7" s="98"/>
+      <c r="EV7" s="98"/>
+      <c r="EW7" s="98"/>
+      <c r="EX7" s="98"/>
+      <c r="EY7" s="98"/>
+      <c r="EZ7" s="98"/>
+      <c r="FA7" s="98"/>
+      <c r="FB7" s="98"/>
+      <c r="FC7" s="98"/>
+      <c r="FD7" s="98"/>
+      <c r="FE7" s="98"/>
+      <c r="FF7" s="98"/>
+      <c r="FG7" s="98"/>
+      <c r="FH7" s="98"/>
+      <c r="FI7" s="98"/>
+      <c r="FJ7" s="98"/>
+      <c r="FK7" s="98"/>
+      <c r="FL7" s="98"/>
+      <c r="FM7" s="98"/>
+      <c r="FN7" s="98"/>
+      <c r="FO7" s="98"/>
+      <c r="FP7" s="98"/>
+      <c r="FQ7" s="98"/>
+      <c r="FR7" s="98"/>
+      <c r="FS7" s="98"/>
+      <c r="FT7" s="98"/>
+      <c r="FU7" s="98"/>
+      <c r="FV7" s="98"/>
+      <c r="FW7" s="98"/>
+      <c r="FX7" s="98"/>
+      <c r="FY7" s="98"/>
+      <c r="FZ7" s="98"/>
+      <c r="GA7" s="98"/>
+      <c r="GB7" s="98"/>
+      <c r="GC7" s="98"/>
+      <c r="GD7" s="98"/>
+      <c r="GE7" s="98"/>
+      <c r="GF7" s="98"/>
+      <c r="GG7" s="98"/>
+      <c r="GH7" s="98"/>
+      <c r="GI7" s="98"/>
+      <c r="GJ7" s="98"/>
+      <c r="GK7" s="98"/>
+      <c r="GL7" s="98"/>
+      <c r="GM7" s="98"/>
+      <c r="GN7" s="98"/>
+      <c r="GO7" s="98"/>
+      <c r="GP7" s="98"/>
+      <c r="GQ7" s="98"/>
+      <c r="GR7" s="98"/>
+      <c r="GS7" s="98"/>
+      <c r="GT7" s="98"/>
+      <c r="GU7" s="98"/>
+      <c r="GV7" s="98"/>
+      <c r="GW7" s="98"/>
+      <c r="GX7" s="98"/>
+      <c r="GY7" s="98"/>
+      <c r="GZ7" s="98"/>
+      <c r="HA7" s="98"/>
+      <c r="HB7" s="98"/>
+      <c r="HC7" s="98"/>
+      <c r="HD7" s="98"/>
+      <c r="HE7" s="98"/>
+      <c r="HF7" s="98"/>
+      <c r="HG7" s="98"/>
+      <c r="HH7" s="98"/>
+      <c r="HI7" s="98"/>
+      <c r="HJ7" s="98"/>
+      <c r="HK7" s="98"/>
+      <c r="HL7" s="98"/>
+      <c r="HM7" s="98"/>
+      <c r="HN7" s="98"/>
+      <c r="HO7" s="98"/>
+      <c r="HP7" s="98"/>
+      <c r="HQ7" s="98"/>
+      <c r="HR7" s="98"/>
+      <c r="HS7" s="98"/>
+      <c r="HT7" s="98"/>
+      <c r="HU7" s="98"/>
+      <c r="HV7" s="98"/>
+      <c r="HW7" s="98"/>
+      <c r="HX7" s="98"/>
+      <c r="HY7" s="98"/>
+      <c r="HZ7" s="98"/>
+      <c r="IA7" s="98"/>
+      <c r="IB7" s="98"/>
+      <c r="IC7" s="98"/>
+      <c r="ID7" s="98"/>
+      <c r="IE7" s="98"/>
+      <c r="IF7" s="98"/>
+      <c r="IG7" s="98"/>
+      <c r="IH7" s="98"/>
+      <c r="II7" s="98"/>
+      <c r="IJ7" s="98"/>
+      <c r="IK7" s="98"/>
+      <c r="IL7" s="98"/>
+      <c r="IM7" s="98"/>
+      <c r="IN7" s="98"/>
+      <c r="IO7" s="98"/>
+      <c r="IP7" s="98"/>
+      <c r="IQ7" s="98"/>
+      <c r="IR7" s="98"/>
+      <c r="IS7" s="98"/>
+      <c r="IT7" s="98"/>
+      <c r="IU7" s="98"/>
+      <c r="IV7" s="98"/>
+      <c r="IW7" s="98"/>
     </row>
     <row r="8" spans="1:257" ht="39.950000000000003" customHeight="1">
-      <c r="A8" s="156" t="s">
+      <c r="A8" s="152" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="156"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="129"/>
-      <c r="F8" s="130">
-        <f>ROUNDDOWN(F7*1,-3)</f>
-        <v>4335000</v>
+      <c r="B8" s="152"/>
+      <c r="C8" s="113"/>
+      <c r="D8" s="114"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="116">
+        <f>F7</f>
+        <v>4620000</v>
       </c>
-      <c r="G8" s="130">
-        <f>ROUNDDOWN(G7*1,-3)</f>
-        <v>4335000</v>
+      <c r="G8" s="116">
+        <f>G7</f>
+        <v>4620000</v>
       </c>
-      <c r="H8" s="131">
+      <c r="H8" s="117">
         <f>F8+G8</f>
-        <v>8670000</v>
+        <v>9240000</v>
       </c>
-      <c r="I8" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="109"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="110"/>
-      <c r="M8" s="101"/>
-      <c r="N8" s="101"/>
-      <c r="O8" s="112"/>
-      <c r="P8" s="112"/>
-      <c r="Q8" s="112"/>
-      <c r="R8" s="112"/>
-      <c r="S8" s="112"/>
-      <c r="T8" s="112"/>
-      <c r="U8" s="112"/>
-      <c r="V8" s="112"/>
-      <c r="W8" s="112"/>
-      <c r="X8" s="112"/>
-      <c r="Y8" s="112"/>
-      <c r="Z8" s="112"/>
-      <c r="AA8" s="112"/>
-      <c r="AB8" s="112"/>
-      <c r="AC8" s="112"/>
-      <c r="AD8" s="112"/>
-      <c r="AE8" s="112"/>
-      <c r="AF8" s="112"/>
-      <c r="AG8" s="112"/>
-      <c r="AH8" s="112"/>
-      <c r="AI8" s="112"/>
-      <c r="AJ8" s="112"/>
-      <c r="AK8" s="112"/>
-      <c r="AL8" s="112"/>
-      <c r="AM8" s="112"/>
-      <c r="AN8" s="112"/>
-      <c r="AO8" s="112"/>
-      <c r="AP8" s="112"/>
-      <c r="AQ8" s="112"/>
-      <c r="AR8" s="112"/>
-      <c r="AS8" s="112"/>
-      <c r="AT8" s="112"/>
-      <c r="AU8" s="112"/>
-      <c r="AV8" s="112"/>
-      <c r="AW8" s="112"/>
-      <c r="AX8" s="112"/>
-      <c r="AY8" s="112"/>
-      <c r="AZ8" s="112"/>
-      <c r="BA8" s="112"/>
-      <c r="BB8" s="112"/>
-      <c r="BC8" s="112"/>
-      <c r="BD8" s="112"/>
-      <c r="BE8" s="112"/>
-      <c r="BF8" s="112"/>
-      <c r="BG8" s="112"/>
-      <c r="BH8" s="112"/>
-      <c r="BI8" s="112"/>
-      <c r="BJ8" s="112"/>
-      <c r="BK8" s="112"/>
-      <c r="BL8" s="112"/>
-      <c r="BM8" s="112"/>
-      <c r="BN8" s="112"/>
-      <c r="BO8" s="112"/>
-      <c r="BP8" s="112"/>
-      <c r="BQ8" s="112"/>
-      <c r="BR8" s="112"/>
-      <c r="BS8" s="112"/>
-      <c r="BT8" s="112"/>
-      <c r="BU8" s="112"/>
-      <c r="BV8" s="112"/>
-      <c r="BW8" s="112"/>
-      <c r="BX8" s="112"/>
-      <c r="BY8" s="112"/>
-      <c r="BZ8" s="112"/>
-      <c r="CA8" s="112"/>
-      <c r="CB8" s="112"/>
-      <c r="CC8" s="112"/>
-      <c r="CD8" s="112"/>
-      <c r="CE8" s="112"/>
-      <c r="CF8" s="112"/>
-      <c r="CG8" s="112"/>
-      <c r="CH8" s="112"/>
-      <c r="CI8" s="112"/>
-      <c r="CJ8" s="112"/>
-      <c r="CK8" s="112"/>
-      <c r="CL8" s="112"/>
-      <c r="CM8" s="112"/>
-      <c r="CN8" s="112"/>
-      <c r="CO8" s="112"/>
-      <c r="CP8" s="112"/>
-      <c r="CQ8" s="112"/>
-      <c r="CR8" s="112"/>
-      <c r="CS8" s="112"/>
-      <c r="CT8" s="112"/>
-      <c r="CU8" s="112"/>
-      <c r="CV8" s="112"/>
-      <c r="CW8" s="112"/>
-      <c r="CX8" s="112"/>
-      <c r="CY8" s="112"/>
-      <c r="CZ8" s="112"/>
-      <c r="DA8" s="112"/>
-      <c r="DB8" s="112"/>
-      <c r="DC8" s="112"/>
-      <c r="DD8" s="112"/>
-      <c r="DE8" s="112"/>
-      <c r="DF8" s="112"/>
-      <c r="DG8" s="112"/>
-      <c r="DH8" s="112"/>
-      <c r="DI8" s="112"/>
-      <c r="DJ8" s="112"/>
-      <c r="DK8" s="112"/>
-      <c r="DL8" s="112"/>
-      <c r="DM8" s="112"/>
-      <c r="DN8" s="112"/>
-      <c r="DO8" s="112"/>
-      <c r="DP8" s="112"/>
-      <c r="DQ8" s="112"/>
-      <c r="DR8" s="112"/>
-      <c r="DS8" s="112"/>
-      <c r="DT8" s="112"/>
-      <c r="DU8" s="112"/>
-      <c r="DV8" s="112"/>
-      <c r="DW8" s="112"/>
-      <c r="DX8" s="112"/>
-      <c r="DY8" s="112"/>
-      <c r="DZ8" s="112"/>
-      <c r="EA8" s="112"/>
-      <c r="EB8" s="112"/>
-      <c r="EC8" s="112"/>
-      <c r="ED8" s="112"/>
-      <c r="EE8" s="112"/>
-      <c r="EF8" s="112"/>
-      <c r="EG8" s="112"/>
-      <c r="EH8" s="112"/>
-      <c r="EI8" s="112"/>
-      <c r="EJ8" s="112"/>
-      <c r="EK8" s="112"/>
-      <c r="EL8" s="112"/>
-      <c r="EM8" s="112"/>
-      <c r="EN8" s="112"/>
-      <c r="EO8" s="112"/>
-      <c r="EP8" s="112"/>
-      <c r="EQ8" s="112"/>
-      <c r="ER8" s="112"/>
-      <c r="ES8" s="112"/>
-      <c r="ET8" s="112"/>
-      <c r="EU8" s="112"/>
-      <c r="EV8" s="112"/>
-      <c r="EW8" s="112"/>
-      <c r="EX8" s="112"/>
-      <c r="EY8" s="112"/>
-      <c r="EZ8" s="112"/>
-      <c r="FA8" s="112"/>
-      <c r="FB8" s="112"/>
-      <c r="FC8" s="112"/>
-      <c r="FD8" s="112"/>
-      <c r="FE8" s="112"/>
-      <c r="FF8" s="112"/>
-      <c r="FG8" s="112"/>
-      <c r="FH8" s="112"/>
-      <c r="FI8" s="112"/>
-      <c r="FJ8" s="112"/>
-      <c r="FK8" s="112"/>
-      <c r="FL8" s="112"/>
-      <c r="FM8" s="112"/>
-      <c r="FN8" s="112"/>
-      <c r="FO8" s="112"/>
-      <c r="FP8" s="112"/>
-      <c r="FQ8" s="112"/>
-      <c r="FR8" s="112"/>
-      <c r="FS8" s="112"/>
-      <c r="FT8" s="112"/>
-      <c r="FU8" s="112"/>
-      <c r="FV8" s="112"/>
-      <c r="FW8" s="112"/>
-      <c r="FX8" s="112"/>
-      <c r="FY8" s="112"/>
-      <c r="FZ8" s="112"/>
-      <c r="GA8" s="112"/>
-      <c r="GB8" s="112"/>
-      <c r="GC8" s="112"/>
-      <c r="GD8" s="112"/>
-      <c r="GE8" s="112"/>
-      <c r="GF8" s="112"/>
-      <c r="GG8" s="112"/>
-      <c r="GH8" s="112"/>
-      <c r="GI8" s="112"/>
-      <c r="GJ8" s="112"/>
-      <c r="GK8" s="112"/>
-      <c r="GL8" s="112"/>
-      <c r="GM8" s="112"/>
-      <c r="GN8" s="112"/>
-      <c r="GO8" s="112"/>
-      <c r="GP8" s="112"/>
-      <c r="GQ8" s="112"/>
-      <c r="GR8" s="112"/>
-      <c r="GS8" s="112"/>
-      <c r="GT8" s="112"/>
-      <c r="GU8" s="112"/>
-      <c r="GV8" s="112"/>
-      <c r="GW8" s="112"/>
-      <c r="GX8" s="112"/>
-      <c r="GY8" s="112"/>
-      <c r="GZ8" s="112"/>
-      <c r="HA8" s="112"/>
-      <c r="HB8" s="112"/>
-      <c r="HC8" s="112"/>
-      <c r="HD8" s="112"/>
-      <c r="HE8" s="112"/>
-      <c r="HF8" s="112"/>
-      <c r="HG8" s="112"/>
-      <c r="HH8" s="112"/>
-      <c r="HI8" s="112"/>
-      <c r="HJ8" s="112"/>
-      <c r="HK8" s="112"/>
-      <c r="HL8" s="112"/>
-      <c r="HM8" s="112"/>
-      <c r="HN8" s="112"/>
-      <c r="HO8" s="112"/>
-      <c r="HP8" s="112"/>
-      <c r="HQ8" s="112"/>
-      <c r="HR8" s="112"/>
-      <c r="HS8" s="112"/>
-      <c r="HT8" s="112"/>
-      <c r="HU8" s="112"/>
-      <c r="HV8" s="112"/>
-      <c r="HW8" s="112"/>
-      <c r="HX8" s="112"/>
-      <c r="HY8" s="112"/>
-      <c r="HZ8" s="112"/>
-      <c r="IA8" s="112"/>
-      <c r="IB8" s="112"/>
-      <c r="IC8" s="112"/>
-      <c r="ID8" s="112"/>
-      <c r="IE8" s="112"/>
-      <c r="IF8" s="112"/>
-      <c r="IG8" s="112"/>
-      <c r="IH8" s="112"/>
-      <c r="II8" s="112"/>
-      <c r="IJ8" s="112"/>
-      <c r="IK8" s="112"/>
-      <c r="IL8" s="112"/>
-      <c r="IM8" s="112"/>
-      <c r="IN8" s="112"/>
-      <c r="IO8" s="112"/>
-      <c r="IP8" s="112"/>
-      <c r="IQ8" s="112"/>
-      <c r="IR8" s="112"/>
-      <c r="IS8" s="112"/>
-      <c r="IT8" s="112"/>
-      <c r="IU8" s="112"/>
-      <c r="IV8" s="112"/>
-      <c r="IW8" s="112"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="95"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="87"/>
+      <c r="N8" s="87"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="98"/>
+      <c r="U8" s="98"/>
+      <c r="V8" s="98"/>
+      <c r="W8" s="98"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="98"/>
+      <c r="AB8" s="98"/>
+      <c r="AC8" s="98"/>
+      <c r="AD8" s="98"/>
+      <c r="AE8" s="98"/>
+      <c r="AF8" s="98"/>
+      <c r="AG8" s="98"/>
+      <c r="AH8" s="98"/>
+      <c r="AI8" s="98"/>
+      <c r="AJ8" s="98"/>
+      <c r="AK8" s="98"/>
+      <c r="AL8" s="98"/>
+      <c r="AM8" s="98"/>
+      <c r="AN8" s="98"/>
+      <c r="AO8" s="98"/>
+      <c r="AP8" s="98"/>
+      <c r="AQ8" s="98"/>
+      <c r="AR8" s="98"/>
+      <c r="AS8" s="98"/>
+      <c r="AT8" s="98"/>
+      <c r="AU8" s="98"/>
+      <c r="AV8" s="98"/>
+      <c r="AW8" s="98"/>
+      <c r="AX8" s="98"/>
+      <c r="AY8" s="98"/>
+      <c r="AZ8" s="98"/>
+      <c r="BA8" s="98"/>
+      <c r="BB8" s="98"/>
+      <c r="BC8" s="98"/>
+      <c r="BD8" s="98"/>
+      <c r="BE8" s="98"/>
+      <c r="BF8" s="98"/>
+      <c r="BG8" s="98"/>
+      <c r="BH8" s="98"/>
+      <c r="BI8" s="98"/>
+      <c r="BJ8" s="98"/>
+      <c r="BK8" s="98"/>
+      <c r="BL8" s="98"/>
+      <c r="BM8" s="98"/>
+      <c r="BN8" s="98"/>
+      <c r="BO8" s="98"/>
+      <c r="BP8" s="98"/>
+      <c r="BQ8" s="98"/>
+      <c r="BR8" s="98"/>
+      <c r="BS8" s="98"/>
+      <c r="BT8" s="98"/>
+      <c r="BU8" s="98"/>
+      <c r="BV8" s="98"/>
+      <c r="BW8" s="98"/>
+      <c r="BX8" s="98"/>
+      <c r="BY8" s="98"/>
+      <c r="BZ8" s="98"/>
+      <c r="CA8" s="98"/>
+      <c r="CB8" s="98"/>
+      <c r="CC8" s="98"/>
+      <c r="CD8" s="98"/>
+      <c r="CE8" s="98"/>
+      <c r="CF8" s="98"/>
+      <c r="CG8" s="98"/>
+      <c r="CH8" s="98"/>
+      <c r="CI8" s="98"/>
+      <c r="CJ8" s="98"/>
+      <c r="CK8" s="98"/>
+      <c r="CL8" s="98"/>
+      <c r="CM8" s="98"/>
+      <c r="CN8" s="98"/>
+      <c r="CO8" s="98"/>
+      <c r="CP8" s="98"/>
+      <c r="CQ8" s="98"/>
+      <c r="CR8" s="98"/>
+      <c r="CS8" s="98"/>
+      <c r="CT8" s="98"/>
+      <c r="CU8" s="98"/>
+      <c r="CV8" s="98"/>
+      <c r="CW8" s="98"/>
+      <c r="CX8" s="98"/>
+      <c r="CY8" s="98"/>
+      <c r="CZ8" s="98"/>
+      <c r="DA8" s="98"/>
+      <c r="DB8" s="98"/>
+      <c r="DC8" s="98"/>
+      <c r="DD8" s="98"/>
+      <c r="DE8" s="98"/>
+      <c r="DF8" s="98"/>
+      <c r="DG8" s="98"/>
+      <c r="DH8" s="98"/>
+      <c r="DI8" s="98"/>
+      <c r="DJ8" s="98"/>
+      <c r="DK8" s="98"/>
+      <c r="DL8" s="98"/>
+      <c r="DM8" s="98"/>
+      <c r="DN8" s="98"/>
+      <c r="DO8" s="98"/>
+      <c r="DP8" s="98"/>
+      <c r="DQ8" s="98"/>
+      <c r="DR8" s="98"/>
+      <c r="DS8" s="98"/>
+      <c r="DT8" s="98"/>
+      <c r="DU8" s="98"/>
+      <c r="DV8" s="98"/>
+      <c r="DW8" s="98"/>
+      <c r="DX8" s="98"/>
+      <c r="DY8" s="98"/>
+      <c r="DZ8" s="98"/>
+      <c r="EA8" s="98"/>
+      <c r="EB8" s="98"/>
+      <c r="EC8" s="98"/>
+      <c r="ED8" s="98"/>
+      <c r="EE8" s="98"/>
+      <c r="EF8" s="98"/>
+      <c r="EG8" s="98"/>
+      <c r="EH8" s="98"/>
+      <c r="EI8" s="98"/>
+      <c r="EJ8" s="98"/>
+      <c r="EK8" s="98"/>
+      <c r="EL8" s="98"/>
+      <c r="EM8" s="98"/>
+      <c r="EN8" s="98"/>
+      <c r="EO8" s="98"/>
+      <c r="EP8" s="98"/>
+      <c r="EQ8" s="98"/>
+      <c r="ER8" s="98"/>
+      <c r="ES8" s="98"/>
+      <c r="ET8" s="98"/>
+      <c r="EU8" s="98"/>
+      <c r="EV8" s="98"/>
+      <c r="EW8" s="98"/>
+      <c r="EX8" s="98"/>
+      <c r="EY8" s="98"/>
+      <c r="EZ8" s="98"/>
+      <c r="FA8" s="98"/>
+      <c r="FB8" s="98"/>
+      <c r="FC8" s="98"/>
+      <c r="FD8" s="98"/>
+      <c r="FE8" s="98"/>
+      <c r="FF8" s="98"/>
+      <c r="FG8" s="98"/>
+      <c r="FH8" s="98"/>
+      <c r="FI8" s="98"/>
+      <c r="FJ8" s="98"/>
+      <c r="FK8" s="98"/>
+      <c r="FL8" s="98"/>
+      <c r="FM8" s="98"/>
+      <c r="FN8" s="98"/>
+      <c r="FO8" s="98"/>
+      <c r="FP8" s="98"/>
+      <c r="FQ8" s="98"/>
+      <c r="FR8" s="98"/>
+      <c r="FS8" s="98"/>
+      <c r="FT8" s="98"/>
+      <c r="FU8" s="98"/>
+      <c r="FV8" s="98"/>
+      <c r="FW8" s="98"/>
+      <c r="FX8" s="98"/>
+      <c r="FY8" s="98"/>
+      <c r="FZ8" s="98"/>
+      <c r="GA8" s="98"/>
+      <c r="GB8" s="98"/>
+      <c r="GC8" s="98"/>
+      <c r="GD8" s="98"/>
+      <c r="GE8" s="98"/>
+      <c r="GF8" s="98"/>
+      <c r="GG8" s="98"/>
+      <c r="GH8" s="98"/>
+      <c r="GI8" s="98"/>
+      <c r="GJ8" s="98"/>
+      <c r="GK8" s="98"/>
+      <c r="GL8" s="98"/>
+      <c r="GM8" s="98"/>
+      <c r="GN8" s="98"/>
+      <c r="GO8" s="98"/>
+      <c r="GP8" s="98"/>
+      <c r="GQ8" s="98"/>
+      <c r="GR8" s="98"/>
+      <c r="GS8" s="98"/>
+      <c r="GT8" s="98"/>
+      <c r="GU8" s="98"/>
+      <c r="GV8" s="98"/>
+      <c r="GW8" s="98"/>
+      <c r="GX8" s="98"/>
+      <c r="GY8" s="98"/>
+      <c r="GZ8" s="98"/>
+      <c r="HA8" s="98"/>
+      <c r="HB8" s="98"/>
+      <c r="HC8" s="98"/>
+      <c r="HD8" s="98"/>
+      <c r="HE8" s="98"/>
+      <c r="HF8" s="98"/>
+      <c r="HG8" s="98"/>
+      <c r="HH8" s="98"/>
+      <c r="HI8" s="98"/>
+      <c r="HJ8" s="98"/>
+      <c r="HK8" s="98"/>
+      <c r="HL8" s="98"/>
+      <c r="HM8" s="98"/>
+      <c r="HN8" s="98"/>
+      <c r="HO8" s="98"/>
+      <c r="HP8" s="98"/>
+      <c r="HQ8" s="98"/>
+      <c r="HR8" s="98"/>
+      <c r="HS8" s="98"/>
+      <c r="HT8" s="98"/>
+      <c r="HU8" s="98"/>
+      <c r="HV8" s="98"/>
+      <c r="HW8" s="98"/>
+      <c r="HX8" s="98"/>
+      <c r="HY8" s="98"/>
+      <c r="HZ8" s="98"/>
+      <c r="IA8" s="98"/>
+      <c r="IB8" s="98"/>
+      <c r="IC8" s="98"/>
+      <c r="ID8" s="98"/>
+      <c r="IE8" s="98"/>
+      <c r="IF8" s="98"/>
+      <c r="IG8" s="98"/>
+      <c r="IH8" s="98"/>
+      <c r="II8" s="98"/>
+      <c r="IJ8" s="98"/>
+      <c r="IK8" s="98"/>
+      <c r="IL8" s="98"/>
+      <c r="IM8" s="98"/>
+      <c r="IN8" s="98"/>
+      <c r="IO8" s="98"/>
+      <c r="IP8" s="98"/>
+      <c r="IQ8" s="98"/>
+      <c r="IR8" s="98"/>
+      <c r="IS8" s="98"/>
+      <c r="IT8" s="98"/>
+      <c r="IU8" s="98"/>
+      <c r="IV8" s="98"/>
+      <c r="IW8" s="98"/>
     </row>
     <row r="10" spans="1:257" ht="30" customHeight="1">
-      <c r="D10" s="133"/>
+      <c r="D10" s="119"/>
     </row>
     <row r="11" spans="1:257" ht="30" customHeight="1">
-      <c r="H11" s="134"/>
+      <c r="H11" s="120"/>
     </row>
     <row r="17" spans="5:9" ht="30" customHeight="1">
-      <c r="E17" s="135"/>
-      <c r="F17" s="135"/>
-      <c r="G17" s="135"/>
-      <c r="I17" s="136"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="I17" s="122"/>
     </row>
     <row r="18" spans="5:9" ht="30" customHeight="1">
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="135"/>
-      <c r="I18" s="136"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="121"/>
+      <c r="I18" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -35794,895 +35791,894 @@
   <dimension ref="A1:IW10"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" style="137" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" style="137" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="137" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="137" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" style="137" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" style="137" customWidth="1"/>
-    <col min="7" max="14" width="10.77734375" style="137" customWidth="1"/>
-    <col min="15" max="15" width="12.77734375" style="138" customWidth="1"/>
-    <col min="16" max="17" width="13.109375" style="137" customWidth="1"/>
-    <col min="18" max="257" width="8" style="137"/>
+    <col min="1" max="1" width="29.88671875" style="123" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" style="123" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="123" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="123" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="123" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" style="123" customWidth="1"/>
+    <col min="7" max="14" width="10.77734375" style="123" customWidth="1"/>
+    <col min="15" max="15" width="12.77734375" style="124" customWidth="1"/>
+    <col min="16" max="17" width="13.109375" style="123" customWidth="1"/>
+    <col min="18" max="257" width="8" style="123"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:257" ht="57" customHeight="1">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="159" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="125"/>
+      <c r="Q1" s="125"/>
+      <c r="R1" s="125"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
+      <c r="U1" s="125"/>
+      <c r="V1" s="125"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
+      <c r="Y1" s="125"/>
+      <c r="Z1" s="125"/>
+      <c r="AA1" s="125"/>
+      <c r="AB1" s="125"/>
+      <c r="AC1" s="125"/>
+      <c r="AD1" s="125"/>
+      <c r="AE1" s="125"/>
+      <c r="AF1" s="125"/>
+      <c r="AG1" s="125"/>
+      <c r="AH1" s="125"/>
+      <c r="AI1" s="125"/>
+      <c r="AJ1" s="125"/>
+      <c r="AK1" s="125"/>
+      <c r="AL1" s="125"/>
+      <c r="AM1" s="125"/>
+      <c r="AN1" s="125"/>
+      <c r="AO1" s="125"/>
+      <c r="AP1" s="125"/>
+      <c r="AQ1" s="125"/>
+      <c r="AR1" s="125"/>
+      <c r="AS1" s="125"/>
+      <c r="AT1" s="125"/>
+      <c r="AU1" s="125"/>
+      <c r="AV1" s="125"/>
+      <c r="AW1" s="125"/>
+      <c r="AX1" s="125"/>
+      <c r="AY1" s="125"/>
+      <c r="AZ1" s="125"/>
+      <c r="BA1" s="125"/>
+      <c r="BB1" s="125"/>
+      <c r="BC1" s="125"/>
+      <c r="BD1" s="125"/>
+      <c r="BE1" s="125"/>
+      <c r="BF1" s="125"/>
+      <c r="BG1" s="125"/>
+      <c r="BH1" s="125"/>
+      <c r="BI1" s="125"/>
+      <c r="BJ1" s="125"/>
+      <c r="BK1" s="125"/>
+      <c r="BL1" s="125"/>
+      <c r="BM1" s="125"/>
+      <c r="BN1" s="125"/>
+      <c r="BO1" s="125"/>
+      <c r="BP1" s="125"/>
+      <c r="BQ1" s="125"/>
+      <c r="BR1" s="125"/>
+      <c r="BS1" s="125"/>
+      <c r="BT1" s="125"/>
+      <c r="BU1" s="125"/>
+      <c r="BV1" s="125"/>
+      <c r="BW1" s="125"/>
+      <c r="BX1" s="125"/>
+      <c r="BY1" s="125"/>
+      <c r="BZ1" s="125"/>
+      <c r="CA1" s="125"/>
+      <c r="CB1" s="125"/>
+      <c r="CC1" s="125"/>
+      <c r="CD1" s="125"/>
+      <c r="CE1" s="125"/>
+      <c r="CF1" s="125"/>
+      <c r="CG1" s="125"/>
+      <c r="CH1" s="125"/>
+      <c r="CI1" s="125"/>
+      <c r="CJ1" s="125"/>
+      <c r="CK1" s="125"/>
+      <c r="CL1" s="125"/>
+      <c r="CM1" s="125"/>
+      <c r="CN1" s="125"/>
+      <c r="CO1" s="125"/>
+      <c r="CP1" s="125"/>
+      <c r="CQ1" s="125"/>
+      <c r="CR1" s="125"/>
+      <c r="CS1" s="125"/>
+      <c r="CT1" s="125"/>
+      <c r="CU1" s="125"/>
+      <c r="CV1" s="125"/>
+      <c r="CW1" s="125"/>
+      <c r="CX1" s="125"/>
+      <c r="CY1" s="125"/>
+      <c r="CZ1" s="125"/>
+      <c r="DA1" s="125"/>
+      <c r="DB1" s="125"/>
+      <c r="DC1" s="125"/>
+      <c r="DD1" s="125"/>
+      <c r="DE1" s="125"/>
+      <c r="DF1" s="125"/>
+      <c r="DG1" s="125"/>
+      <c r="DH1" s="125"/>
+      <c r="DI1" s="125"/>
+      <c r="DJ1" s="125"/>
+      <c r="DK1" s="125"/>
+      <c r="DL1" s="125"/>
+      <c r="DM1" s="125"/>
+      <c r="DN1" s="125"/>
+      <c r="DO1" s="125"/>
+      <c r="DP1" s="125"/>
+      <c r="DQ1" s="125"/>
+      <c r="DR1" s="125"/>
+      <c r="DS1" s="125"/>
+      <c r="DT1" s="125"/>
+      <c r="DU1" s="125"/>
+      <c r="DV1" s="125"/>
+      <c r="DW1" s="125"/>
+      <c r="DX1" s="125"/>
+      <c r="DY1" s="125"/>
+      <c r="DZ1" s="125"/>
+      <c r="EA1" s="125"/>
+      <c r="EB1" s="125"/>
+      <c r="EC1" s="125"/>
+      <c r="ED1" s="125"/>
+      <c r="EE1" s="125"/>
+      <c r="EF1" s="125"/>
+      <c r="EG1" s="125"/>
+      <c r="EH1" s="125"/>
+      <c r="EI1" s="125"/>
+      <c r="EJ1" s="125"/>
+      <c r="EK1" s="125"/>
+      <c r="EL1" s="125"/>
+      <c r="EM1" s="125"/>
+      <c r="EN1" s="125"/>
+      <c r="EO1" s="125"/>
+      <c r="EP1" s="125"/>
+      <c r="EQ1" s="125"/>
+      <c r="ER1" s="125"/>
+      <c r="ES1" s="125"/>
+      <c r="ET1" s="125"/>
+      <c r="EU1" s="125"/>
+      <c r="EV1" s="125"/>
+      <c r="EW1" s="125"/>
+      <c r="EX1" s="125"/>
+      <c r="EY1" s="125"/>
+      <c r="EZ1" s="125"/>
+      <c r="FA1" s="125"/>
+      <c r="FB1" s="125"/>
+      <c r="FC1" s="125"/>
+      <c r="FD1" s="125"/>
+      <c r="FE1" s="125"/>
+      <c r="FF1" s="125"/>
+      <c r="FG1" s="125"/>
+      <c r="FH1" s="125"/>
+      <c r="FI1" s="125"/>
+      <c r="FJ1" s="125"/>
+      <c r="FK1" s="125"/>
+      <c r="FL1" s="125"/>
+      <c r="FM1" s="125"/>
+      <c r="FN1" s="125"/>
+      <c r="FO1" s="125"/>
+      <c r="FP1" s="125"/>
+      <c r="FQ1" s="125"/>
+      <c r="FR1" s="125"/>
+      <c r="FS1" s="125"/>
+      <c r="FT1" s="125"/>
+      <c r="FU1" s="125"/>
+      <c r="FV1" s="125"/>
+      <c r="FW1" s="125"/>
+      <c r="FX1" s="125"/>
+      <c r="FY1" s="125"/>
+      <c r="FZ1" s="125"/>
+      <c r="GA1" s="125"/>
+      <c r="GB1" s="125"/>
+      <c r="GC1" s="125"/>
+      <c r="GD1" s="125"/>
+      <c r="GE1" s="125"/>
+      <c r="GF1" s="125"/>
+      <c r="GG1" s="125"/>
+      <c r="GH1" s="125"/>
+      <c r="GI1" s="125"/>
+      <c r="GJ1" s="125"/>
+      <c r="GK1" s="125"/>
+      <c r="GL1" s="125"/>
+      <c r="GM1" s="125"/>
+      <c r="GN1" s="125"/>
+      <c r="GO1" s="125"/>
+      <c r="GP1" s="125"/>
+      <c r="GQ1" s="125"/>
+      <c r="GR1" s="125"/>
+      <c r="GS1" s="125"/>
+      <c r="GT1" s="125"/>
+      <c r="GU1" s="125"/>
+      <c r="GV1" s="125"/>
+      <c r="GW1" s="125"/>
+      <c r="GX1" s="125"/>
+      <c r="GY1" s="125"/>
+      <c r="GZ1" s="125"/>
+      <c r="HA1" s="125"/>
+      <c r="HB1" s="125"/>
+      <c r="HC1" s="125"/>
+      <c r="HD1" s="125"/>
+      <c r="HE1" s="125"/>
+      <c r="HF1" s="125"/>
+      <c r="HG1" s="125"/>
+      <c r="HH1" s="125"/>
+      <c r="HI1" s="125"/>
+      <c r="HJ1" s="125"/>
+      <c r="HK1" s="125"/>
+      <c r="HL1" s="125"/>
+      <c r="HM1" s="125"/>
+      <c r="HN1" s="125"/>
+      <c r="HO1" s="125"/>
+      <c r="HP1" s="125"/>
+      <c r="HQ1" s="125"/>
+      <c r="HR1" s="125"/>
+      <c r="HS1" s="125"/>
+      <c r="HT1" s="125"/>
+      <c r="HU1" s="125"/>
+      <c r="HV1" s="125"/>
+      <c r="HW1" s="125"/>
+      <c r="HX1" s="125"/>
+      <c r="HY1" s="125"/>
+      <c r="HZ1" s="125"/>
+      <c r="IA1" s="125"/>
+      <c r="IB1" s="125"/>
+      <c r="IC1" s="125"/>
+      <c r="ID1" s="125"/>
+      <c r="IE1" s="125"/>
+      <c r="IF1" s="125"/>
+      <c r="IG1" s="125"/>
+      <c r="IH1" s="125"/>
+      <c r="II1" s="125"/>
+      <c r="IJ1" s="125"/>
+      <c r="IK1" s="125"/>
+      <c r="IL1" s="125"/>
+      <c r="IM1" s="125"/>
+      <c r="IN1" s="125"/>
+      <c r="IO1" s="125"/>
+      <c r="IP1" s="125"/>
+      <c r="IQ1" s="125"/>
+      <c r="IR1" s="125"/>
+      <c r="IS1" s="125"/>
+      <c r="IT1" s="125"/>
+      <c r="IU1" s="125"/>
+      <c r="IV1" s="125"/>
+      <c r="IW1" s="125"/>
+    </row>
+    <row r="2" spans="1:257" ht="39.950000000000003" customHeight="1">
+      <c r="A2" s="160" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
-      <c r="M1" s="157"/>
-      <c r="N1" s="157"/>
-      <c r="O1" s="157"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="139"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="139"/>
-      <c r="Z1" s="139"/>
-      <c r="AA1" s="139"/>
-      <c r="AB1" s="139"/>
-      <c r="AC1" s="139"/>
-      <c r="AD1" s="139"/>
-      <c r="AE1" s="139"/>
-      <c r="AF1" s="139"/>
-      <c r="AG1" s="139"/>
-      <c r="AH1" s="139"/>
-      <c r="AI1" s="139"/>
-      <c r="AJ1" s="139"/>
-      <c r="AK1" s="139"/>
-      <c r="AL1" s="139"/>
-      <c r="AM1" s="139"/>
-      <c r="AN1" s="139"/>
-      <c r="AO1" s="139"/>
-      <c r="AP1" s="139"/>
-      <c r="AQ1" s="139"/>
-      <c r="AR1" s="139"/>
-      <c r="AS1" s="139"/>
-      <c r="AT1" s="139"/>
-      <c r="AU1" s="139"/>
-      <c r="AV1" s="139"/>
-      <c r="AW1" s="139"/>
-      <c r="AX1" s="139"/>
-      <c r="AY1" s="139"/>
-      <c r="AZ1" s="139"/>
-      <c r="BA1" s="139"/>
-      <c r="BB1" s="139"/>
-      <c r="BC1" s="139"/>
-      <c r="BD1" s="139"/>
-      <c r="BE1" s="139"/>
-      <c r="BF1" s="139"/>
-      <c r="BG1" s="139"/>
-      <c r="BH1" s="139"/>
-      <c r="BI1" s="139"/>
-      <c r="BJ1" s="139"/>
-      <c r="BK1" s="139"/>
-      <c r="BL1" s="139"/>
-      <c r="BM1" s="139"/>
-      <c r="BN1" s="139"/>
-      <c r="BO1" s="139"/>
-      <c r="BP1" s="139"/>
-      <c r="BQ1" s="139"/>
-      <c r="BR1" s="139"/>
-      <c r="BS1" s="139"/>
-      <c r="BT1" s="139"/>
-      <c r="BU1" s="139"/>
-      <c r="BV1" s="139"/>
-      <c r="BW1" s="139"/>
-      <c r="BX1" s="139"/>
-      <c r="BY1" s="139"/>
-      <c r="BZ1" s="139"/>
-      <c r="CA1" s="139"/>
-      <c r="CB1" s="139"/>
-      <c r="CC1" s="139"/>
-      <c r="CD1" s="139"/>
-      <c r="CE1" s="139"/>
-      <c r="CF1" s="139"/>
-      <c r="CG1" s="139"/>
-      <c r="CH1" s="139"/>
-      <c r="CI1" s="139"/>
-      <c r="CJ1" s="139"/>
-      <c r="CK1" s="139"/>
-      <c r="CL1" s="139"/>
-      <c r="CM1" s="139"/>
-      <c r="CN1" s="139"/>
-      <c r="CO1" s="139"/>
-      <c r="CP1" s="139"/>
-      <c r="CQ1" s="139"/>
-      <c r="CR1" s="139"/>
-      <c r="CS1" s="139"/>
-      <c r="CT1" s="139"/>
-      <c r="CU1" s="139"/>
-      <c r="CV1" s="139"/>
-      <c r="CW1" s="139"/>
-      <c r="CX1" s="139"/>
-      <c r="CY1" s="139"/>
-      <c r="CZ1" s="139"/>
-      <c r="DA1" s="139"/>
-      <c r="DB1" s="139"/>
-      <c r="DC1" s="139"/>
-      <c r="DD1" s="139"/>
-      <c r="DE1" s="139"/>
-      <c r="DF1" s="139"/>
-      <c r="DG1" s="139"/>
-      <c r="DH1" s="139"/>
-      <c r="DI1" s="139"/>
-      <c r="DJ1" s="139"/>
-      <c r="DK1" s="139"/>
-      <c r="DL1" s="139"/>
-      <c r="DM1" s="139"/>
-      <c r="DN1" s="139"/>
-      <c r="DO1" s="139"/>
-      <c r="DP1" s="139"/>
-      <c r="DQ1" s="139"/>
-      <c r="DR1" s="139"/>
-      <c r="DS1" s="139"/>
-      <c r="DT1" s="139"/>
-      <c r="DU1" s="139"/>
-      <c r="DV1" s="139"/>
-      <c r="DW1" s="139"/>
-      <c r="DX1" s="139"/>
-      <c r="DY1" s="139"/>
-      <c r="DZ1" s="139"/>
-      <c r="EA1" s="139"/>
-      <c r="EB1" s="139"/>
-      <c r="EC1" s="139"/>
-      <c r="ED1" s="139"/>
-      <c r="EE1" s="139"/>
-      <c r="EF1" s="139"/>
-      <c r="EG1" s="139"/>
-      <c r="EH1" s="139"/>
-      <c r="EI1" s="139"/>
-      <c r="EJ1" s="139"/>
-      <c r="EK1" s="139"/>
-      <c r="EL1" s="139"/>
-      <c r="EM1" s="139"/>
-      <c r="EN1" s="139"/>
-      <c r="EO1" s="139"/>
-      <c r="EP1" s="139"/>
-      <c r="EQ1" s="139"/>
-      <c r="ER1" s="139"/>
-      <c r="ES1" s="139"/>
-      <c r="ET1" s="139"/>
-      <c r="EU1" s="139"/>
-      <c r="EV1" s="139"/>
-      <c r="EW1" s="139"/>
-      <c r="EX1" s="139"/>
-      <c r="EY1" s="139"/>
-      <c r="EZ1" s="139"/>
-      <c r="FA1" s="139"/>
-      <c r="FB1" s="139"/>
-      <c r="FC1" s="139"/>
-      <c r="FD1" s="139"/>
-      <c r="FE1" s="139"/>
-      <c r="FF1" s="139"/>
-      <c r="FG1" s="139"/>
-      <c r="FH1" s="139"/>
-      <c r="FI1" s="139"/>
-      <c r="FJ1" s="139"/>
-      <c r="FK1" s="139"/>
-      <c r="FL1" s="139"/>
-      <c r="FM1" s="139"/>
-      <c r="FN1" s="139"/>
-      <c r="FO1" s="139"/>
-      <c r="FP1" s="139"/>
-      <c r="FQ1" s="139"/>
-      <c r="FR1" s="139"/>
-      <c r="FS1" s="139"/>
-      <c r="FT1" s="139"/>
-      <c r="FU1" s="139"/>
-      <c r="FV1" s="139"/>
-      <c r="FW1" s="139"/>
-      <c r="FX1" s="139"/>
-      <c r="FY1" s="139"/>
-      <c r="FZ1" s="139"/>
-      <c r="GA1" s="139"/>
-      <c r="GB1" s="139"/>
-      <c r="GC1" s="139"/>
-      <c r="GD1" s="139"/>
-      <c r="GE1" s="139"/>
-      <c r="GF1" s="139"/>
-      <c r="GG1" s="139"/>
-      <c r="GH1" s="139"/>
-      <c r="GI1" s="139"/>
-      <c r="GJ1" s="139"/>
-      <c r="GK1" s="139"/>
-      <c r="GL1" s="139"/>
-      <c r="GM1" s="139"/>
-      <c r="GN1" s="139"/>
-      <c r="GO1" s="139"/>
-      <c r="GP1" s="139"/>
-      <c r="GQ1" s="139"/>
-      <c r="GR1" s="139"/>
-      <c r="GS1" s="139"/>
-      <c r="GT1" s="139"/>
-      <c r="GU1" s="139"/>
-      <c r="GV1" s="139"/>
-      <c r="GW1" s="139"/>
-      <c r="GX1" s="139"/>
-      <c r="GY1" s="139"/>
-      <c r="GZ1" s="139"/>
-      <c r="HA1" s="139"/>
-      <c r="HB1" s="139"/>
-      <c r="HC1" s="139"/>
-      <c r="HD1" s="139"/>
-      <c r="HE1" s="139"/>
-      <c r="HF1" s="139"/>
-      <c r="HG1" s="139"/>
-      <c r="HH1" s="139"/>
-      <c r="HI1" s="139"/>
-      <c r="HJ1" s="139"/>
-      <c r="HK1" s="139"/>
-      <c r="HL1" s="139"/>
-      <c r="HM1" s="139"/>
-      <c r="HN1" s="139"/>
-      <c r="HO1" s="139"/>
-      <c r="HP1" s="139"/>
-      <c r="HQ1" s="139"/>
-      <c r="HR1" s="139"/>
-      <c r="HS1" s="139"/>
-      <c r="HT1" s="139"/>
-      <c r="HU1" s="139"/>
-      <c r="HV1" s="139"/>
-      <c r="HW1" s="139"/>
-      <c r="HX1" s="139"/>
-      <c r="HY1" s="139"/>
-      <c r="HZ1" s="139"/>
-      <c r="IA1" s="139"/>
-      <c r="IB1" s="139"/>
-      <c r="IC1" s="139"/>
-      <c r="ID1" s="139"/>
-      <c r="IE1" s="139"/>
-      <c r="IF1" s="139"/>
-      <c r="IG1" s="139"/>
-      <c r="IH1" s="139"/>
-      <c r="II1" s="139"/>
-      <c r="IJ1" s="139"/>
-      <c r="IK1" s="139"/>
-      <c r="IL1" s="139"/>
-      <c r="IM1" s="139"/>
-      <c r="IN1" s="139"/>
-      <c r="IO1" s="139"/>
-      <c r="IP1" s="139"/>
-      <c r="IQ1" s="139"/>
-      <c r="IR1" s="139"/>
-      <c r="IS1" s="139"/>
-      <c r="IT1" s="139"/>
-      <c r="IU1" s="139"/>
-      <c r="IV1" s="139"/>
-      <c r="IW1" s="139"/>
-    </row>
-    <row r="2" spans="1:257" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="158" t="s">
+      <c r="B2" s="160" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="158" t="s">
+      <c r="C2" s="160"/>
+      <c r="D2" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="158"/>
-      <c r="D2" s="159" t="s">
+      <c r="E2" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="159" t="s">
+      <c r="F2" s="160" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="158" t="s">
+      <c r="G2" s="162" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="162"/>
+      <c r="I2" s="163" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="160" t="s">
-        <v>54</v>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163" t="s">
+        <v>11</v>
       </c>
-      <c r="H2" s="160"/>
-      <c r="I2" s="161" t="s">
+      <c r="L2" s="163"/>
+      <c r="M2" s="163" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161" t="s">
-        <v>11</v>
+      <c r="N2" s="163"/>
+      <c r="O2" s="160" t="s">
+        <v>27</v>
       </c>
-      <c r="L2" s="161"/>
-      <c r="M2" s="161" t="s">
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="125"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="125"/>
+      <c r="V2" s="125"/>
+      <c r="W2" s="125"/>
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="125"/>
+      <c r="AC2" s="125"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="125"/>
+      <c r="AQ2" s="125"/>
+      <c r="AR2" s="125"/>
+      <c r="AS2" s="125"/>
+      <c r="AT2" s="125"/>
+      <c r="AU2" s="125"/>
+      <c r="AV2" s="125"/>
+      <c r="AW2" s="125"/>
+      <c r="AX2" s="125"/>
+      <c r="AY2" s="125"/>
+      <c r="AZ2" s="125"/>
+      <c r="BA2" s="125"/>
+      <c r="BB2" s="125"/>
+      <c r="BC2" s="125"/>
+      <c r="BD2" s="125"/>
+      <c r="BE2" s="125"/>
+      <c r="BF2" s="125"/>
+      <c r="BG2" s="125"/>
+      <c r="BH2" s="125"/>
+      <c r="BI2" s="125"/>
+      <c r="BJ2" s="125"/>
+      <c r="BK2" s="125"/>
+      <c r="BL2" s="125"/>
+      <c r="BM2" s="125"/>
+      <c r="BN2" s="125"/>
+      <c r="BO2" s="125"/>
+      <c r="BP2" s="125"/>
+      <c r="BQ2" s="125"/>
+      <c r="BR2" s="125"/>
+      <c r="BS2" s="125"/>
+      <c r="BT2" s="125"/>
+      <c r="BU2" s="125"/>
+      <c r="BV2" s="125"/>
+      <c r="BW2" s="125"/>
+      <c r="BX2" s="125"/>
+      <c r="BY2" s="125"/>
+      <c r="BZ2" s="125"/>
+      <c r="CA2" s="125"/>
+      <c r="CB2" s="125"/>
+      <c r="CC2" s="125"/>
+      <c r="CD2" s="125"/>
+      <c r="CE2" s="125"/>
+      <c r="CF2" s="125"/>
+      <c r="CG2" s="125"/>
+      <c r="CH2" s="125"/>
+      <c r="CI2" s="125"/>
+      <c r="CJ2" s="125"/>
+      <c r="CK2" s="125"/>
+      <c r="CL2" s="125"/>
+      <c r="CM2" s="125"/>
+      <c r="CN2" s="125"/>
+      <c r="CO2" s="125"/>
+      <c r="CP2" s="125"/>
+      <c r="CQ2" s="125"/>
+      <c r="CR2" s="125"/>
+      <c r="CS2" s="125"/>
+      <c r="CT2" s="125"/>
+      <c r="CU2" s="125"/>
+      <c r="CV2" s="125"/>
+      <c r="CW2" s="125"/>
+      <c r="CX2" s="125"/>
+      <c r="CY2" s="125"/>
+      <c r="CZ2" s="125"/>
+      <c r="DA2" s="125"/>
+      <c r="DB2" s="125"/>
+      <c r="DC2" s="125"/>
+      <c r="DD2" s="125"/>
+      <c r="DE2" s="125"/>
+      <c r="DF2" s="125"/>
+      <c r="DG2" s="125"/>
+      <c r="DH2" s="125"/>
+      <c r="DI2" s="125"/>
+      <c r="DJ2" s="125"/>
+      <c r="DK2" s="125"/>
+      <c r="DL2" s="125"/>
+      <c r="DM2" s="125"/>
+      <c r="DN2" s="125"/>
+      <c r="DO2" s="125"/>
+      <c r="DP2" s="125"/>
+      <c r="DQ2" s="125"/>
+      <c r="DR2" s="125"/>
+      <c r="DS2" s="125"/>
+      <c r="DT2" s="125"/>
+      <c r="DU2" s="125"/>
+      <c r="DV2" s="125"/>
+      <c r="DW2" s="125"/>
+      <c r="DX2" s="125"/>
+      <c r="DY2" s="125"/>
+      <c r="DZ2" s="125"/>
+      <c r="EA2" s="125"/>
+      <c r="EB2" s="125"/>
+      <c r="EC2" s="125"/>
+      <c r="ED2" s="125"/>
+      <c r="EE2" s="125"/>
+      <c r="EF2" s="125"/>
+      <c r="EG2" s="125"/>
+      <c r="EH2" s="125"/>
+      <c r="EI2" s="125"/>
+      <c r="EJ2" s="125"/>
+      <c r="EK2" s="125"/>
+      <c r="EL2" s="125"/>
+      <c r="EM2" s="125"/>
+      <c r="EN2" s="125"/>
+      <c r="EO2" s="125"/>
+      <c r="EP2" s="125"/>
+      <c r="EQ2" s="125"/>
+      <c r="ER2" s="125"/>
+      <c r="ES2" s="125"/>
+      <c r="ET2" s="125"/>
+      <c r="EU2" s="125"/>
+      <c r="EV2" s="125"/>
+      <c r="EW2" s="125"/>
+      <c r="EX2" s="125"/>
+      <c r="EY2" s="125"/>
+      <c r="EZ2" s="125"/>
+      <c r="FA2" s="125"/>
+      <c r="FB2" s="125"/>
+      <c r="FC2" s="125"/>
+      <c r="FD2" s="125"/>
+      <c r="FE2" s="125"/>
+      <c r="FF2" s="125"/>
+      <c r="FG2" s="125"/>
+      <c r="FH2" s="125"/>
+      <c r="FI2" s="125"/>
+      <c r="FJ2" s="125"/>
+      <c r="FK2" s="125"/>
+      <c r="FL2" s="125"/>
+      <c r="FM2" s="125"/>
+      <c r="FN2" s="125"/>
+      <c r="FO2" s="125"/>
+      <c r="FP2" s="125"/>
+      <c r="FQ2" s="125"/>
+      <c r="FR2" s="125"/>
+      <c r="FS2" s="125"/>
+      <c r="FT2" s="125"/>
+      <c r="FU2" s="125"/>
+      <c r="FV2" s="125"/>
+      <c r="FW2" s="125"/>
+      <c r="FX2" s="125"/>
+      <c r="FY2" s="125"/>
+      <c r="FZ2" s="125"/>
+      <c r="GA2" s="125"/>
+      <c r="GB2" s="125"/>
+      <c r="GC2" s="125"/>
+      <c r="GD2" s="125"/>
+      <c r="GE2" s="125"/>
+      <c r="GF2" s="125"/>
+      <c r="GG2" s="125"/>
+      <c r="GH2" s="125"/>
+      <c r="GI2" s="125"/>
+      <c r="GJ2" s="125"/>
+      <c r="GK2" s="125"/>
+      <c r="GL2" s="125"/>
+      <c r="GM2" s="125"/>
+      <c r="GN2" s="125"/>
+      <c r="GO2" s="125"/>
+      <c r="GP2" s="125"/>
+      <c r="GQ2" s="125"/>
+      <c r="GR2" s="125"/>
+      <c r="GS2" s="125"/>
+      <c r="GT2" s="125"/>
+      <c r="GU2" s="125"/>
+      <c r="GV2" s="125"/>
+      <c r="GW2" s="125"/>
+      <c r="GX2" s="125"/>
+      <c r="GY2" s="125"/>
+      <c r="GZ2" s="125"/>
+      <c r="HA2" s="125"/>
+      <c r="HB2" s="125"/>
+      <c r="HC2" s="125"/>
+      <c r="HD2" s="125"/>
+      <c r="HE2" s="125"/>
+      <c r="HF2" s="125"/>
+      <c r="HG2" s="125"/>
+      <c r="HH2" s="125"/>
+      <c r="HI2" s="125"/>
+      <c r="HJ2" s="125"/>
+      <c r="HK2" s="125"/>
+      <c r="HL2" s="125"/>
+      <c r="HM2" s="125"/>
+      <c r="HN2" s="125"/>
+      <c r="HO2" s="125"/>
+      <c r="HP2" s="125"/>
+      <c r="HQ2" s="125"/>
+      <c r="HR2" s="125"/>
+      <c r="HS2" s="125"/>
+      <c r="HT2" s="125"/>
+      <c r="HU2" s="125"/>
+      <c r="HV2" s="125"/>
+      <c r="HW2" s="125"/>
+      <c r="HX2" s="125"/>
+      <c r="HY2" s="125"/>
+      <c r="HZ2" s="125"/>
+      <c r="IA2" s="125"/>
+      <c r="IB2" s="125"/>
+      <c r="IC2" s="125"/>
+      <c r="ID2" s="125"/>
+      <c r="IE2" s="125"/>
+      <c r="IF2" s="125"/>
+      <c r="IG2" s="125"/>
+      <c r="IH2" s="125"/>
+      <c r="II2" s="125"/>
+      <c r="IJ2" s="125"/>
+      <c r="IK2" s="125"/>
+      <c r="IL2" s="125"/>
+      <c r="IM2" s="125"/>
+      <c r="IN2" s="125"/>
+      <c r="IO2" s="125"/>
+      <c r="IP2" s="125"/>
+      <c r="IQ2" s="125"/>
+      <c r="IR2" s="125"/>
+      <c r="IS2" s="125"/>
+      <c r="IT2" s="125"/>
+      <c r="IU2" s="125"/>
+      <c r="IV2" s="125"/>
+      <c r="IW2" s="125"/>
+    </row>
+    <row r="3" spans="1:257" ht="39.950000000000003" customHeight="1">
+      <c r="A3" s="160"/>
+      <c r="B3" s="160"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="N2" s="161"/>
-      <c r="O2" s="158" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="139"/>
-      <c r="Q2" s="139"/>
-      <c r="R2" s="139"/>
-      <c r="S2" s="139"/>
-      <c r="T2" s="139"/>
-      <c r="U2" s="139"/>
-      <c r="V2" s="139"/>
-      <c r="W2" s="139"/>
-      <c r="X2" s="139"/>
-      <c r="Y2" s="139"/>
-      <c r="Z2" s="139"/>
-      <c r="AA2" s="139"/>
-      <c r="AB2" s="139"/>
-      <c r="AC2" s="139"/>
-      <c r="AD2" s="139"/>
-      <c r="AE2" s="139"/>
-      <c r="AF2" s="139"/>
-      <c r="AG2" s="139"/>
-      <c r="AH2" s="139"/>
-      <c r="AI2" s="139"/>
-      <c r="AJ2" s="139"/>
-      <c r="AK2" s="139"/>
-      <c r="AL2" s="139"/>
-      <c r="AM2" s="139"/>
-      <c r="AN2" s="139"/>
-      <c r="AO2" s="139"/>
-      <c r="AP2" s="139"/>
-      <c r="AQ2" s="139"/>
-      <c r="AR2" s="139"/>
-      <c r="AS2" s="139"/>
-      <c r="AT2" s="139"/>
-      <c r="AU2" s="139"/>
-      <c r="AV2" s="139"/>
-      <c r="AW2" s="139"/>
-      <c r="AX2" s="139"/>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
-      <c r="BB2" s="139"/>
-      <c r="BC2" s="139"/>
-      <c r="BD2" s="139"/>
-      <c r="BE2" s="139"/>
-      <c r="BF2" s="139"/>
-      <c r="BG2" s="139"/>
-      <c r="BH2" s="139"/>
-      <c r="BI2" s="139"/>
-      <c r="BJ2" s="139"/>
-      <c r="BK2" s="139"/>
-      <c r="BL2" s="139"/>
-      <c r="BM2" s="139"/>
-      <c r="BN2" s="139"/>
-      <c r="BO2" s="139"/>
-      <c r="BP2" s="139"/>
-      <c r="BQ2" s="139"/>
-      <c r="BR2" s="139"/>
-      <c r="BS2" s="139"/>
-      <c r="BT2" s="139"/>
-      <c r="BU2" s="139"/>
-      <c r="BV2" s="139"/>
-      <c r="BW2" s="139"/>
-      <c r="BX2" s="139"/>
-      <c r="BY2" s="139"/>
-      <c r="BZ2" s="139"/>
-      <c r="CA2" s="139"/>
-      <c r="CB2" s="139"/>
-      <c r="CC2" s="139"/>
-      <c r="CD2" s="139"/>
-      <c r="CE2" s="139"/>
-      <c r="CF2" s="139"/>
-      <c r="CG2" s="139"/>
-      <c r="CH2" s="139"/>
-      <c r="CI2" s="139"/>
-      <c r="CJ2" s="139"/>
-      <c r="CK2" s="139"/>
-      <c r="CL2" s="139"/>
-      <c r="CM2" s="139"/>
-      <c r="CN2" s="139"/>
-      <c r="CO2" s="139"/>
-      <c r="CP2" s="139"/>
-      <c r="CQ2" s="139"/>
-      <c r="CR2" s="139"/>
-      <c r="CS2" s="139"/>
-      <c r="CT2" s="139"/>
-      <c r="CU2" s="139"/>
-      <c r="CV2" s="139"/>
-      <c r="CW2" s="139"/>
-      <c r="CX2" s="139"/>
-      <c r="CY2" s="139"/>
-      <c r="CZ2" s="139"/>
-      <c r="DA2" s="139"/>
-      <c r="DB2" s="139"/>
-      <c r="DC2" s="139"/>
-      <c r="DD2" s="139"/>
-      <c r="DE2" s="139"/>
-      <c r="DF2" s="139"/>
-      <c r="DG2" s="139"/>
-      <c r="DH2" s="139"/>
-      <c r="DI2" s="139"/>
-      <c r="DJ2" s="139"/>
-      <c r="DK2" s="139"/>
-      <c r="DL2" s="139"/>
-      <c r="DM2" s="139"/>
-      <c r="DN2" s="139"/>
-      <c r="DO2" s="139"/>
-      <c r="DP2" s="139"/>
-      <c r="DQ2" s="139"/>
-      <c r="DR2" s="139"/>
-      <c r="DS2" s="139"/>
-      <c r="DT2" s="139"/>
-      <c r="DU2" s="139"/>
-      <c r="DV2" s="139"/>
-      <c r="DW2" s="139"/>
-      <c r="DX2" s="139"/>
-      <c r="DY2" s="139"/>
-      <c r="DZ2" s="139"/>
-      <c r="EA2" s="139"/>
-      <c r="EB2" s="139"/>
-      <c r="EC2" s="139"/>
-      <c r="ED2" s="139"/>
-      <c r="EE2" s="139"/>
-      <c r="EF2" s="139"/>
-      <c r="EG2" s="139"/>
-      <c r="EH2" s="139"/>
-      <c r="EI2" s="139"/>
-      <c r="EJ2" s="139"/>
-      <c r="EK2" s="139"/>
-      <c r="EL2" s="139"/>
-      <c r="EM2" s="139"/>
-      <c r="EN2" s="139"/>
-      <c r="EO2" s="139"/>
-      <c r="EP2" s="139"/>
-      <c r="EQ2" s="139"/>
-      <c r="ER2" s="139"/>
-      <c r="ES2" s="139"/>
-      <c r="ET2" s="139"/>
-      <c r="EU2" s="139"/>
-      <c r="EV2" s="139"/>
-      <c r="EW2" s="139"/>
-      <c r="EX2" s="139"/>
-      <c r="EY2" s="139"/>
-      <c r="EZ2" s="139"/>
-      <c r="FA2" s="139"/>
-      <c r="FB2" s="139"/>
-      <c r="FC2" s="139"/>
-      <c r="FD2" s="139"/>
-      <c r="FE2" s="139"/>
-      <c r="FF2" s="139"/>
-      <c r="FG2" s="139"/>
-      <c r="FH2" s="139"/>
-      <c r="FI2" s="139"/>
-      <c r="FJ2" s="139"/>
-      <c r="FK2" s="139"/>
-      <c r="FL2" s="139"/>
-      <c r="FM2" s="139"/>
-      <c r="FN2" s="139"/>
-      <c r="FO2" s="139"/>
-      <c r="FP2" s="139"/>
-      <c r="FQ2" s="139"/>
-      <c r="FR2" s="139"/>
-      <c r="FS2" s="139"/>
-      <c r="FT2" s="139"/>
-      <c r="FU2" s="139"/>
-      <c r="FV2" s="139"/>
-      <c r="FW2" s="139"/>
-      <c r="FX2" s="139"/>
-      <c r="FY2" s="139"/>
-      <c r="FZ2" s="139"/>
-      <c r="GA2" s="139"/>
-      <c r="GB2" s="139"/>
-      <c r="GC2" s="139"/>
-      <c r="GD2" s="139"/>
-      <c r="GE2" s="139"/>
-      <c r="GF2" s="139"/>
-      <c r="GG2" s="139"/>
-      <c r="GH2" s="139"/>
-      <c r="GI2" s="139"/>
-      <c r="GJ2" s="139"/>
-      <c r="GK2" s="139"/>
-      <c r="GL2" s="139"/>
-      <c r="GM2" s="139"/>
-      <c r="GN2" s="139"/>
-      <c r="GO2" s="139"/>
-      <c r="GP2" s="139"/>
-      <c r="GQ2" s="139"/>
-      <c r="GR2" s="139"/>
-      <c r="GS2" s="139"/>
-      <c r="GT2" s="139"/>
-      <c r="GU2" s="139"/>
-      <c r="GV2" s="139"/>
-      <c r="GW2" s="139"/>
-      <c r="GX2" s="139"/>
-      <c r="GY2" s="139"/>
-      <c r="GZ2" s="139"/>
-      <c r="HA2" s="139"/>
-      <c r="HB2" s="139"/>
-      <c r="HC2" s="139"/>
-      <c r="HD2" s="139"/>
-      <c r="HE2" s="139"/>
-      <c r="HF2" s="139"/>
-      <c r="HG2" s="139"/>
-      <c r="HH2" s="139"/>
-      <c r="HI2" s="139"/>
-      <c r="HJ2" s="139"/>
-      <c r="HK2" s="139"/>
-      <c r="HL2" s="139"/>
-      <c r="HM2" s="139"/>
-      <c r="HN2" s="139"/>
-      <c r="HO2" s="139"/>
-      <c r="HP2" s="139"/>
-      <c r="HQ2" s="139"/>
-      <c r="HR2" s="139"/>
-      <c r="HS2" s="139"/>
-      <c r="HT2" s="139"/>
-      <c r="HU2" s="139"/>
-      <c r="HV2" s="139"/>
-      <c r="HW2" s="139"/>
-      <c r="HX2" s="139"/>
-      <c r="HY2" s="139"/>
-      <c r="HZ2" s="139"/>
-      <c r="IA2" s="139"/>
-      <c r="IB2" s="139"/>
-      <c r="IC2" s="139"/>
-      <c r="ID2" s="139"/>
-      <c r="IE2" s="139"/>
-      <c r="IF2" s="139"/>
-      <c r="IG2" s="139"/>
-      <c r="IH2" s="139"/>
-      <c r="II2" s="139"/>
-      <c r="IJ2" s="139"/>
-      <c r="IK2" s="139"/>
-      <c r="IL2" s="139"/>
-      <c r="IM2" s="139"/>
-      <c r="IN2" s="139"/>
-      <c r="IO2" s="139"/>
-      <c r="IP2" s="139"/>
-      <c r="IQ2" s="139"/>
-      <c r="IR2" s="139"/>
-      <c r="IS2" s="139"/>
-      <c r="IT2" s="139"/>
-      <c r="IU2" s="139"/>
-      <c r="IV2" s="139"/>
-      <c r="IW2" s="139"/>
-    </row>
-    <row r="3" spans="1:257" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="158"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="141" t="s">
+      <c r="H3" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="140" t="s">
+      <c r="I3" s="127" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="126" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="127" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="126" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="163"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="125"/>
+      <c r="W3" s="125"/>
+      <c r="X3" s="125"/>
+      <c r="Y3" s="125"/>
+      <c r="Z3" s="125"/>
+      <c r="AA3" s="125"/>
+      <c r="AB3" s="125"/>
+      <c r="AC3" s="125"/>
+      <c r="AD3" s="125"/>
+      <c r="AE3" s="125"/>
+      <c r="AF3" s="125"/>
+      <c r="AG3" s="125"/>
+      <c r="AH3" s="125"/>
+      <c r="AI3" s="125"/>
+      <c r="AJ3" s="125"/>
+      <c r="AK3" s="125"/>
+      <c r="AL3" s="125"/>
+      <c r="AM3" s="125"/>
+      <c r="AN3" s="125"/>
+      <c r="AO3" s="125"/>
+      <c r="AP3" s="125"/>
+      <c r="AQ3" s="125"/>
+      <c r="AR3" s="125"/>
+      <c r="AS3" s="125"/>
+      <c r="AT3" s="125"/>
+      <c r="AU3" s="125"/>
+      <c r="AV3" s="125"/>
+      <c r="AW3" s="125"/>
+      <c r="AX3" s="125"/>
+      <c r="AY3" s="125"/>
+      <c r="AZ3" s="125"/>
+      <c r="BA3" s="125"/>
+      <c r="BB3" s="125"/>
+      <c r="BC3" s="125"/>
+      <c r="BD3" s="125"/>
+      <c r="BE3" s="125"/>
+      <c r="BF3" s="125"/>
+      <c r="BG3" s="125"/>
+      <c r="BH3" s="125"/>
+      <c r="BI3" s="125"/>
+      <c r="BJ3" s="125"/>
+      <c r="BK3" s="125"/>
+      <c r="BL3" s="125"/>
+      <c r="BM3" s="125"/>
+      <c r="BN3" s="125"/>
+      <c r="BO3" s="125"/>
+      <c r="BP3" s="125"/>
+      <c r="BQ3" s="125"/>
+      <c r="BR3" s="125"/>
+      <c r="BS3" s="125"/>
+      <c r="BT3" s="125"/>
+      <c r="BU3" s="125"/>
+      <c r="BV3" s="125"/>
+      <c r="BW3" s="125"/>
+      <c r="BX3" s="125"/>
+      <c r="BY3" s="125"/>
+      <c r="BZ3" s="125"/>
+      <c r="CA3" s="125"/>
+      <c r="CB3" s="125"/>
+      <c r="CC3" s="125"/>
+      <c r="CD3" s="125"/>
+      <c r="CE3" s="125"/>
+      <c r="CF3" s="125"/>
+      <c r="CG3" s="125"/>
+      <c r="CH3" s="125"/>
+      <c r="CI3" s="125"/>
+      <c r="CJ3" s="125"/>
+      <c r="CK3" s="125"/>
+      <c r="CL3" s="125"/>
+      <c r="CM3" s="125"/>
+      <c r="CN3" s="125"/>
+      <c r="CO3" s="125"/>
+      <c r="CP3" s="125"/>
+      <c r="CQ3" s="125"/>
+      <c r="CR3" s="125"/>
+      <c r="CS3" s="125"/>
+      <c r="CT3" s="125"/>
+      <c r="CU3" s="125"/>
+      <c r="CV3" s="125"/>
+      <c r="CW3" s="125"/>
+      <c r="CX3" s="125"/>
+      <c r="CY3" s="125"/>
+      <c r="CZ3" s="125"/>
+      <c r="DA3" s="125"/>
+      <c r="DB3" s="125"/>
+      <c r="DC3" s="125"/>
+      <c r="DD3" s="125"/>
+      <c r="DE3" s="125"/>
+      <c r="DF3" s="125"/>
+      <c r="DG3" s="125"/>
+      <c r="DH3" s="125"/>
+      <c r="DI3" s="125"/>
+      <c r="DJ3" s="125"/>
+      <c r="DK3" s="125"/>
+      <c r="DL3" s="125"/>
+      <c r="DM3" s="125"/>
+      <c r="DN3" s="125"/>
+      <c r="DO3" s="125"/>
+      <c r="DP3" s="125"/>
+      <c r="DQ3" s="125"/>
+      <c r="DR3" s="125"/>
+      <c r="DS3" s="125"/>
+      <c r="DT3" s="125"/>
+      <c r="DU3" s="125"/>
+      <c r="DV3" s="125"/>
+      <c r="DW3" s="125"/>
+      <c r="DX3" s="125"/>
+      <c r="DY3" s="125"/>
+      <c r="DZ3" s="125"/>
+      <c r="EA3" s="125"/>
+      <c r="EB3" s="125"/>
+      <c r="EC3" s="125"/>
+      <c r="ED3" s="125"/>
+      <c r="EE3" s="125"/>
+      <c r="EF3" s="125"/>
+      <c r="EG3" s="125"/>
+      <c r="EH3" s="125"/>
+      <c r="EI3" s="125"/>
+      <c r="EJ3" s="125"/>
+      <c r="EK3" s="125"/>
+      <c r="EL3" s="125"/>
+      <c r="EM3" s="125"/>
+      <c r="EN3" s="125"/>
+      <c r="EO3" s="125"/>
+      <c r="EP3" s="125"/>
+      <c r="EQ3" s="125"/>
+      <c r="ER3" s="125"/>
+      <c r="ES3" s="125"/>
+      <c r="ET3" s="125"/>
+      <c r="EU3" s="125"/>
+      <c r="EV3" s="125"/>
+      <c r="EW3" s="125"/>
+      <c r="EX3" s="125"/>
+      <c r="EY3" s="125"/>
+      <c r="EZ3" s="125"/>
+      <c r="FA3" s="125"/>
+      <c r="FB3" s="125"/>
+      <c r="FC3" s="125"/>
+      <c r="FD3" s="125"/>
+      <c r="FE3" s="125"/>
+      <c r="FF3" s="125"/>
+      <c r="FG3" s="125"/>
+      <c r="FH3" s="125"/>
+      <c r="FI3" s="125"/>
+      <c r="FJ3" s="125"/>
+      <c r="FK3" s="125"/>
+      <c r="FL3" s="125"/>
+      <c r="FM3" s="125"/>
+      <c r="FN3" s="125"/>
+      <c r="FO3" s="125"/>
+      <c r="FP3" s="125"/>
+      <c r="FQ3" s="125"/>
+      <c r="FR3" s="125"/>
+      <c r="FS3" s="125"/>
+      <c r="FT3" s="125"/>
+      <c r="FU3" s="125"/>
+      <c r="FV3" s="125"/>
+      <c r="FW3" s="125"/>
+      <c r="FX3" s="125"/>
+      <c r="FY3" s="125"/>
+      <c r="FZ3" s="125"/>
+      <c r="GA3" s="125"/>
+      <c r="GB3" s="125"/>
+      <c r="GC3" s="125"/>
+      <c r="GD3" s="125"/>
+      <c r="GE3" s="125"/>
+      <c r="GF3" s="125"/>
+      <c r="GG3" s="125"/>
+      <c r="GH3" s="125"/>
+      <c r="GI3" s="125"/>
+      <c r="GJ3" s="125"/>
+      <c r="GK3" s="125"/>
+      <c r="GL3" s="125"/>
+      <c r="GM3" s="125"/>
+      <c r="GN3" s="125"/>
+      <c r="GO3" s="125"/>
+      <c r="GP3" s="125"/>
+      <c r="GQ3" s="125"/>
+      <c r="GR3" s="125"/>
+      <c r="GS3" s="125"/>
+      <c r="GT3" s="125"/>
+      <c r="GU3" s="125"/>
+      <c r="GV3" s="125"/>
+      <c r="GW3" s="125"/>
+      <c r="GX3" s="125"/>
+      <c r="GY3" s="125"/>
+      <c r="GZ3" s="125"/>
+      <c r="HA3" s="125"/>
+      <c r="HB3" s="125"/>
+      <c r="HC3" s="125"/>
+      <c r="HD3" s="125"/>
+      <c r="HE3" s="125"/>
+      <c r="HF3" s="125"/>
+      <c r="HG3" s="125"/>
+      <c r="HH3" s="125"/>
+      <c r="HI3" s="125"/>
+      <c r="HJ3" s="125"/>
+      <c r="HK3" s="125"/>
+      <c r="HL3" s="125"/>
+      <c r="HM3" s="125"/>
+      <c r="HN3" s="125"/>
+      <c r="HO3" s="125"/>
+      <c r="HP3" s="125"/>
+      <c r="HQ3" s="125"/>
+      <c r="HR3" s="125"/>
+      <c r="HS3" s="125"/>
+      <c r="HT3" s="125"/>
+      <c r="HU3" s="125"/>
+      <c r="HV3" s="125"/>
+      <c r="HW3" s="125"/>
+      <c r="HX3" s="125"/>
+      <c r="HY3" s="125"/>
+      <c r="HZ3" s="125"/>
+      <c r="IA3" s="125"/>
+      <c r="IB3" s="125"/>
+      <c r="IC3" s="125"/>
+      <c r="ID3" s="125"/>
+      <c r="IE3" s="125"/>
+      <c r="IF3" s="125"/>
+      <c r="IG3" s="125"/>
+      <c r="IH3" s="125"/>
+      <c r="II3" s="125"/>
+      <c r="IJ3" s="125"/>
+      <c r="IK3" s="125"/>
+      <c r="IL3" s="125"/>
+      <c r="IM3" s="125"/>
+      <c r="IN3" s="125"/>
+      <c r="IO3" s="125"/>
+      <c r="IP3" s="125"/>
+      <c r="IQ3" s="125"/>
+      <c r="IR3" s="125"/>
+      <c r="IS3" s="125"/>
+      <c r="IT3" s="125"/>
+      <c r="IU3" s="125"/>
+      <c r="IV3" s="125"/>
+      <c r="IW3" s="125"/>
+    </row>
+    <row r="4" spans="1:257" ht="50.1" customHeight="1">
+      <c r="A4" s="129" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="157" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="141" t="s">
-        <v>43</v>
+      <c r="C4" s="157"/>
+      <c r="D4" s="131">
+        <v>77000000</v>
       </c>
-      <c r="J3" s="140" t="s">
-        <v>44</v>
+      <c r="E4" s="129">
+        <v>70000000</v>
       </c>
-      <c r="K3" s="141" t="s">
-        <v>43</v>
+      <c r="F4" s="132">
+        <v>0.12</v>
       </c>
-      <c r="L3" s="140" t="s">
-        <v>44</v>
+      <c r="G4" s="133">
+        <v>12</v>
       </c>
-      <c r="M3" s="161"/>
-      <c r="N3" s="161"/>
-      <c r="O3" s="158"/>
-      <c r="P3" s="142"/>
-      <c r="Q3" s="139"/>
-      <c r="R3" s="139"/>
-      <c r="S3" s="139"/>
-      <c r="T3" s="139"/>
-      <c r="U3" s="139"/>
-      <c r="V3" s="139"/>
-      <c r="W3" s="139"/>
-      <c r="X3" s="139"/>
-      <c r="Y3" s="139"/>
-      <c r="Z3" s="139"/>
-      <c r="AA3" s="139"/>
-      <c r="AB3" s="139"/>
-      <c r="AC3" s="139"/>
-      <c r="AD3" s="139"/>
-      <c r="AE3" s="139"/>
-      <c r="AF3" s="139"/>
-      <c r="AG3" s="139"/>
-      <c r="AH3" s="139"/>
-      <c r="AI3" s="139"/>
-      <c r="AJ3" s="139"/>
-      <c r="AK3" s="139"/>
-      <c r="AL3" s="139"/>
-      <c r="AM3" s="139"/>
-      <c r="AN3" s="139"/>
-      <c r="AO3" s="139"/>
-      <c r="AP3" s="139"/>
-      <c r="AQ3" s="139"/>
-      <c r="AR3" s="139"/>
-      <c r="AS3" s="139"/>
-      <c r="AT3" s="139"/>
-      <c r="AU3" s="139"/>
-      <c r="AV3" s="139"/>
-      <c r="AW3" s="139"/>
-      <c r="AX3" s="139"/>
-      <c r="AY3" s="139"/>
-      <c r="AZ3" s="139"/>
-      <c r="BA3" s="139"/>
-      <c r="BB3" s="139"/>
-      <c r="BC3" s="139"/>
-      <c r="BD3" s="139"/>
-      <c r="BE3" s="139"/>
-      <c r="BF3" s="139"/>
-      <c r="BG3" s="139"/>
-      <c r="BH3" s="139"/>
-      <c r="BI3" s="139"/>
-      <c r="BJ3" s="139"/>
-      <c r="BK3" s="139"/>
-      <c r="BL3" s="139"/>
-      <c r="BM3" s="139"/>
-      <c r="BN3" s="139"/>
-      <c r="BO3" s="139"/>
-      <c r="BP3" s="139"/>
-      <c r="BQ3" s="139"/>
-      <c r="BR3" s="139"/>
-      <c r="BS3" s="139"/>
-      <c r="BT3" s="139"/>
-      <c r="BU3" s="139"/>
-      <c r="BV3" s="139"/>
-      <c r="BW3" s="139"/>
-      <c r="BX3" s="139"/>
-      <c r="BY3" s="139"/>
-      <c r="BZ3" s="139"/>
-      <c r="CA3" s="139"/>
-      <c r="CB3" s="139"/>
-      <c r="CC3" s="139"/>
-      <c r="CD3" s="139"/>
-      <c r="CE3" s="139"/>
-      <c r="CF3" s="139"/>
-      <c r="CG3" s="139"/>
-      <c r="CH3" s="139"/>
-      <c r="CI3" s="139"/>
-      <c r="CJ3" s="139"/>
-      <c r="CK3" s="139"/>
-      <c r="CL3" s="139"/>
-      <c r="CM3" s="139"/>
-      <c r="CN3" s="139"/>
-      <c r="CO3" s="139"/>
-      <c r="CP3" s="139"/>
-      <c r="CQ3" s="139"/>
-      <c r="CR3" s="139"/>
-      <c r="CS3" s="139"/>
-      <c r="CT3" s="139"/>
-      <c r="CU3" s="139"/>
-      <c r="CV3" s="139"/>
-      <c r="CW3" s="139"/>
-      <c r="CX3" s="139"/>
-      <c r="CY3" s="139"/>
-      <c r="CZ3" s="139"/>
-      <c r="DA3" s="139"/>
-      <c r="DB3" s="139"/>
-      <c r="DC3" s="139"/>
-      <c r="DD3" s="139"/>
-      <c r="DE3" s="139"/>
-      <c r="DF3" s="139"/>
-      <c r="DG3" s="139"/>
-      <c r="DH3" s="139"/>
-      <c r="DI3" s="139"/>
-      <c r="DJ3" s="139"/>
-      <c r="DK3" s="139"/>
-      <c r="DL3" s="139"/>
-      <c r="DM3" s="139"/>
-      <c r="DN3" s="139"/>
-      <c r="DO3" s="139"/>
-      <c r="DP3" s="139"/>
-      <c r="DQ3" s="139"/>
-      <c r="DR3" s="139"/>
-      <c r="DS3" s="139"/>
-      <c r="DT3" s="139"/>
-      <c r="DU3" s="139"/>
-      <c r="DV3" s="139"/>
-      <c r="DW3" s="139"/>
-      <c r="DX3" s="139"/>
-      <c r="DY3" s="139"/>
-      <c r="DZ3" s="139"/>
-      <c r="EA3" s="139"/>
-      <c r="EB3" s="139"/>
-      <c r="EC3" s="139"/>
-      <c r="ED3" s="139"/>
-      <c r="EE3" s="139"/>
-      <c r="EF3" s="139"/>
-      <c r="EG3" s="139"/>
-      <c r="EH3" s="139"/>
-      <c r="EI3" s="139"/>
-      <c r="EJ3" s="139"/>
-      <c r="EK3" s="139"/>
-      <c r="EL3" s="139"/>
-      <c r="EM3" s="139"/>
-      <c r="EN3" s="139"/>
-      <c r="EO3" s="139"/>
-      <c r="EP3" s="139"/>
-      <c r="EQ3" s="139"/>
-      <c r="ER3" s="139"/>
-      <c r="ES3" s="139"/>
-      <c r="ET3" s="139"/>
-      <c r="EU3" s="139"/>
-      <c r="EV3" s="139"/>
-      <c r="EW3" s="139"/>
-      <c r="EX3" s="139"/>
-      <c r="EY3" s="139"/>
-      <c r="EZ3" s="139"/>
-      <c r="FA3" s="139"/>
-      <c r="FB3" s="139"/>
-      <c r="FC3" s="139"/>
-      <c r="FD3" s="139"/>
-      <c r="FE3" s="139"/>
-      <c r="FF3" s="139"/>
-      <c r="FG3" s="139"/>
-      <c r="FH3" s="139"/>
-      <c r="FI3" s="139"/>
-      <c r="FJ3" s="139"/>
-      <c r="FK3" s="139"/>
-      <c r="FL3" s="139"/>
-      <c r="FM3" s="139"/>
-      <c r="FN3" s="139"/>
-      <c r="FO3" s="139"/>
-      <c r="FP3" s="139"/>
-      <c r="FQ3" s="139"/>
-      <c r="FR3" s="139"/>
-      <c r="FS3" s="139"/>
-      <c r="FT3" s="139"/>
-      <c r="FU3" s="139"/>
-      <c r="FV3" s="139"/>
-      <c r="FW3" s="139"/>
-      <c r="FX3" s="139"/>
-      <c r="FY3" s="139"/>
-      <c r="FZ3" s="139"/>
-      <c r="GA3" s="139"/>
-      <c r="GB3" s="139"/>
-      <c r="GC3" s="139"/>
-      <c r="GD3" s="139"/>
-      <c r="GE3" s="139"/>
-      <c r="GF3" s="139"/>
-      <c r="GG3" s="139"/>
-      <c r="GH3" s="139"/>
-      <c r="GI3" s="139"/>
-      <c r="GJ3" s="139"/>
-      <c r="GK3" s="139"/>
-      <c r="GL3" s="139"/>
-      <c r="GM3" s="139"/>
-      <c r="GN3" s="139"/>
-      <c r="GO3" s="139"/>
-      <c r="GP3" s="139"/>
-      <c r="GQ3" s="139"/>
-      <c r="GR3" s="139"/>
-      <c r="GS3" s="139"/>
-      <c r="GT3" s="139"/>
-      <c r="GU3" s="139"/>
-      <c r="GV3" s="139"/>
-      <c r="GW3" s="139"/>
-      <c r="GX3" s="139"/>
-      <c r="GY3" s="139"/>
-      <c r="GZ3" s="139"/>
-      <c r="HA3" s="139"/>
-      <c r="HB3" s="139"/>
-      <c r="HC3" s="139"/>
-      <c r="HD3" s="139"/>
-      <c r="HE3" s="139"/>
-      <c r="HF3" s="139"/>
-      <c r="HG3" s="139"/>
-      <c r="HH3" s="139"/>
-      <c r="HI3" s="139"/>
-      <c r="HJ3" s="139"/>
-      <c r="HK3" s="139"/>
-      <c r="HL3" s="139"/>
-      <c r="HM3" s="139"/>
-      <c r="HN3" s="139"/>
-      <c r="HO3" s="139"/>
-      <c r="HP3" s="139"/>
-      <c r="HQ3" s="139"/>
-      <c r="HR3" s="139"/>
-      <c r="HS3" s="139"/>
-      <c r="HT3" s="139"/>
-      <c r="HU3" s="139"/>
-      <c r="HV3" s="139"/>
-      <c r="HW3" s="139"/>
-      <c r="HX3" s="139"/>
-      <c r="HY3" s="139"/>
-      <c r="HZ3" s="139"/>
-      <c r="IA3" s="139"/>
-      <c r="IB3" s="139"/>
-      <c r="IC3" s="139"/>
-      <c r="ID3" s="139"/>
-      <c r="IE3" s="139"/>
-      <c r="IF3" s="139"/>
-      <c r="IG3" s="139"/>
-      <c r="IH3" s="139"/>
-      <c r="II3" s="139"/>
-      <c r="IJ3" s="139"/>
-      <c r="IK3" s="139"/>
-      <c r="IL3" s="139"/>
-      <c r="IM3" s="139"/>
-      <c r="IN3" s="139"/>
-      <c r="IO3" s="139"/>
-      <c r="IP3" s="139"/>
-      <c r="IQ3" s="139"/>
-      <c r="IR3" s="139"/>
-      <c r="IS3" s="139"/>
-      <c r="IT3" s="139"/>
-      <c r="IU3" s="139"/>
-      <c r="IV3" s="139"/>
-      <c r="IW3" s="139"/>
+      <c r="H4" s="131">
+        <f>E4*F4</f>
+        <v>8400000</v>
+      </c>
+      <c r="I4" s="136">
+        <v>6</v>
+      </c>
+      <c r="J4" s="131">
+        <f>H4/(G4/I4)</f>
+        <v>4200000</v>
+      </c>
+      <c r="K4" s="136">
+        <v>6</v>
+      </c>
+      <c r="L4" s="131">
+        <f>H4-J4</f>
+        <v>4200000</v>
+      </c>
+      <c r="M4" s="157"/>
+      <c r="N4" s="157"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="134"/>
+      <c r="Q4" s="135"/>
     </row>
-    <row r="4" spans="1:257" ht="50.1" customHeight="1">
-      <c r="A4" s="143" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="162" t="s">
+    <row r="5" spans="1:257" ht="39.950000000000003" customHeight="1">
+      <c r="A5" s="158" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="162"/>
-      <c r="D4" s="145">
-        <v>77000000</v>
-      </c>
-      <c r="E4" s="143">
-        <f>D4/1.1</f>
-        <v>70000000</v>
-      </c>
-      <c r="F4" s="146">
-        <v>0.12</v>
-      </c>
-      <c r="G4" s="147">
-        <v>12</v>
-      </c>
-      <c r="H4" s="145">
-        <f>E4*F4*93.84%</f>
-        <v>7882560</v>
-      </c>
-      <c r="I4" s="164">
-        <v>6</v>
-      </c>
-      <c r="J4" s="145">
-        <f>H4/(G4/I4)</f>
-        <v>3941280</v>
-      </c>
-      <c r="K4" s="164">
-        <v>6</v>
-      </c>
-      <c r="L4" s="145">
-        <f>H4/(G4/K4)</f>
-        <v>3941280</v>
-      </c>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="144"/>
-      <c r="P4" s="148"/>
-      <c r="Q4" s="149"/>
-    </row>
-    <row r="5" spans="1:257" ht="39.950000000000003" customHeight="1">
-      <c r="A5" s="163" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="163"/>
-      <c r="C5" s="163"/>
-      <c r="D5" s="163"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="163"/>
-      <c r="G5" s="163"/>
-      <c r="H5" s="163"/>
-      <c r="I5" s="163"/>
-      <c r="J5" s="163"/>
-      <c r="K5" s="163"/>
-      <c r="L5" s="163"/>
-      <c r="M5" s="163"/>
-      <c r="N5" s="163"/>
-      <c r="O5" s="163"/>
+      <c r="B5" s="158"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="158"/>
+      <c r="J5" s="158"/>
+      <c r="K5" s="158"/>
+      <c r="L5" s="158"/>
+      <c r="M5" s="158"/>
+      <c r="N5" s="158"/>
+      <c r="O5" s="158"/>
     </row>
     <row r="10" spans="1:257">
-      <c r="I10" s="149"/>
+      <c r="I10" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="14">
